--- a/PhD_PI_Listup.xlsx
+++ b/PhD_PI_Listup.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyeonbeen/Git/LaTeX-Docs/MyResume/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEA982D-EBBB-E94A-A1C4-DA94695CFC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03602441-7217-B54C-9795-127C04E67285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{422F52E5-BD25-DB4D-B83C-2D9AD22AB820}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="22540" activeTab="1" xr2:uid="{422F52E5-BD25-DB4D-B83C-2D9AD22AB820}"/>
   </bookViews>
   <sheets>
     <sheet name="Professors" sheetId="1" r:id="rId1"/>
     <sheet name="Programs" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Professors!$E$1:$E$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Professors!$E$1:$E$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="471">
   <si>
     <t>PI</t>
   </si>
@@ -90,6 +90,9 @@
     <t>Shuran Song</t>
   </si>
   <si>
+    <t>EE, CS</t>
+  </si>
+  <si>
     <t>Jeannette Bohg</t>
   </si>
   <si>
@@ -141,12 +144,6 @@
     <t>Koushil Sreenath</t>
   </si>
   <si>
-    <t>Control theory, Language-guided RL, Humanoid</t>
-  </si>
-  <si>
-    <t>Not mentioned?</t>
-  </si>
-  <si>
     <t>Roberto Horowitz</t>
   </si>
   <si>
@@ -237,9 +234,6 @@
     <t>Aniket Bera</t>
   </si>
   <si>
-    <t>Possible</t>
-  </si>
-  <si>
     <t>IE</t>
   </si>
   <si>
@@ -256,9 +250,6 @@
   </si>
   <si>
     <t>Ahmed H. Qureshi</t>
-  </si>
-  <si>
-    <t>Motion planning and generation, Diffusion RL, HRI</t>
   </si>
   <si>
     <t>Carnegie Mellon</t>
@@ -406,9 +397,6 @@
     <t>ROBO, EECS, ME</t>
   </si>
   <si>
-    <t>Control, Tactile, interaction, Multimodal RL (visuo-tactile)</t>
-  </si>
-  <si>
     <t>Cornell</t>
   </si>
   <si>
@@ -622,20 +610,6 @@
   </si>
   <si>
     <t>Daniel Seita</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Multimodal representation for RL, Foundation model, Whole body control, HRI, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Not recruiting</t>
-    </r>
   </si>
   <si>
     <t>Not Recruiting</t>
@@ -736,9 +710,6 @@
     <t>Skill learning, Neurosymbolic, Representation learning, RL</t>
   </si>
   <si>
-    <t>No but Little picky</t>
-  </si>
-  <si>
     <t>NYU</t>
   </si>
   <si>
@@ -944,9 +915,6 @@
   </si>
   <si>
     <t>Real-world RL, Skills from videos, VLM-guided manipulation</t>
-  </si>
-  <si>
-    <t>CannotReply</t>
   </si>
   <si>
     <t>Camillo J. Taylor</t>
@@ -1516,6 +1484,187 @@
   <si>
     <t>#5 PI</t>
   </si>
+  <si>
+    <t>UT Dallas</t>
+  </si>
+  <si>
+    <t>Yu Xiang</t>
+  </si>
+  <si>
+    <t>Multimodal reference, Transfer learning, Knowledge distilliation, Vision, Haptic...</t>
+  </si>
+  <si>
+    <t>UMass Amherst</t>
+  </si>
+  <si>
+    <t>CICS</t>
+  </si>
+  <si>
+    <t>Scott Niekum</t>
+  </si>
+  <si>
+    <t>RL algorithm base,Transfer learning, Foundation models</t>
+  </si>
+  <si>
+    <t>UNC Chapel Hill</t>
+  </si>
+  <si>
+    <t>Mingyu Ding</t>
+  </si>
+  <si>
+    <t>RL manipulation, Physics-aware, simulation, foundation models, Multimodal LLMs, reasoning</t>
+  </si>
+  <si>
+    <t>UVA</t>
+  </si>
+  <si>
+    <t>Yen-Ling Kuo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language, vision, multimodal based robot manipulation, diffusion policy, </t>
+  </si>
+  <si>
+    <t>CS, SIE</t>
+  </si>
+  <si>
+    <t>Tariq Iqbal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multimodal learning, HRI, HR teaming and collab, </t>
+  </si>
+  <si>
+    <t>ISU</t>
+  </si>
+  <si>
+    <t>Cody Fleming</t>
+  </si>
+  <si>
+    <t>VLM, RL, motion planning for UAV, Multi-agent</t>
+  </si>
+  <si>
+    <t>After admission</t>
+  </si>
+  <si>
+    <t>Henrik I. Christensen</t>
+  </si>
+  <si>
+    <t>Work closely with Hao Su, SLAM &amp; manipulation RL</t>
+  </si>
+  <si>
+    <t>Coming soon..? No need to email</t>
+  </si>
+  <si>
+    <t>Contact to students..?</t>
+  </si>
+  <si>
+    <t>HRI, Sparse rewards, Visual context</t>
+  </si>
+  <si>
+    <t>RL+PINN+Physics aware policy</t>
+  </si>
+  <si>
+    <t>Mention in appl.</t>
+  </si>
+  <si>
+    <t>Motion planning and generation, Diffusion RL, 3D vision, HRI</t>
+  </si>
+  <si>
+    <t>합격 가망이 안보인다여긴</t>
+  </si>
+  <si>
+    <t>After admission or submission</t>
+  </si>
+  <si>
+    <t>No, mention in SOP</t>
+  </si>
+  <si>
+    <t>Form</t>
+  </si>
+  <si>
+    <t>Yes, but you'll not be replied</t>
+  </si>
+  <si>
+    <t>Apply and mention</t>
+  </si>
+  <si>
+    <t>Yes with Research Statement</t>
+  </si>
+  <si>
+    <t>No..? Officially apply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBO, EECS </t>
+  </si>
+  <si>
+    <t>Vision, Long term pose gen, Robotics, Simulation</t>
+  </si>
+  <si>
+    <t>CONTACT, Deformable object, Language guided, diffusion RL</t>
+  </si>
+  <si>
+    <t>Tactile, Control, interaction, Multimodal RL (visuo-tactile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vision, Locomotion, Mobile manipulation, </t>
+  </si>
+  <si>
+    <t>Officially apply, slow respond</t>
+  </si>
+  <si>
+    <t>Apply and mention, admitting new PhD</t>
+  </si>
+  <si>
+    <t>Can send me but likely not replying</t>
+  </si>
+  <si>
+    <t>Apply and mention, cannotReply</t>
+  </si>
+  <si>
+    <t>Yes, Looking for PhD</t>
+  </si>
+  <si>
+    <t>No, apply officially and thats all</t>
+  </si>
+  <si>
+    <t>apply and mention</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Multimodal representation for RL, Foundation model, Whole body control, HRI, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Not recruiting</t>
+    </r>
+  </si>
+  <si>
+    <t>freely send After Submission</t>
+  </si>
+  <si>
+    <t>Contact if you're connectable</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Form and email</t>
+  </si>
+  <si>
+    <t>Robotics Specialty</t>
+  </si>
+  <si>
+    <t>RL algorithm, General robot policies</t>
+  </si>
+  <si>
+    <t>Locomotion, Control theory, Language-guided RL, Humanoid</t>
+  </si>
 </sst>
 </file>
 
@@ -1525,7 +1674,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1578,20 +1727,36 @@
       <family val="1"/>
     </font>
     <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
+      <b/>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1634,6 +1799,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1648,7 +1819,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1668,7 +1839,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1728,7 +1899,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1758,7 +1929,7 @@
     <xf numFmtId="10" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
@@ -1776,10 +1947,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2118,7 +2298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132F7052-85E4-E84F-9E71-39A4BFB15A06}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" style="5" bestFit="1" customWidth="1"/>
@@ -2126,7 +2306,7 @@
     <col min="3" max="3" width="19.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="102.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="56.6640625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="1"/>
@@ -2146,16 +2326,16 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -2169,19 +2349,19 @@
         <v>7</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
@@ -2198,10 +2378,10 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -2218,10 +2398,10 @@
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -2238,10 +2418,10 @@
         <v>14</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -2252,16 +2432,16 @@
         <v>10</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -2272,16 +2452,16 @@
         <v>10</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -2289,19 +2469,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -2309,1658 +2489,1973 @@
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>420</v>
+        <v>16</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>33</v>
+        <v>470</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>34</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>38</v>
-      </c>
       <c r="E13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>21</v>
+      <c r="F15" s="13" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>41</v>
+      <c r="F18" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>51</v>
-      </c>
       <c r="D19" s="12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="E21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="1" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>23</v>
+      <c r="D22" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="12" t="s">
+      <c r="D26" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>76</v>
+      <c r="F26" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C27" s="3" t="s">
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F29" s="23"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>405</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>404</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>403</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>407</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="13"/>
+      <c r="E31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F32" s="23"/>
+        <v>130</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="C33" s="13" t="s">
+      <c r="A33" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F33" s="13"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>409</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="23" t="s">
-        <v>21</v>
+      <c r="D34" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C35" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="41" t="s">
+        <v>351</v>
+      </c>
+      <c r="B39" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>353</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D40" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D41" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E35" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F35" s="23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="41" t="s">
-        <v>358</v>
-      </c>
-      <c r="B36" s="42" t="s">
-        <v>405</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>360</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="E41" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>417</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>23</v>
+      <c r="F41" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="14" t="s">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>390</v>
+        <v>85</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>391</v>
+        <v>86</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>60</v>
+        <v>445</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="14" t="s">
-        <v>389</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>23</v>
+      <c r="A43" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>41</v>
+      <c r="A45" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="B46" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>102</v>
+        <v>382</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>388</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>105</v>
+        <v>387</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>31</v>
+        <v>130</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="45" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="E52" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E53" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>29</v>
+      <c r="F53" s="13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="F58" s="13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E59" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>31</v>
+      <c r="F59" s="13" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="E70" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C60" s="3" t="s">
+      <c r="F70" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="B72" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E72" s="12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F62" s="6"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="F63" s="20"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F64" s="6"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F67" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B69" s="22" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="E69" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F69" s="22"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>154</v>
+      <c r="F72" s="13" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="14" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>156</v>
+        <v>309</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>157</v>
+        <v>310</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>120</v>
+        <v>459</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="15" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>159</v>
+        <v>304</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F74" s="16"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C75" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F75" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>29</v>
+      <c r="A76" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E77" s="12" t="s">
+      <c r="A77" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F77" s="13" t="s">
-        <v>167</v>
+      <c r="F77" s="3" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="14" t="s">
-        <v>155</v>
+        <v>347</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>171</v>
+        <v>88</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="E78" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F78" s="12"/>
-    </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B80" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="E80" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F80" s="16"/>
+      <c r="F80" s="13" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="15" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>120</v>
+        <v>461</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="15" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F82" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="F82" s="17" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B84" s="1" t="s">
+      <c r="A84" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="B84" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>59</v>
+      <c r="C84" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D84" s="42" t="s">
+        <v>463</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F84" s="47" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F87" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E88" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F88" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B89" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="E89" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F89" s="17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="B85" s="12" t="s">
+      <c r="D92" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C93" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="D93" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="D85" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F85" s="13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="B86" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B90" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C90" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="D90" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="E90" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F90" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B91" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C91" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="D91" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="E91" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F91" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>134</v>
+      <c r="E93" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>277</v>
+      <c r="C94" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>31</v>
+        <v>191</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>278</v>
+      <c r="C95" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>29</v>
+        <v>190</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D97" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F97" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B98" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C98" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F98" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F100" s="17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B101" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F101" s="17" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="D104" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="E104" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F104" s="20" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F106" s="13" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="E107" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F107" s="17" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="E109" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F109" s="17" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E91" xr:uid="{132F7052-85E4-E84F-9E71-39A4BFB15A06}">
+  <autoFilter ref="E1:E98" xr:uid="{132F7052-85E4-E84F-9E71-39A4BFB15A06}">
     <filterColumn colId="0">
       <filters blank="1">
         <filter val="High"/>
@@ -3980,127 +4475,187 @@
     <hyperlink ref="C7" r:id="rId8" xr:uid="{5C6D8E4D-C69F-A546-95DE-EE42D8AB8089}"/>
     <hyperlink ref="C10" r:id="rId9" xr:uid="{A9020D64-DAB9-3E47-AED5-6AE7F10D93A8}"/>
     <hyperlink ref="C11" r:id="rId10" xr:uid="{9FE9E8C0-9671-FD4F-88A9-79291BC64D5A}"/>
-    <hyperlink ref="F11" r:id="rId11" display="?" xr:uid="{66F59F4B-9B01-7546-AFBB-CA1740AC4F67}"/>
+    <hyperlink ref="F11" r:id="rId11" xr:uid="{66F59F4B-9B01-7546-AFBB-CA1740AC4F67}"/>
     <hyperlink ref="C12" r:id="rId12" xr:uid="{7A0A8504-2B7E-8346-B9B4-6FA6C3FB59FE}"/>
     <hyperlink ref="C13" r:id="rId13" xr:uid="{A233F54A-7B3B-BF49-A4DB-C70550B00017}"/>
-    <hyperlink ref="C14" r:id="rId14" xr:uid="{5327D505-B7E7-AB42-A864-D87C1C130843}"/>
-    <hyperlink ref="F14" r:id="rId15" xr:uid="{7D4005A3-151D-DD46-A15F-D83D01E657AD}"/>
-    <hyperlink ref="F15" r:id="rId16" xr:uid="{A04EC1EA-D533-8D41-8207-24B50E7927DD}"/>
-    <hyperlink ref="F16" r:id="rId17" xr:uid="{E4A60B9C-4533-BA49-AD0B-F4AA55DBD473}"/>
-    <hyperlink ref="C16" r:id="rId18" xr:uid="{88BA93F9-325B-1949-A84B-841920F3AC87}"/>
-    <hyperlink ref="C15" r:id="rId19" xr:uid="{B81D9CC2-9D59-FB40-BF26-550E35A86B3E}"/>
-    <hyperlink ref="C17" r:id="rId20" xr:uid="{DC62901E-0D49-2C46-BBB6-DFCA02929FC3}"/>
-    <hyperlink ref="C18" r:id="rId21" xr:uid="{A7425927-15C9-2B47-B442-D6622AB3DD92}"/>
-    <hyperlink ref="F18" r:id="rId22" xr:uid="{CB83AE0D-0C3B-CC42-B83C-BDBD28D88240}"/>
-    <hyperlink ref="B18" r:id="rId23" display="ME, ROBO(preferred)" xr:uid="{35C45632-B60B-C64F-9579-4518F537C884}"/>
-    <hyperlink ref="C19" r:id="rId24" xr:uid="{4332801B-5602-114C-BE41-15DDA2A562E6}"/>
-    <hyperlink ref="F19" r:id="rId25" xr:uid="{F29BDC9E-0153-1448-AA28-33241D6A26BB}"/>
-    <hyperlink ref="C20" r:id="rId26" xr:uid="{77807196-58B3-1740-9207-03DFFAE42BC7}"/>
-    <hyperlink ref="F20" r:id="rId27" display="Yes" xr:uid="{0B091E55-ADC9-6B48-99BF-94530DA49108}"/>
-    <hyperlink ref="C21" r:id="rId28" xr:uid="{6C3CEE39-37EF-8643-9408-7143832EE6CC}"/>
-    <hyperlink ref="F21" r:id="rId29" location="heading=h.o56b04aeo1c9" display="No" xr:uid="{4A448277-35FA-D54B-878F-7884D25EF08A}"/>
-    <hyperlink ref="C22" r:id="rId30" location="content4-e" xr:uid="{68DAC647-2FF5-7D40-9B3F-A7CFDE9F9724}"/>
-    <hyperlink ref="C23" r:id="rId31" xr:uid="{39872464-0223-E74D-B0EB-E1DD076A4CD2}"/>
-    <hyperlink ref="C25" r:id="rId32" xr:uid="{B0DEBDAF-2E75-E74D-8BE7-D41D17A6F850}"/>
-    <hyperlink ref="C24" r:id="rId33" xr:uid="{BBC8B767-1512-6649-8B7F-9F2D824F0F9D}"/>
-    <hyperlink ref="C26" r:id="rId34" location="projects" xr:uid="{FFF4F158-9F83-CE48-9808-B7D6B356CC4F}"/>
-    <hyperlink ref="F26" r:id="rId35" xr:uid="{BFC1CA03-B547-7042-BAFD-B8F6E90D8427}"/>
-    <hyperlink ref="C28" r:id="rId36" xr:uid="{EC3E5B97-7A3C-5A49-931B-B173E87B0151}"/>
-    <hyperlink ref="F28" r:id="rId37" xr:uid="{A610CFA6-EE72-D14E-80CD-4848929AE14C}"/>
-    <hyperlink ref="C27" r:id="rId38" xr:uid="{78B13E7E-1127-A547-8244-FA6E5002698A}"/>
-    <hyperlink ref="C35" r:id="rId39" xr:uid="{7E848999-856A-A849-B657-521AADD30D66}"/>
-    <hyperlink ref="F35" r:id="rId40" xr:uid="{4C566A0A-64A5-BA44-A80B-CCB366CCF7AD}"/>
-    <hyperlink ref="C37" r:id="rId41" xr:uid="{3DD32363-C20D-0F48-A8AB-04A87B8806EB}"/>
-    <hyperlink ref="C38" r:id="rId42" xr:uid="{79D9D827-AAB5-2D4B-99E3-474BC0B9AA4E}"/>
-    <hyperlink ref="F38" r:id="rId43" xr:uid="{12ACB131-F843-B04E-B2C8-B048573A0F61}"/>
-    <hyperlink ref="F37" r:id="rId44" xr:uid="{9BAD156A-7083-9041-ABF4-2FF0E51F57B4}"/>
-    <hyperlink ref="C39" r:id="rId45" xr:uid="{121EFBFF-EE3D-C34F-8C33-A880AD30A609}"/>
-    <hyperlink ref="F39" r:id="rId46" xr:uid="{39D7A72A-DF53-1742-94F2-6C1949649485}"/>
-    <hyperlink ref="C41" r:id="rId47" xr:uid="{58A1494B-6445-E54C-B70A-94BCC8E76B48}"/>
-    <hyperlink ref="F41" r:id="rId48" xr:uid="{F2B34C73-0BB9-804C-82A8-83FD1428FCF4}"/>
-    <hyperlink ref="C40" r:id="rId49" xr:uid="{B5BEFC2B-5EBE-AF43-A956-2C83591CC3A1}"/>
-    <hyperlink ref="F40" r:id="rId50" xr:uid="{C7BA0F10-763D-C044-AC03-318F8F3912C1}"/>
-    <hyperlink ref="C45" r:id="rId51" location="_ri" xr:uid="{398354CA-7B5B-9149-A6A1-EA339C4F9153}"/>
-    <hyperlink ref="F45" r:id="rId52" xr:uid="{577E5293-D8C5-FB4A-B5D2-4D68FFEF909A}"/>
-    <hyperlink ref="F46" r:id="rId53" xr:uid="{46E24BC5-2E2D-1143-A5E2-B03653E054B3}"/>
-    <hyperlink ref="C46" r:id="rId54" xr:uid="{D4E488D7-008C-7041-89A3-A142D3179430}"/>
-    <hyperlink ref="C47" r:id="rId55" xr:uid="{7525C0C7-0476-1844-80BD-C64A1FD08428}"/>
-    <hyperlink ref="C48" r:id="rId56" location="Publications-Section" xr:uid="{D2E4E0C6-3578-7842-9B7B-3D4E15B431D2}"/>
-    <hyperlink ref="C49" r:id="rId57" xr:uid="{9493C1D5-873A-914C-B90E-FEEDC858E63A}"/>
-    <hyperlink ref="C50" r:id="rId58" xr:uid="{903CD93B-52AB-4244-9247-F63FFBC2B66E}"/>
-    <hyperlink ref="C51" r:id="rId59" xr:uid="{E11FE763-70DE-C843-98C2-D0666AEC11CB}"/>
-    <hyperlink ref="F51" r:id="rId60" xr:uid="{578842D3-A5E6-9A4D-A12F-433FEB4AA4A9}"/>
-    <hyperlink ref="F52" r:id="rId61" xr:uid="{6857B64A-8193-8C49-B5DE-EF672F9FE0C8}"/>
-    <hyperlink ref="C52" r:id="rId62" location="teaching-section" xr:uid="{3FEB6C00-AB64-8848-A2BB-19CE73970FA2}"/>
-    <hyperlink ref="C53" r:id="rId63" xr:uid="{6888BF5B-E86F-B943-B6F3-8320FAFA1445}"/>
-    <hyperlink ref="C54" r:id="rId64" xr:uid="{4950B2C5-F17D-624A-AE62-9834277190C0}"/>
-    <hyperlink ref="C55" r:id="rId65" xr:uid="{EB00FB88-140C-FF4E-97F0-7A534D9127FD}"/>
-    <hyperlink ref="F55" r:id="rId66" xr:uid="{C81212D7-0A6B-AC4F-A3BB-87C0DF2B141B}"/>
-    <hyperlink ref="C56" r:id="rId67" xr:uid="{28FD696E-AA3D-5340-9AEE-9B33DAA9100D}"/>
-    <hyperlink ref="F56" r:id="rId68" xr:uid="{301665C9-748B-B74C-8E22-3C2BE315B9A0}"/>
-    <hyperlink ref="C57" r:id="rId69" xr:uid="{9BEA1D4E-E0E9-7F4D-95FF-AA1E5A0A38A7}"/>
-    <hyperlink ref="C58" r:id="rId70" xr:uid="{C54146DC-1962-304A-9ADE-27C93D064A33}"/>
-    <hyperlink ref="F58" r:id="rId71" xr:uid="{BB877229-AE13-9D41-B111-355DE3218E1F}"/>
-    <hyperlink ref="C59" r:id="rId72" xr:uid="{CAE1FF08-3B4A-AF4B-A8FA-73AF2979DDFB}"/>
-    <hyperlink ref="C65" r:id="rId73" xr:uid="{FD5EA699-A473-E14B-A007-8B39747A7B97}"/>
-    <hyperlink ref="F65" r:id="rId74" xr:uid="{2F58E973-C7F1-6F4F-992D-3FE73FC1921B}"/>
-    <hyperlink ref="C67" r:id="rId75" xr:uid="{908C7485-2276-F845-B011-956C90745E36}"/>
-    <hyperlink ref="C68" r:id="rId76" xr:uid="{56CA5437-DF65-7741-BCB4-0097BF46AF5A}"/>
-    <hyperlink ref="C71" r:id="rId77" xr:uid="{E3A4C8BD-C578-CD47-ACE1-48F233318094}"/>
-    <hyperlink ref="C72" r:id="rId78" xr:uid="{BB02585E-E4AF-7B40-A5E2-FA20343B6B7D}"/>
-    <hyperlink ref="F72" r:id="rId79" xr:uid="{11068305-3E64-9847-B25B-E7B4232FDC83}"/>
-    <hyperlink ref="F67" r:id="rId80" xr:uid="{E1F068DF-7982-B140-891F-18371252BEE9}"/>
-    <hyperlink ref="F71" r:id="rId81" xr:uid="{4857BCFA-63F9-D343-996F-B0086015D867}"/>
-    <hyperlink ref="C73" r:id="rId82" xr:uid="{8478D9E5-A9E7-1F41-9E1F-E87F15560F85}"/>
-    <hyperlink ref="F73" r:id="rId83" xr:uid="{F208C5E3-A0C4-1D4B-91C0-2BDC60993E9E}"/>
-    <hyperlink ref="C74" r:id="rId84" xr:uid="{45834B70-B9CF-874E-BDDD-07DC65A97A82}"/>
-    <hyperlink ref="C75" r:id="rId85" xr:uid="{5999988D-62DD-7740-8281-D4A8476498DF}"/>
-    <hyperlink ref="C76" r:id="rId86" xr:uid="{D4D3BD11-6490-B646-B302-20BFB3D7DF5F}"/>
-    <hyperlink ref="C77" r:id="rId87" xr:uid="{923B455F-766D-1245-B440-3E155C36EB08}"/>
-    <hyperlink ref="F77" r:id="rId88" xr:uid="{13585F3B-4D88-FD44-80C6-27534407E6B3}"/>
-    <hyperlink ref="C78" r:id="rId89" location="conference-publications" xr:uid="{1A804911-E79D-9141-A167-60595CEE1F71}"/>
-    <hyperlink ref="C79" r:id="rId90" xr:uid="{3D2271F2-C077-F646-9F3C-5EB7256C0CF2}"/>
-    <hyperlink ref="C80" r:id="rId91" xr:uid="{51A16F76-2C2A-6C41-8E1D-A56F68000383}"/>
-    <hyperlink ref="C81" r:id="rId92" xr:uid="{B3FE6472-8368-3248-AA97-CD0B8A02AD56}"/>
-    <hyperlink ref="F81" r:id="rId93" xr:uid="{CFB38AB7-6FFD-7543-9665-38F4AF916308}"/>
-    <hyperlink ref="C82" r:id="rId94" xr:uid="{6E550245-9521-014D-B426-EDEBB6147E4A}"/>
-    <hyperlink ref="C83" r:id="rId95" xr:uid="{E81A1570-9990-814E-A1D5-C6962C1806DF}"/>
-    <hyperlink ref="C84" r:id="rId96" xr:uid="{D7C55900-5024-034A-80F6-B1670134D8A0}"/>
-    <hyperlink ref="C85" r:id="rId97" xr:uid="{7A00C4FC-9BB4-A242-A1B2-00F729E0EA3E}"/>
-    <hyperlink ref="F85" r:id="rId98" display="Little picky" xr:uid="{59CA0194-3E75-0C43-B43E-0C657B6C82D9}"/>
-    <hyperlink ref="F86" r:id="rId99" xr:uid="{CB8A4941-FC1A-754C-A7FD-599935DB3F31}"/>
-    <hyperlink ref="C86" r:id="rId100" location="publications" xr:uid="{8EFA9C06-FE89-7447-91CE-180A9ED16794}"/>
-    <hyperlink ref="C89" r:id="rId101" xr:uid="{1855347E-1501-8D43-99C6-EDC1CFB4E3C1}"/>
-    <hyperlink ref="C90" r:id="rId102" xr:uid="{E744FF8F-6454-894D-BD61-E9C957C07630}"/>
-    <hyperlink ref="C91" r:id="rId103" xr:uid="{7BFC847F-6034-004A-AE72-78A60552C37F}"/>
-    <hyperlink ref="C61" r:id="rId104" xr:uid="{3CAB4899-21CA-0746-9AC4-6377AFF983C9}"/>
-    <hyperlink ref="F61" r:id="rId105" xr:uid="{03AA3462-3833-5642-8AD2-02DEA2EB7DBF}"/>
-    <hyperlink ref="C62" r:id="rId106" xr:uid="{0AFF4185-421E-A044-8B14-063F232DF23C}"/>
-    <hyperlink ref="C63" r:id="rId107" xr:uid="{29B84BC6-13E1-D044-A869-EB5134497CD6}"/>
-    <hyperlink ref="C60" r:id="rId108" xr:uid="{B013B9EF-FD6B-4A41-9F39-38433F1DCC01}"/>
-    <hyperlink ref="C64" r:id="rId109" location="publications" xr:uid="{5E9B8B5B-7402-A34B-99E6-3C227D4F15CC}"/>
-    <hyperlink ref="C92" r:id="rId110" xr:uid="{C0F1ADC4-2A51-C345-9349-4003E44424D3}"/>
-    <hyperlink ref="C93" r:id="rId111" xr:uid="{1DE714D0-AA68-304E-8CCC-E3DEACD98304}"/>
-    <hyperlink ref="C94" r:id="rId112" display="https://adaptive-robotics-lab.github.io/publications/" xr:uid="{E2444A72-A995-5841-989A-59F8AF15478C}"/>
-    <hyperlink ref="C95" r:id="rId113" xr:uid="{3FD7C805-92F3-A749-8523-B5D649B8F890}"/>
-    <hyperlink ref="C66" r:id="rId114" xr:uid="{40710B08-AA99-674E-A8D0-57AD1EC6F7F0}"/>
-    <hyperlink ref="F66" r:id="rId115" xr:uid="{7723E8AA-A3DD-F942-9BD3-714A761F568E}"/>
-    <hyperlink ref="C69" r:id="rId116" xr:uid="{90C16231-A7FD-A64F-9A5A-23E4BF55CB78}"/>
-    <hyperlink ref="C70" r:id="rId117" xr:uid="{7D14C868-8C11-F341-893C-8FA380BE026F}"/>
-    <hyperlink ref="C36" r:id="rId118" xr:uid="{69317078-8695-5A49-99D1-8B4E2BC4589E}"/>
-    <hyperlink ref="F84" r:id="rId119" xr:uid="{C41937AD-C8AA-6949-BD93-5A3AAC89257A}"/>
-    <hyperlink ref="C42" r:id="rId120" xr:uid="{949E7CA5-065E-0649-9348-614FE6505218}"/>
-    <hyperlink ref="F42" r:id="rId121" xr:uid="{994371A4-342D-F348-B88E-265C6A27BF72}"/>
-    <hyperlink ref="C44" r:id="rId122" xr:uid="{05889E0F-3F97-D04C-9B20-AAD392054221}"/>
-    <hyperlink ref="C43" r:id="rId123" xr:uid="{33DBF5E1-B81D-2142-83D8-9C7A127864C4}"/>
-    <hyperlink ref="C34" r:id="rId124" xr:uid="{70A5B074-FE39-E04D-AFDE-543B180584E3}"/>
-    <hyperlink ref="F34" r:id="rId125" xr:uid="{7DF036FC-9EA0-5E45-8FE0-AF7D834D24A5}"/>
-    <hyperlink ref="C33" r:id="rId126" xr:uid="{CFCA4AD5-6D8E-CB44-A671-333BE022437B}"/>
-    <hyperlink ref="C32" r:id="rId127" xr:uid="{B4346412-B077-4844-ABEA-8398BD09DDA1}"/>
-    <hyperlink ref="F30" r:id="rId128" xr:uid="{219FC3BD-1ECB-BC44-9FA1-411B97509B53}"/>
-    <hyperlink ref="C31" r:id="rId129" display="https://r-pad.github.io/publications/" xr:uid="{4DA529A4-12B5-7D4F-B712-E4D97CFDAEDB}"/>
-    <hyperlink ref="C30" r:id="rId130" xr:uid="{B5109ACE-0258-1F44-836F-DF406D7A1D75}"/>
-    <hyperlink ref="C29" r:id="rId131" xr:uid="{0A1707DB-8872-0648-B9E4-B8A0B8B1F90C}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{5327D505-B7E7-AB42-A864-D87C1C130843}"/>
+    <hyperlink ref="F15" r:id="rId15" display="Yes" xr:uid="{7D4005A3-151D-DD46-A15F-D83D01E657AD}"/>
+    <hyperlink ref="F16" r:id="rId16" xr:uid="{A04EC1EA-D533-8D41-8207-24B50E7927DD}"/>
+    <hyperlink ref="F17" r:id="rId17" xr:uid="{E4A60B9C-4533-BA49-AD0B-F4AA55DBD473}"/>
+    <hyperlink ref="C17" r:id="rId18" xr:uid="{88BA93F9-325B-1949-A84B-841920F3AC87}"/>
+    <hyperlink ref="C16" r:id="rId19" xr:uid="{B81D9CC2-9D59-FB40-BF26-550E35A86B3E}"/>
+    <hyperlink ref="C18" r:id="rId20" xr:uid="{DC62901E-0D49-2C46-BBB6-DFCA02929FC3}"/>
+    <hyperlink ref="C19" r:id="rId21" xr:uid="{A7425927-15C9-2B47-B442-D6622AB3DD92}"/>
+    <hyperlink ref="F19" r:id="rId22" xr:uid="{CB83AE0D-0C3B-CC42-B83C-BDBD28D88240}"/>
+    <hyperlink ref="B19" r:id="rId23" display="ME, ROBO(preferred)" xr:uid="{35C45632-B60B-C64F-9579-4518F537C884}"/>
+    <hyperlink ref="C20" r:id="rId24" xr:uid="{4332801B-5602-114C-BE41-15DDA2A562E6}"/>
+    <hyperlink ref="F20" r:id="rId25" xr:uid="{F29BDC9E-0153-1448-AA28-33241D6A26BB}"/>
+    <hyperlink ref="C21" r:id="rId26" xr:uid="{77807196-58B3-1740-9207-03DFFAE42BC7}"/>
+    <hyperlink ref="F21" r:id="rId27" display="Yes" xr:uid="{0B091E55-ADC9-6B48-99BF-94530DA49108}"/>
+    <hyperlink ref="C23" r:id="rId28" xr:uid="{6C3CEE39-37EF-8643-9408-7143832EE6CC}"/>
+    <hyperlink ref="F23" r:id="rId29" location="heading=h.o56b04aeo1c9" display="No" xr:uid="{4A448277-35FA-D54B-878F-7884D25EF08A}"/>
+    <hyperlink ref="C24" r:id="rId30" location="content4-e" xr:uid="{68DAC647-2FF5-7D40-9B3F-A7CFDE9F9724}"/>
+    <hyperlink ref="C26" r:id="rId31" xr:uid="{39872464-0223-E74D-B0EB-E1DD076A4CD2}"/>
+    <hyperlink ref="C28" r:id="rId32" xr:uid="{B0DEBDAF-2E75-E74D-8BE7-D41D17A6F850}"/>
+    <hyperlink ref="C27" r:id="rId33" xr:uid="{BBC8B767-1512-6649-8B7F-9F2D824F0F9D}"/>
+    <hyperlink ref="C29" r:id="rId34" location="projects" xr:uid="{FFF4F158-9F83-CE48-9808-B7D6B356CC4F}"/>
+    <hyperlink ref="F29" r:id="rId35" xr:uid="{BFC1CA03-B547-7042-BAFD-B8F6E90D8427}"/>
+    <hyperlink ref="C31" r:id="rId36" xr:uid="{EC3E5B97-7A3C-5A49-931B-B173E87B0151}"/>
+    <hyperlink ref="F31" r:id="rId37" xr:uid="{A610CFA6-EE72-D14E-80CD-4848929AE14C}"/>
+    <hyperlink ref="C30" r:id="rId38" xr:uid="{78B13E7E-1127-A547-8244-FA6E5002698A}"/>
+    <hyperlink ref="C38" r:id="rId39" xr:uid="{7E848999-856A-A849-B657-521AADD30D66}"/>
+    <hyperlink ref="F38" r:id="rId40" xr:uid="{4C566A0A-64A5-BA44-A80B-CCB366CCF7AD}"/>
+    <hyperlink ref="C41" r:id="rId41" xr:uid="{3DD32363-C20D-0F48-A8AB-04A87B8806EB}"/>
+    <hyperlink ref="C42" r:id="rId42" xr:uid="{79D9D827-AAB5-2D4B-99E3-474BC0B9AA4E}"/>
+    <hyperlink ref="F42" r:id="rId43" display="No" xr:uid="{12ACB131-F843-B04E-B2C8-B048573A0F61}"/>
+    <hyperlink ref="F41" r:id="rId44" xr:uid="{9BAD156A-7083-9041-ABF4-2FF0E51F57B4}"/>
+    <hyperlink ref="C43" r:id="rId45" xr:uid="{121EFBFF-EE3D-C34F-8C33-A880AD30A609}"/>
+    <hyperlink ref="F43" r:id="rId46" display="Form" xr:uid="{39D7A72A-DF53-1742-94F2-6C1949649485}"/>
+    <hyperlink ref="C45" r:id="rId47" xr:uid="{58A1494B-6445-E54C-B70A-94BCC8E76B48}"/>
+    <hyperlink ref="F45" r:id="rId48" xr:uid="{F2B34C73-0BB9-804C-82A8-83FD1428FCF4}"/>
+    <hyperlink ref="C44" r:id="rId49" xr:uid="{B5BEFC2B-5EBE-AF43-A956-2C83591CC3A1}"/>
+    <hyperlink ref="F44" r:id="rId50" xr:uid="{C7BA0F10-763D-C044-AC03-318F8F3912C1}"/>
+    <hyperlink ref="C50" r:id="rId51" location="_ri" xr:uid="{398354CA-7B5B-9149-A6A1-EA339C4F9153}"/>
+    <hyperlink ref="C51" r:id="rId52" xr:uid="{D4E488D7-008C-7041-89A3-A142D3179430}"/>
+    <hyperlink ref="C52" r:id="rId53" xr:uid="{7525C0C7-0476-1844-80BD-C64A1FD08428}"/>
+    <hyperlink ref="C53" r:id="rId54" location="Publications-Section" xr:uid="{D2E4E0C6-3578-7842-9B7B-3D4E15B431D2}"/>
+    <hyperlink ref="C54" r:id="rId55" xr:uid="{9493C1D5-873A-914C-B90E-FEEDC858E63A}"/>
+    <hyperlink ref="C57" r:id="rId56" xr:uid="{903CD93B-52AB-4244-9247-F63FFBC2B66E}"/>
+    <hyperlink ref="C58" r:id="rId57" xr:uid="{E11FE763-70DE-C843-98C2-D0666AEC11CB}"/>
+    <hyperlink ref="F58" r:id="rId58" xr:uid="{578842D3-A5E6-9A4D-A12F-433FEB4AA4A9}"/>
+    <hyperlink ref="F59" r:id="rId59" display="No..?" xr:uid="{6857B64A-8193-8C49-B5DE-EF672F9FE0C8}"/>
+    <hyperlink ref="C59" r:id="rId60" location="teaching-section" xr:uid="{3FEB6C00-AB64-8848-A2BB-19CE73970FA2}"/>
+    <hyperlink ref="C60" r:id="rId61" xr:uid="{6888BF5B-E86F-B943-B6F3-8320FAFA1445}"/>
+    <hyperlink ref="C61" r:id="rId62" xr:uid="{4950B2C5-F17D-624A-AE62-9834277190C0}"/>
+    <hyperlink ref="C62" r:id="rId63" xr:uid="{EB00FB88-140C-FF4E-97F0-7A534D9127FD}"/>
+    <hyperlink ref="F62" r:id="rId64" xr:uid="{C81212D7-0A6B-AC4F-A3BB-87C0DF2B141B}"/>
+    <hyperlink ref="C63" r:id="rId65" xr:uid="{28FD696E-AA3D-5340-9AEE-9B33DAA9100D}"/>
+    <hyperlink ref="F63" r:id="rId66" xr:uid="{301665C9-748B-B74C-8E22-3C2BE315B9A0}"/>
+    <hyperlink ref="C64" r:id="rId67" xr:uid="{9BEA1D4E-E0E9-7F4D-95FF-AA1E5A0A38A7}"/>
+    <hyperlink ref="C65" r:id="rId68" xr:uid="{C54146DC-1962-304A-9ADE-27C93D064A33}"/>
+    <hyperlink ref="F65" r:id="rId69" xr:uid="{BB877229-AE13-9D41-B111-355DE3218E1F}"/>
+    <hyperlink ref="C66" r:id="rId70" xr:uid="{CAE1FF08-3B4A-AF4B-A8FA-73AF2979DDFB}"/>
+    <hyperlink ref="C72" r:id="rId71" xr:uid="{FD5EA699-A473-E14B-A007-8B39747A7B97}"/>
+    <hyperlink ref="F72" r:id="rId72" xr:uid="{2F58E973-C7F1-6F4F-992D-3FE73FC1921B}"/>
+    <hyperlink ref="C74" r:id="rId73" xr:uid="{908C7485-2276-F845-B011-956C90745E36}"/>
+    <hyperlink ref="C75" r:id="rId74" xr:uid="{56CA5437-DF65-7741-BCB4-0097BF46AF5A}"/>
+    <hyperlink ref="C78" r:id="rId75" xr:uid="{E3A4C8BD-C578-CD47-ACE1-48F233318094}"/>
+    <hyperlink ref="C79" r:id="rId76" xr:uid="{BB02585E-E4AF-7B40-A5E2-FA20343B6B7D}"/>
+    <hyperlink ref="F79" r:id="rId77" xr:uid="{11068305-3E64-9847-B25B-E7B4232FDC83}"/>
+    <hyperlink ref="F74" r:id="rId78" xr:uid="{E1F068DF-7982-B140-891F-18371252BEE9}"/>
+    <hyperlink ref="F78" r:id="rId79" xr:uid="{4857BCFA-63F9-D343-996F-B0086015D867}"/>
+    <hyperlink ref="C80" r:id="rId80" xr:uid="{8478D9E5-A9E7-1F41-9E1F-E87F15560F85}"/>
+    <hyperlink ref="F80" r:id="rId81" xr:uid="{F208C5E3-A0C4-1D4B-91C0-2BDC60993E9E}"/>
+    <hyperlink ref="C81" r:id="rId82" xr:uid="{45834B70-B9CF-874E-BDDD-07DC65A97A82}"/>
+    <hyperlink ref="C82" r:id="rId83" xr:uid="{5999988D-62DD-7740-8281-D4A8476498DF}"/>
+    <hyperlink ref="C83" r:id="rId84" xr:uid="{D4D3BD11-6490-B646-B302-20BFB3D7DF5F}"/>
+    <hyperlink ref="C84" r:id="rId85" xr:uid="{923B455F-766D-1245-B440-3E155C36EB08}"/>
+    <hyperlink ref="F84" r:id="rId86" xr:uid="{13585F3B-4D88-FD44-80C6-27534407E6B3}"/>
+    <hyperlink ref="C85" r:id="rId87" location="conference-publications" xr:uid="{1A804911-E79D-9141-A167-60595CEE1F71}"/>
+    <hyperlink ref="C86" r:id="rId88" xr:uid="{3D2271F2-C077-F646-9F3C-5EB7256C0CF2}"/>
+    <hyperlink ref="C87" r:id="rId89" xr:uid="{51A16F76-2C2A-6C41-8E1D-A56F68000383}"/>
+    <hyperlink ref="C88" r:id="rId90" xr:uid="{B3FE6472-8368-3248-AA97-CD0B8A02AD56}"/>
+    <hyperlink ref="F88" r:id="rId91" xr:uid="{CFB38AB7-6FFD-7543-9665-38F4AF916308}"/>
+    <hyperlink ref="C89" r:id="rId92" xr:uid="{6E550245-9521-014D-B426-EDEBB6147E4A}"/>
+    <hyperlink ref="C90" r:id="rId93" xr:uid="{E81A1570-9990-814E-A1D5-C6962C1806DF}"/>
+    <hyperlink ref="C91" r:id="rId94" xr:uid="{D7C55900-5024-034A-80F6-B1670134D8A0}"/>
+    <hyperlink ref="C92" r:id="rId95" xr:uid="{7A00C4FC-9BB4-A242-A1B2-00F729E0EA3E}"/>
+    <hyperlink ref="F92" r:id="rId96" display="Little picky" xr:uid="{59CA0194-3E75-0C43-B43E-0C657B6C82D9}"/>
+    <hyperlink ref="F93" r:id="rId97" display="Yes..?" xr:uid="{CB8A4941-FC1A-754C-A7FD-599935DB3F31}"/>
+    <hyperlink ref="C93" r:id="rId98" location="publications" xr:uid="{8EFA9C06-FE89-7447-91CE-180A9ED16794}"/>
+    <hyperlink ref="C96" r:id="rId99" xr:uid="{1855347E-1501-8D43-99C6-EDC1CFB4E3C1}"/>
+    <hyperlink ref="C97" r:id="rId100" xr:uid="{E744FF8F-6454-894D-BD61-E9C957C07630}"/>
+    <hyperlink ref="C98" r:id="rId101" xr:uid="{7BFC847F-6034-004A-AE72-78A60552C37F}"/>
+    <hyperlink ref="C68" r:id="rId102" xr:uid="{3CAB4899-21CA-0746-9AC4-6377AFF983C9}"/>
+    <hyperlink ref="F68" r:id="rId103" xr:uid="{03AA3462-3833-5642-8AD2-02DEA2EB7DBF}"/>
+    <hyperlink ref="C69" r:id="rId104" xr:uid="{0AFF4185-421E-A044-8B14-063F232DF23C}"/>
+    <hyperlink ref="C70" r:id="rId105" xr:uid="{29B84BC6-13E1-D044-A869-EB5134497CD6}"/>
+    <hyperlink ref="C67" r:id="rId106" xr:uid="{B013B9EF-FD6B-4A41-9F39-38433F1DCC01}"/>
+    <hyperlink ref="C71" r:id="rId107" location="publications" xr:uid="{5E9B8B5B-7402-A34B-99E6-3C227D4F15CC}"/>
+    <hyperlink ref="C100" r:id="rId108" xr:uid="{C0F1ADC4-2A51-C345-9349-4003E44424D3}"/>
+    <hyperlink ref="C101" r:id="rId109" xr:uid="{1DE714D0-AA68-304E-8CCC-E3DEACD98304}"/>
+    <hyperlink ref="C102" r:id="rId110" display="https://adaptive-robotics-lab.github.io/publications/" xr:uid="{E2444A72-A995-5841-989A-59F8AF15478C}"/>
+    <hyperlink ref="C103" r:id="rId111" xr:uid="{3FD7C805-92F3-A749-8523-B5D649B8F890}"/>
+    <hyperlink ref="C73" r:id="rId112" xr:uid="{40710B08-AA99-674E-A8D0-57AD1EC6F7F0}"/>
+    <hyperlink ref="F73" r:id="rId113" xr:uid="{7723E8AA-A3DD-F942-9BD3-714A761F568E}"/>
+    <hyperlink ref="C76" r:id="rId114" xr:uid="{90C16231-A7FD-A64F-9A5A-23E4BF55CB78}"/>
+    <hyperlink ref="C77" r:id="rId115" xr:uid="{7D14C868-8C11-F341-893C-8FA380BE026F}"/>
+    <hyperlink ref="C39" r:id="rId116" xr:uid="{69317078-8695-5A49-99D1-8B4E2BC4589E}"/>
+    <hyperlink ref="F91" r:id="rId117" display="After Submission" xr:uid="{C41937AD-C8AA-6949-BD93-5A3AAC89257A}"/>
+    <hyperlink ref="C46" r:id="rId118" xr:uid="{949E7CA5-065E-0649-9348-614FE6505218}"/>
+    <hyperlink ref="F46" r:id="rId119" display="After Admission" xr:uid="{994371A4-342D-F348-B88E-265C6A27BF72}"/>
+    <hyperlink ref="C48" r:id="rId120" xr:uid="{05889E0F-3F97-D04C-9B20-AAD392054221}"/>
+    <hyperlink ref="C47" r:id="rId121" xr:uid="{33DBF5E1-B81D-2142-83D8-9C7A127864C4}"/>
+    <hyperlink ref="C37" r:id="rId122" xr:uid="{70A5B074-FE39-E04D-AFDE-543B180584E3}"/>
+    <hyperlink ref="F37" r:id="rId123" display="No" xr:uid="{7DF036FC-9EA0-5E45-8FE0-AF7D834D24A5}"/>
+    <hyperlink ref="C36" r:id="rId124" xr:uid="{CFCA4AD5-6D8E-CB44-A671-333BE022437B}"/>
+    <hyperlink ref="C35" r:id="rId125" xr:uid="{B4346412-B077-4844-ABEA-8398BD09DDA1}"/>
+    <hyperlink ref="F33" r:id="rId126" xr:uid="{219FC3BD-1ECB-BC44-9FA1-411B97509B53}"/>
+    <hyperlink ref="C34" r:id="rId127" display="https://r-pad.github.io/publications/" xr:uid="{4DA529A4-12B5-7D4F-B712-E4D97CFDAEDB}"/>
+    <hyperlink ref="C33" r:id="rId128" xr:uid="{B5109ACE-0258-1F44-836F-DF406D7A1D75}"/>
+    <hyperlink ref="C32" r:id="rId129" xr:uid="{0A1707DB-8872-0648-B9E4-B8A0B8B1F90C}"/>
+    <hyperlink ref="C104" r:id="rId130" xr:uid="{5FFFB542-20CD-D44B-89B3-96A8A16DBC55}"/>
+    <hyperlink ref="C105" r:id="rId131" xr:uid="{CFA370B5-79A6-4A41-AF90-E9894E531D42}"/>
+    <hyperlink ref="C106" r:id="rId132" xr:uid="{ABC72816-BD2A-0B41-852C-A1EBC5A6508E}"/>
+    <hyperlink ref="F106" r:id="rId133" xr:uid="{EA5CBE3C-DFC3-374F-865A-D0252E2A2DCB}"/>
+    <hyperlink ref="C107" r:id="rId134" xr:uid="{735F21D3-12C3-8246-B974-D051B982625C}"/>
+    <hyperlink ref="C108" r:id="rId135" xr:uid="{4A5FEC95-F3F6-334E-9E89-0B03889995EB}"/>
+    <hyperlink ref="C109" r:id="rId136" xr:uid="{2EE01EE5-3A04-534B-BFE5-EAB18816D082}"/>
+    <hyperlink ref="F2" r:id="rId137" display="Not mentioned" xr:uid="{945FBC30-5CEB-424C-9D78-0B7E11F08E89}"/>
+    <hyperlink ref="F7" r:id="rId138" xr:uid="{8E501F13-5237-BB49-A5AD-C5F6AD88218F}"/>
+    <hyperlink ref="F6" r:id="rId139" location="contact" xr:uid="{3F0E09B4-19AF-3A48-85EA-7A7DC6686FB4}"/>
+    <hyperlink ref="C49" r:id="rId140" xr:uid="{E99926AE-00F4-AD41-9D8A-24CAB858B2FE}"/>
+    <hyperlink ref="F8" r:id="rId141" xr:uid="{AB30AB90-2D8C-FA4A-8E71-DA50CA4E22A7}"/>
+    <hyperlink ref="F13" r:id="rId142" xr:uid="{C1CFADFE-12B7-994A-B16E-3F6AD565E21B}"/>
+    <hyperlink ref="C22" r:id="rId143" xr:uid="{BE76FDC1-465C-4F4B-A40C-F4F0BA7AACC2}"/>
+    <hyperlink ref="C25" r:id="rId144" xr:uid="{6124BD60-DE89-E04A-B3F5-390F2315CBAA}"/>
+    <hyperlink ref="F25" r:id="rId145" location="join" xr:uid="{A750D1F5-A848-F743-8E23-3832B5596DCE}"/>
+    <hyperlink ref="F26" r:id="rId146" xr:uid="{26D2091C-C6A1-1E4F-A0F0-D71C15084E5A}"/>
+    <hyperlink ref="F32" r:id="rId147" xr:uid="{E99E2298-7017-A047-B3BD-4472343CDD0B}"/>
+    <hyperlink ref="F35" r:id="rId148" xr:uid="{54121DDB-5B4A-024C-9715-F3B5F3D34B7D}"/>
+    <hyperlink ref="F34" r:id="rId149" xr:uid="{B1E5435C-6261-F94A-AB9E-18E85110B5F9}"/>
+    <hyperlink ref="F36" r:id="rId150" xr:uid="{51B6C597-6715-A547-A972-7D01EB1DFD3A}"/>
+    <hyperlink ref="F39" r:id="rId151" xr:uid="{F951ECEC-1BEF-D543-A034-9B5EB7CACF17}"/>
+    <hyperlink ref="F47" r:id="rId152" xr:uid="{C958B7E0-4842-F241-A83E-6A2D49C1F1BF}"/>
+    <hyperlink ref="F48" r:id="rId153" xr:uid="{E17F42DF-7DFF-224E-94B1-67029A85337E}"/>
+    <hyperlink ref="F49" r:id="rId154" xr:uid="{5011C913-565B-C94C-8151-F93A1234C732}"/>
+    <hyperlink ref="F50" r:id="rId155" xr:uid="{9560BA90-E86C-5F4C-B19C-112CCBE2DE66}"/>
+    <hyperlink ref="F51" r:id="rId156" display="Yes" xr:uid="{27135B7B-7AD5-D345-AFCC-E2140680F4C3}"/>
+    <hyperlink ref="F53" r:id="rId157" xr:uid="{B45135B3-2794-FB4A-AB7C-BD309B78A26A}"/>
+    <hyperlink ref="C56" r:id="rId158" display="https://scholar.google.com/citations?hl=en&amp;user=g9bV-_sAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{4F6AE197-5746-404B-8769-4EE7E276C903}"/>
+    <hyperlink ref="C55" r:id="rId159" xr:uid="{1F444EB0-204F-7C49-A6CC-703D102B53BF}"/>
+    <hyperlink ref="F55" r:id="rId160" xr:uid="{64D5B3CB-331B-3448-B9BD-7128151E70CD}"/>
+    <hyperlink ref="F56" r:id="rId161" xr:uid="{BE30AA51-3EBF-954D-8B74-233C8AE3B7CB}"/>
+    <hyperlink ref="A40" r:id="rId162" display="Saurabh Gupta" xr:uid="{97643B95-EFA8-1140-AB11-805B406DB3DD}"/>
+    <hyperlink ref="C40" r:id="rId163" xr:uid="{D5A6EDD9-7B0A-DF48-BAAF-F75C4255559D}"/>
+    <hyperlink ref="F40" r:id="rId164" xr:uid="{2E2B510D-51C4-F141-AA3F-5E508EA52EBE}"/>
+    <hyperlink ref="F67" r:id="rId165" xr:uid="{F4275B35-6C02-384F-B465-2B40F9902EA5}"/>
+    <hyperlink ref="F69" r:id="rId166" xr:uid="{2F527CCC-CE9E-C543-BCF3-9B1B1B430985}"/>
+    <hyperlink ref="F70" r:id="rId167" xr:uid="{1FDD1B1F-2127-424B-88C6-DF5433C40969}"/>
+    <hyperlink ref="F71" r:id="rId168" location="contact" xr:uid="{994856F7-7861-B348-B765-4A7A4EB58B2D}"/>
+    <hyperlink ref="F76" r:id="rId169" xr:uid="{129EBEC2-9896-CA4A-AA98-A1AABC252688}"/>
+    <hyperlink ref="F77" r:id="rId170" xr:uid="{7099098B-9801-324A-9F12-C1DDE138B9EF}"/>
+    <hyperlink ref="F81" r:id="rId171" xr:uid="{9CD28BF9-1DFB-6C49-9CDF-BC08937EE939}"/>
+    <hyperlink ref="F82" r:id="rId172" xr:uid="{CC4F20FD-36B4-FA4B-8A4A-6A5B989C6573}"/>
+    <hyperlink ref="F83" r:id="rId173" xr:uid="{B18B63C2-1FD2-564D-91AD-DF48E52B84B4}"/>
+    <hyperlink ref="F85" r:id="rId174" xr:uid="{B95E39AC-29F4-C749-A281-DAE1BA48DAB7}"/>
+    <hyperlink ref="F87" r:id="rId175" xr:uid="{18AEE6CC-8D1E-2E46-B870-68ED2D0832B5}"/>
+    <hyperlink ref="F89" r:id="rId176" xr:uid="{0FF872C9-2AD5-074E-93E4-55865CE4A81A}"/>
+    <hyperlink ref="F90" r:id="rId177" xr:uid="{4EC9CF74-9C72-B045-893B-C3456A860A92}"/>
+    <hyperlink ref="F96" r:id="rId178" location="contact" xr:uid="{C8215F07-1913-394E-A17D-CEA30B1C30C2}"/>
+    <hyperlink ref="F97" r:id="rId179" xr:uid="{5FF07C5B-E6B2-D745-B6A1-001FCB6CF8AB}"/>
+    <hyperlink ref="F98" r:id="rId180" xr:uid="{C267F854-4600-C949-BB34-3C61ADA7D51A}"/>
+    <hyperlink ref="F100" r:id="rId181" xr:uid="{FC2865FB-7FF7-6D49-9A82-9D1E512981D9}"/>
+    <hyperlink ref="F101" r:id="rId182" xr:uid="{2B3F3304-CE72-E048-AEA1-908D2AC74C41}"/>
+    <hyperlink ref="F102" r:id="rId183" xr:uid="{12826E40-D942-D644-984A-09E0983C2BF1}"/>
+    <hyperlink ref="F103" r:id="rId184" xr:uid="{0F348FD7-AD57-8243-8D22-13815A1AEE73}"/>
+    <hyperlink ref="F104" r:id="rId185" xr:uid="{769BF1AD-B98A-844E-9E8F-6E2F030E8FFD}"/>
+    <hyperlink ref="F105" r:id="rId186" xr:uid="{89472F04-5E91-D540-95CC-42F3C6631B21}"/>
+    <hyperlink ref="F107" r:id="rId187" xr:uid="{E84DFB70-6A83-FB48-BE73-EF22E66C660B}"/>
+    <hyperlink ref="F108" r:id="rId188" xr:uid="{E38E8E60-9D8D-4344-A9B8-EF8E11166022}"/>
+    <hyperlink ref="F109" r:id="rId189" location="contact" xr:uid="{2A7486D0-C44F-EA47-9CF0-583B629E3B6A}"/>
+    <hyperlink ref="C14" r:id="rId190" xr:uid="{D884EE9B-5EB4-A640-A5D1-664B23E3D668}"/>
+    <hyperlink ref="F14" r:id="rId191" xr:uid="{A8BDAE9A-3D13-B447-B08B-9F1E06C4F226}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4108,7 +4663,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C782443-ED1C-0A4A-9325-4BCE67F3BA7F}">
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
@@ -4117,21 +4672,21 @@
     <col min="4" max="4" width="16.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="44.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.5" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="40.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="30.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="10.83203125" style="1"/>
+    <col min="14" max="15" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
@@ -4139,91 +4694,94 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D1" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="D2" s="25">
+        <v>45992</v>
+      </c>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="J1" s="10" t="s">
+      <c r="H2" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="I2" s="42">
+        <v>4704</v>
+      </c>
+      <c r="J2" s="44">
+        <v>125</v>
+      </c>
+      <c r="K2" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>339</v>
-      </c>
-      <c r="D2" s="30">
-        <v>45992</v>
-      </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="I2" s="22">
-        <v>4704</v>
-      </c>
-      <c r="J2" s="31">
-        <v>125</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="L2" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="M2" s="13" t="s">
+      <c r="L2" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="N2" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>5</v>
       </c>
@@ -4231,20 +4789,20 @@
         <v>10</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D3" s="33">
         <v>45993</v>
       </c>
       <c r="E3" s="19"/>
       <c r="F3" s="19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I3" s="19">
         <v>4704</v>
@@ -4253,49 +4811,49 @@
         <v>125</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L3" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>16</v>
+        <v>225</v>
       </c>
       <c r="N3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="13" t="s">
-        <v>24</v>
-      </c>
       <c r="P3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D4" s="33">
         <v>45994</v>
       </c>
       <c r="E4" s="19"/>
       <c r="F4" s="19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I4" s="19">
         <v>4833</v>
@@ -4304,234 +4862,261 @@
         <v>155</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L4" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="18" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="33">
+        <v>45992</v>
+      </c>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I5" s="19">
+        <v>4833</v>
+      </c>
+      <c r="J5" s="34">
+        <v>155</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="N5" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="D5" s="25">
-        <v>45992</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="I5" s="1">
-        <v>4833</v>
-      </c>
-      <c r="J5" s="11">
-        <v>155</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="O5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D6" s="33">
         <v>46006</v>
       </c>
       <c r="E6" s="19"/>
       <c r="F6" s="20" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J6" s="34">
         <v>105</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="D7" s="25">
         <v>46006</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="J7" s="11">
         <v>105</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D8" s="33">
         <v>46006</v>
       </c>
       <c r="E8" s="19"/>
       <c r="F8" s="19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G8" s="19"/>
       <c r="H8" s="20" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J8" s="34">
         <v>75</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L8" s="35" t="s">
-        <v>380</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>412</v>
+        <v>373</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+      <c r="Q8" s="23" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D9" s="25">
         <v>46001</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="J9" s="11">
         <v>80</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>381</v>
-      </c>
-      <c r="M9" s="13"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q9" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D10" s="25">
         <v>46006</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="I10" s="1">
         <v>1836</v>
@@ -4540,53 +5125,53 @@
         <v>90</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D11" s="25">
         <v>46006</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J11" s="11">
         <v>90</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="M11" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="41" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="41" t="s">
-        <v>87</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>6</v>
@@ -4603,36 +5188,36 @@
       <c r="J12" s="44"/>
       <c r="K12" s="42"/>
       <c r="L12" s="26" t="s">
-        <v>382</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+        <v>375</v>
+      </c>
+      <c r="N12" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D13" s="33">
         <v>46006</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="I13" s="19">
         <v>6882</v>
@@ -4641,84 +5226,84 @@
         <v>90</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L13" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>88</v>
+        <v>248</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D14" s="33">
         <v>46006</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="I14" s="19"/>
       <c r="J14" s="34">
         <v>90</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="L14" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="M14" s="38" t="s">
-        <v>390</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+      <c r="N14" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D15" s="25">
         <v>46008</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I15" s="1">
         <v>4836</v>
@@ -4727,34 +5312,37 @@
         <v>155</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="L15" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="O15" s="20" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D16" s="25">
         <v>45994</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G16" s="27"/>
       <c r="H16" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I16" s="1">
         <v>4836</v>
@@ -4763,78 +5351,84 @@
         <v>155</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D17" s="33">
         <v>45992</v>
       </c>
       <c r="E17" s="19"/>
       <c r="F17" s="19" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="I17" s="19" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="J17" s="34">
         <v>90</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="L17" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O17" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D18" s="25">
         <v>46006</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="I18" s="1">
         <v>1839</v>
@@ -4843,113 +5437,113 @@
         <v>90</v>
       </c>
       <c r="L18" s="26" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D19" s="33">
         <v>46006</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="19" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J19" s="34">
         <v>105</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="L19" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="M19" s="13" t="s">
-        <v>118</v>
+        <v>289</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D20" s="25">
         <v>46006</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G20" s="27" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="J20" s="11">
         <v>155</v>
       </c>
       <c r="L20" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="21" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D21" s="30">
         <v>46006</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I21" s="22">
         <v>2888</v>
@@ -4958,42 +5552,42 @@
         <v>90</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="L21" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="M21" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="D22" s="25">
         <v>46006</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I22" s="1">
         <v>2888</v>
@@ -5002,40 +5596,40 @@
         <v>90</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="N22" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
-        <v>139</v>
       </c>
       <c r="B23" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D23" s="33">
         <v>46006</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="20" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I23" s="19">
         <v>2111</v>
@@ -5045,39 +5639,39 @@
       </c>
       <c r="K23" s="19"/>
       <c r="L23" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>142</v>
+        <v>303</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D24" s="25">
         <v>46002</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I24" s="1">
         <v>5156</v>
@@ -5086,39 +5680,39 @@
         <v>105</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L24" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B25" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D25" s="33">
         <v>46006</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I25" s="19">
         <v>4852</v>
@@ -5128,42 +5722,45 @@
       </c>
       <c r="K25" s="19"/>
       <c r="L25" s="35" t="s">
-        <v>324</v>
-      </c>
-      <c r="M25" s="13" t="s">
-        <v>156</v>
+        <v>317</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+      <c r="P25" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q25" s="17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D26" s="9">
         <v>46006</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I26" s="1">
         <v>4852</v>
@@ -5172,33 +5769,33 @@
         <v>105</v>
       </c>
       <c r="L26" s="26" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D27" s="9">
         <v>46006</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I27" s="1">
         <v>4852</v>
@@ -5207,34 +5804,34 @@
         <v>105</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D28" s="9">
         <v>46006</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G28" s="27"/>
       <c r="H28" s="6" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="I28" s="1">
         <v>3987</v>
@@ -5243,74 +5840,74 @@
         <v>105</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="18" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B29" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D29" s="33">
         <v>46006</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="J29" s="34">
         <v>75</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="L29" s="35" t="s">
-        <v>371</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>183</v>
+        <v>364</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="18" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B30" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D30" s="33">
         <v>46003</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G30" s="37"/>
       <c r="H30" s="20" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I30" s="19">
         <v>2596</v>
@@ -5320,39 +5917,39 @@
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>195</v>
+        <v>303</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>186</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D31" s="29">
         <v>45992</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="I31" s="1">
         <v>5859</v>
@@ -5361,183 +5958,183 @@
         <v>75</v>
       </c>
       <c r="L31" s="26" t="s">
-        <v>372</v>
-      </c>
-      <c r="M31" s="17" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+        <v>365</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D32" s="33">
         <v>46022</v>
       </c>
       <c r="E32" s="19"/>
       <c r="F32" s="19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G32" s="37"/>
       <c r="H32" s="20" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="J32" s="34">
         <v>115</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="M32" s="17" t="s">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+      <c r="O32" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D33" s="25">
         <v>46022</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="J33" s="11">
         <v>115</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="M33" s="17" t="s">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="N33" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="O33" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>349</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>356</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>308</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>211</v>
-      </c>
       <c r="G34" s="37" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="J34" s="34">
         <v>80</v>
       </c>
       <c r="K34" s="19"/>
       <c r="L34" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="M34" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+        <v>366</v>
+      </c>
+      <c r="N34" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D35" s="24"/>
       <c r="G35" s="7"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D36" s="24"/>
       <c r="E36" s="5"/>
       <c r="G36" s="7"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D37" s="24"/>
       <c r="E37" s="5"/>
       <c r="G37" s="7"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D38" s="24"/>
       <c r="G38" s="7"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D39" s="24"/>
       <c r="G39" s="7"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D40" s="24"/>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D41" s="24"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D42" s="24"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D43" s="24"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D44" s="24"/>
       <c r="G44" s="7"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D45" s="24"/>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D46" s="24"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D47" s="24"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D48" s="24"/>
       <c r="G48" s="7"/>
     </row>
@@ -5720,66 +6317,78 @@
     <hyperlink ref="L29" r:id="rId86" xr:uid="{249C5B54-9E95-5148-8652-C9B76C283C0A}"/>
     <hyperlink ref="L31" r:id="rId87" xr:uid="{FA0C8E55-5F55-6145-ABEB-C1BF32579FF5}"/>
     <hyperlink ref="B12" r:id="rId88" xr:uid="{E1371F36-0744-2846-ABD7-A0381F27D62B}"/>
-    <hyperlink ref="M2" r:id="rId89" xr:uid="{0735B2F4-2A7F-334D-B8E8-E3D195E3F9CA}"/>
-    <hyperlink ref="M4" r:id="rId90" xr:uid="{93854774-C734-C642-983D-E55B84C517D0}"/>
+    <hyperlink ref="N2" r:id="rId89" xr:uid="{0735B2F4-2A7F-334D-B8E8-E3D195E3F9CA}"/>
+    <hyperlink ref="P4" r:id="rId90" xr:uid="{93854774-C734-C642-983D-E55B84C517D0}"/>
     <hyperlink ref="N4" r:id="rId91" xr:uid="{EFBFB96D-DB30-3742-881E-C1B51375FB51}"/>
     <hyperlink ref="O4" r:id="rId92" xr:uid="{CB22CC03-9EB2-6748-937B-E18B9EEA7670}"/>
-    <hyperlink ref="M6" r:id="rId93" xr:uid="{A0F647DD-B7E9-1D4D-B39B-C4087AC42BC8}"/>
-    <hyperlink ref="N6" r:id="rId94" xr:uid="{309366AC-2F72-7347-A5D4-B83D2D6AB7C4}"/>
-    <hyperlink ref="O6" r:id="rId95" xr:uid="{CFD1AA27-7267-F140-89F2-E3D4866ECA29}"/>
-    <hyperlink ref="M8" r:id="rId96" location="projects" xr:uid="{8A280929-5088-BD40-B8C3-30C481549BC7}"/>
-    <hyperlink ref="M12" r:id="rId97" xr:uid="{F06E6F43-FB89-1143-B583-A1B99CDBB9C9}"/>
-    <hyperlink ref="M15" r:id="rId98" location="_ri" xr:uid="{470A04D1-F39A-8045-9BF4-FB6BEE1E4182}"/>
-    <hyperlink ref="M17" r:id="rId99" location="Publications-Section" xr:uid="{C096BCE1-6736-8243-A8AC-B4EF826AB7F2}"/>
-    <hyperlink ref="N17" r:id="rId100" xr:uid="{D63E388B-4F12-2B47-82ED-6E508F4A7AD6}"/>
-    <hyperlink ref="M19" r:id="rId101" location="teaching-section" xr:uid="{9CE952F3-9A99-D448-B323-58EB6E5930C2}"/>
-    <hyperlink ref="N19" r:id="rId102" xr:uid="{60AAD254-B63C-8340-B8EF-5E67B5072DDE}"/>
-    <hyperlink ref="M22" r:id="rId103" xr:uid="{63E11AA5-FD7A-114E-A65C-50843B35D7B8}"/>
-    <hyperlink ref="M20" r:id="rId104" xr:uid="{73BCD99F-1586-B140-A4C0-2225D2697D80}"/>
-    <hyperlink ref="M21" r:id="rId105" xr:uid="{74EAEAFC-6931-1346-99C0-5F035BD19ED7}"/>
-    <hyperlink ref="N21" r:id="rId106" xr:uid="{8CF9CEEE-FFC5-0241-B76E-D83EAAC6109E}"/>
-    <hyperlink ref="N22" r:id="rId107" xr:uid="{FDBFC815-BC75-2F4B-BA48-5217E14B054E}"/>
-    <hyperlink ref="M10" r:id="rId108" xr:uid="{DE39C38D-8716-8D41-8538-8ED8BC5489FB}"/>
-    <hyperlink ref="M11" r:id="rId109" xr:uid="{154D8A40-DCB5-6447-A80A-1B492B438297}"/>
-    <hyperlink ref="M23" r:id="rId110" xr:uid="{099399F5-DC71-F04B-8A91-1EFAD0B2685D}"/>
-    <hyperlink ref="N23" r:id="rId111" xr:uid="{5DF00BB1-5736-8B46-BA92-06483DC52C3E}"/>
-    <hyperlink ref="L34" r:id="rId112" xr:uid="{0F0CC69A-9B70-9F45-B107-357ABD04D490}"/>
-    <hyperlink ref="M34" r:id="rId113" xr:uid="{9FBBCBDA-F082-0F4D-906E-FFA61DC4DFA1}"/>
-    <hyperlink ref="N34" r:id="rId114" xr:uid="{504DEB57-DA3D-9545-8C53-E9DC192B63E8}"/>
-    <hyperlink ref="M25" r:id="rId115" xr:uid="{F392E7AF-26BC-704B-96EA-D34CD222CBBF}"/>
-    <hyperlink ref="N25" r:id="rId116" xr:uid="{B4455B44-E39C-2247-B88A-789D44414486}"/>
-    <hyperlink ref="O25" r:id="rId117" location="conference-publications" xr:uid="{70C43FC9-7198-7E4B-B7FD-B127D7781A45}"/>
-    <hyperlink ref="M27" r:id="rId118" location="conference-publications" xr:uid="{EA8B5258-2516-7349-B886-954C03EF2B48}"/>
-    <hyperlink ref="M30" r:id="rId119" location="publications" xr:uid="{B28363B8-28EF-5B46-A228-9F05DCE2AA7A}"/>
-    <hyperlink ref="M32" r:id="rId120" xr:uid="{37537E5E-5D7F-B941-8CE4-8D63AAED64A3}"/>
-    <hyperlink ref="M33" r:id="rId121" xr:uid="{D3697775-A6A4-1F49-A0EE-FD9739C7F19A}"/>
-    <hyperlink ref="N33" r:id="rId122" xr:uid="{0121D612-1A75-E24E-8FD8-101A035201F6}"/>
-    <hyperlink ref="N32" r:id="rId123" xr:uid="{68174A1C-2BFB-2347-A7E6-240E660ECB04}"/>
-    <hyperlink ref="O32" r:id="rId124" xr:uid="{D1B11672-6692-9D42-A0B8-4687E07F327F}"/>
-    <hyperlink ref="O33" r:id="rId125" xr:uid="{425743AC-5059-3D48-9763-6B105E3CBA4C}"/>
-    <hyperlink ref="M29" r:id="rId126" xr:uid="{F7DC1CA4-1B4A-D045-8790-9AB3A1470D88}"/>
-    <hyperlink ref="N29" r:id="rId127" xr:uid="{9D092DAA-F6B8-FD45-A845-AD8733CFDD94}"/>
-    <hyperlink ref="O29" r:id="rId128" xr:uid="{AAD2DA47-9427-E54B-B0F0-AB5CC613989E}"/>
-    <hyperlink ref="M31" r:id="rId129" xr:uid="{5ECD7BA1-72BB-6047-B334-015C81E6286C}"/>
-    <hyperlink ref="M14" r:id="rId130" display="https://weirdlab.cs.washington.edu/publications.html" xr:uid="{51C1FC28-26A3-A344-AB7E-4E077A231084}"/>
-    <hyperlink ref="N14" r:id="rId131" xr:uid="{21C45C99-CA9A-3442-8729-39868C7D9B0B}"/>
-    <hyperlink ref="O14" r:id="rId132" xr:uid="{10C0CCF9-C154-F64F-9755-492D82CCFA36}"/>
-    <hyperlink ref="B14" r:id="rId133" xr:uid="{FCE0556D-E430-194F-AF60-ACC1A8084480}"/>
-    <hyperlink ref="G14" r:id="rId134" xr:uid="{56C06839-31C5-114D-B277-1EDD7F10FEC9}"/>
-    <hyperlink ref="N10" r:id="rId135" xr:uid="{468E1F59-0542-D649-9D0A-21E69B4CC648}"/>
-    <hyperlink ref="H6" r:id="rId136" xr:uid="{D96D5E25-1412-6F43-8359-3C7402D8B67B}"/>
-    <hyperlink ref="H9" r:id="rId137" xr:uid="{8FBD6F13-0173-4041-80B0-05931023787F}"/>
-    <hyperlink ref="P8" r:id="rId138" xr:uid="{44616CBF-28F2-4641-8705-F96148FD0AB9}"/>
-    <hyperlink ref="O8" r:id="rId139" display="Gunya Shi" xr:uid="{A9CB14E4-7193-5040-B65C-433F775112D8}"/>
-    <hyperlink ref="N8" r:id="rId140" xr:uid="{616B93F6-CC26-894E-B9C6-A1EA13237ACA}"/>
-    <hyperlink ref="M13" r:id="rId141" xr:uid="{1BC51BE8-A6D7-3741-A564-5041E6F9D257}"/>
-    <hyperlink ref="N13" r:id="rId142" xr:uid="{49D4C8B9-2A2C-EF40-ADAE-68D6DD3BB24B}"/>
-    <hyperlink ref="H21" r:id="rId143" xr:uid="{A9250A43-47F1-4A42-A923-CE524DF5C999}"/>
-    <hyperlink ref="M3" r:id="rId144" location="people" xr:uid="{4B51A9C5-8CFC-E443-9F31-E3E3AB7F39DD}"/>
-    <hyperlink ref="N3" r:id="rId145" xr:uid="{43BD84D6-F7F4-134B-B47A-8460C7EEB170}"/>
-    <hyperlink ref="O3" r:id="rId146" xr:uid="{214E9E96-9B00-D043-991D-27A1DB0FCEBC}"/>
-    <hyperlink ref="P3" r:id="rId147" xr:uid="{84DF6AA0-1B2D-4C4B-BB84-45F067BEBA53}"/>
-    <hyperlink ref="Q3" r:id="rId148" xr:uid="{3CD3B42F-B076-034C-BC62-76472DDFCAF1}"/>
+    <hyperlink ref="N6" r:id="rId93" xr:uid="{A0F647DD-B7E9-1D4D-B39B-C4087AC42BC8}"/>
+    <hyperlink ref="O6" r:id="rId94" xr:uid="{309366AC-2F72-7347-A5D4-B83D2D6AB7C4}"/>
+    <hyperlink ref="P6" r:id="rId95" xr:uid="{CFD1AA27-7267-F140-89F2-E3D4866ECA29}"/>
+    <hyperlink ref="N8" r:id="rId96" location="projects" xr:uid="{8A280929-5088-BD40-B8C3-30C481549BC7}"/>
+    <hyperlink ref="N15" r:id="rId97" location="_ri" xr:uid="{470A04D1-F39A-8045-9BF4-FB6BEE1E4182}"/>
+    <hyperlink ref="N17" r:id="rId98" location="Publications-Section" xr:uid="{C096BCE1-6736-8243-A8AC-B4EF826AB7F2}"/>
+    <hyperlink ref="N19" r:id="rId99" location="teaching-section" xr:uid="{9CE952F3-9A99-D448-B323-58EB6E5930C2}"/>
+    <hyperlink ref="O19" r:id="rId100" xr:uid="{60AAD254-B63C-8340-B8EF-5E67B5072DDE}"/>
+    <hyperlink ref="N22" r:id="rId101" xr:uid="{63E11AA5-FD7A-114E-A65C-50843B35D7B8}"/>
+    <hyperlink ref="N20" r:id="rId102" xr:uid="{73BCD99F-1586-B140-A4C0-2225D2697D80}"/>
+    <hyperlink ref="N21" r:id="rId103" xr:uid="{74EAEAFC-6931-1346-99C0-5F035BD19ED7}"/>
+    <hyperlink ref="O21" r:id="rId104" xr:uid="{8CF9CEEE-FFC5-0241-B76E-D83EAAC6109E}"/>
+    <hyperlink ref="O22" r:id="rId105" xr:uid="{FDBFC815-BC75-2F4B-BA48-5217E14B054E}"/>
+    <hyperlink ref="N10" r:id="rId106" xr:uid="{DE39C38D-8716-8D41-8538-8ED8BC5489FB}"/>
+    <hyperlink ref="N11" r:id="rId107" xr:uid="{154D8A40-DCB5-6447-A80A-1B492B438297}"/>
+    <hyperlink ref="N23" r:id="rId108" xr:uid="{099399F5-DC71-F04B-8A91-1EFAD0B2685D}"/>
+    <hyperlink ref="O23" r:id="rId109" xr:uid="{5DF00BB1-5736-8B46-BA92-06483DC52C3E}"/>
+    <hyperlink ref="L34" r:id="rId110" xr:uid="{0F0CC69A-9B70-9F45-B107-357ABD04D490}"/>
+    <hyperlink ref="N34" r:id="rId111" xr:uid="{9FBBCBDA-F082-0F4D-906E-FFA61DC4DFA1}"/>
+    <hyperlink ref="O34" r:id="rId112" xr:uid="{504DEB57-DA3D-9545-8C53-E9DC192B63E8}"/>
+    <hyperlink ref="N25" r:id="rId113" xr:uid="{F392E7AF-26BC-704B-96EA-D34CD222CBBF}"/>
+    <hyperlink ref="O25" r:id="rId114" location="conference-publications" xr:uid="{70C43FC9-7198-7E4B-B7FD-B127D7781A45}"/>
+    <hyperlink ref="N27" r:id="rId115" location="conference-publications" xr:uid="{EA8B5258-2516-7349-B886-954C03EF2B48}"/>
+    <hyperlink ref="N30" r:id="rId116" location="publications" xr:uid="{B28363B8-28EF-5B46-A228-9F05DCE2AA7A}"/>
+    <hyperlink ref="N32" r:id="rId117" xr:uid="{37537E5E-5D7F-B941-8CE4-8D63AAED64A3}"/>
+    <hyperlink ref="N33" r:id="rId118" xr:uid="{D3697775-A6A4-1F49-A0EE-FD9739C7F19A}"/>
+    <hyperlink ref="O33" r:id="rId119" xr:uid="{0121D612-1A75-E24E-8FD8-101A035201F6}"/>
+    <hyperlink ref="O32" r:id="rId120" xr:uid="{68174A1C-2BFB-2347-A7E6-240E660ECB04}"/>
+    <hyperlink ref="P32" r:id="rId121" xr:uid="{D1B11672-6692-9D42-A0B8-4687E07F327F}"/>
+    <hyperlink ref="P33" r:id="rId122" xr:uid="{425743AC-5059-3D48-9763-6B105E3CBA4C}"/>
+    <hyperlink ref="N29" r:id="rId123" xr:uid="{F7DC1CA4-1B4A-D045-8790-9AB3A1470D88}"/>
+    <hyperlink ref="O29" r:id="rId124" xr:uid="{9D092DAA-F6B8-FD45-A845-AD8733CFDD94}"/>
+    <hyperlink ref="P29" r:id="rId125" xr:uid="{AAD2DA47-9427-E54B-B0F0-AB5CC613989E}"/>
+    <hyperlink ref="N31" r:id="rId126" xr:uid="{5ECD7BA1-72BB-6047-B334-015C81E6286C}"/>
+    <hyperlink ref="N14" r:id="rId127" display="https://weirdlab.cs.washington.edu/publications.html" xr:uid="{51C1FC28-26A3-A344-AB7E-4E077A231084}"/>
+    <hyperlink ref="O14" r:id="rId128" xr:uid="{21C45C99-CA9A-3442-8729-39868C7D9B0B}"/>
+    <hyperlink ref="P14" r:id="rId129" xr:uid="{10C0CCF9-C154-F64F-9755-492D82CCFA36}"/>
+    <hyperlink ref="B14" r:id="rId130" xr:uid="{FCE0556D-E430-194F-AF60-ACC1A8084480}"/>
+    <hyperlink ref="G14" r:id="rId131" xr:uid="{56C06839-31C5-114D-B277-1EDD7F10FEC9}"/>
+    <hyperlink ref="O10" r:id="rId132" xr:uid="{468E1F59-0542-D649-9D0A-21E69B4CC648}"/>
+    <hyperlink ref="H6" r:id="rId133" xr:uid="{D96D5E25-1412-6F43-8359-3C7402D8B67B}"/>
+    <hyperlink ref="H9" r:id="rId134" xr:uid="{8FBD6F13-0173-4041-80B0-05931023787F}"/>
+    <hyperlink ref="Q8" r:id="rId135" xr:uid="{44616CBF-28F2-4641-8705-F96148FD0AB9}"/>
+    <hyperlink ref="P8" r:id="rId136" display="Gunya Shi" xr:uid="{A9CB14E4-7193-5040-B65C-433F775112D8}"/>
+    <hyperlink ref="O8" r:id="rId137" xr:uid="{616B93F6-CC26-894E-B9C6-A1EA13237ACA}"/>
+    <hyperlink ref="N13" r:id="rId138" xr:uid="{1BC51BE8-A6D7-3741-A564-5041E6F9D257}"/>
+    <hyperlink ref="O13" r:id="rId139" xr:uid="{49D4C8B9-2A2C-EF40-ADAE-68D6DD3BB24B}"/>
+    <hyperlink ref="H21" r:id="rId140" xr:uid="{A9250A43-47F1-4A42-A923-CE524DF5C999}"/>
+    <hyperlink ref="N3" r:id="rId141" location="people" xr:uid="{4B51A9C5-8CFC-E443-9F31-E3E3AB7F39DD}"/>
+    <hyperlink ref="O3" r:id="rId142" xr:uid="{43BD84D6-F7F4-134B-B47A-8460C7EEB170}"/>
+    <hyperlink ref="P3" r:id="rId143" xr:uid="{214E9E96-9B00-D043-991D-27A1DB0FCEBC}"/>
+    <hyperlink ref="Q3" r:id="rId144" xr:uid="{84DF6AA0-1B2D-4C4B-BB84-45F067BEBA53}"/>
+    <hyperlink ref="R3" r:id="rId145" xr:uid="{3CD3B42F-B076-034C-BC62-76472DDFCAF1}"/>
+    <hyperlink ref="N9" r:id="rId146" display="https://r-pad.github.io/publications/" xr:uid="{32A4D02A-6A22-F346-B03C-B7EE5E28D4B2}"/>
+    <hyperlink ref="O9" r:id="rId147" xr:uid="{0673BACE-26E7-8D45-A1CD-1F259D25246B}"/>
+    <hyperlink ref="P9" r:id="rId148" location="projects" xr:uid="{D5A1FDD5-2A1B-3B44-A074-1CC3C1696B54}"/>
+    <hyperlink ref="Q9" r:id="rId149" xr:uid="{04365586-73EF-F542-B692-1DB76767E69A}"/>
+    <hyperlink ref="R9" r:id="rId150" xr:uid="{783CC1CB-9D11-1F4D-9667-ED0904711623}"/>
+    <hyperlink ref="O15" r:id="rId151" xr:uid="{9F5FEAEB-77E7-394B-A86C-629E14ADF5BA}"/>
+    <hyperlink ref="O17" r:id="rId152" xr:uid="{ECA9B546-B880-9D49-8ED1-5D50E1F0671E}"/>
+    <hyperlink ref="P17" r:id="rId153" display="https://scholar.google.com/citations?hl=en&amp;user=g9bV-_sAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{18614131-3225-D54A-AAB0-AACB9779176D}"/>
+    <hyperlink ref="N16" r:id="rId154" xr:uid="{553EFE86-57C8-5141-9A58-E791AB30209B}"/>
+    <hyperlink ref="N12" r:id="rId155" xr:uid="{B7614621-BAB6-3C44-8C6A-68B39B963474}"/>
+    <hyperlink ref="Q25" r:id="rId156" xr:uid="{1B11210F-E720-5749-A2C9-1F81014E4519}"/>
+    <hyperlink ref="P25" r:id="rId157" xr:uid="{5C3BFB58-3027-F84A-857B-C2229C512A76}"/>
+    <hyperlink ref="N5" r:id="rId158" xr:uid="{111D39DF-6230-F74B-A0E5-AECA9D12D6D9}"/>
+    <hyperlink ref="O5" r:id="rId159" xr:uid="{F1DA6509-52F1-3944-B26A-E9771C3649FB}"/>
+    <hyperlink ref="P5" r:id="rId160" xr:uid="{8CE1DD35-80BD-6448-AD65-40ABDCCF1379}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/PhD_PI_Listup.xlsx
+++ b/PhD_PI_Listup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyeonbeen/Git/LaTeX-Docs/MyResume/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67BF59D-A4A2-664C-BB2C-C0B8712A8C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D707683-0E5B-9F48-A192-AEE8C9A0360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="22540" activeTab="4" xr2:uid="{422F52E5-BD25-DB4D-B83C-2D9AD22AB820}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CS-CE'!$B$1:$B$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Professors!$B$1:$B$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Professors!$B$1:$B$172</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="768">
   <si>
     <t>PI</t>
   </si>
@@ -2443,9 +2443,6 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Publication Sample, Video</t>
-  </si>
-  <si>
     <t>Supplementary form (500w)</t>
   </si>
   <si>
@@ -2477,15 +2474,9 @@
     <t>(PS==SOP)</t>
   </si>
   <si>
-    <t>Personal Statement (~2p), +(Community 200w)</t>
-  </si>
-  <si>
     <t>CS sup(Courses), Personal History Statement (Unlimited)</t>
   </si>
   <si>
-    <t>(SOP==PS, ~3p), GPA 3.4+</t>
-  </si>
-  <si>
     <t>Life Experiences Statement, 3*1min Video, +(Community, Leadership, Adversity 125w)</t>
   </si>
   <si>
@@ -2496,6 +2487,78 @@
   </si>
   <si>
     <t>Personal Statement KAIST 거절 후 성장 스토리 쓰기</t>
+  </si>
+  <si>
+    <t>Yes but hard to reply</t>
+  </si>
+  <si>
+    <t>Brad Hayes</t>
+  </si>
+  <si>
+    <t>Alessandro Roncone</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>(SOP==PS, ~3p), GPA 3.4+, F-1 VISA IS NOT AVAILABLE</t>
+  </si>
+  <si>
+    <t>2200 MT</t>
+  </si>
+  <si>
+    <t>(SOP==PS, ~2p)</t>
+  </si>
+  <si>
+    <t>Additional Coursework</t>
+  </si>
+  <si>
+    <t>(SOP==PS ~2p, +Community), +(Community 200w)</t>
+  </si>
+  <si>
+    <t>Joseph Campbell</t>
+  </si>
+  <si>
+    <t>Explainable robotics and AI but no pub..?</t>
+  </si>
+  <si>
+    <t>Implicit and learned models, planning with constraints</t>
+  </si>
+  <si>
+    <t>Zachary Kingston</t>
+  </si>
+  <si>
+    <t>Yes but AC decides</t>
+  </si>
+  <si>
+    <t>Rohan Paleja</t>
+  </si>
+  <si>
+    <t>LoR Request/TOEFL Not Sent</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open! Collaborative, Human robot teaming, HRI, explainable robotics.... </t>
+  </si>
+  <si>
+    <t>LoR, TOEFL after deadline?</t>
+  </si>
+  <si>
+    <t>LoR받고 제출만</t>
+  </si>
+  <si>
+    <t>Video, LoR받고 제출만</t>
+  </si>
+  <si>
+    <t>Ann Majewicz Fey</t>
+  </si>
+  <si>
+    <t>Mitchell W Pryor</t>
+  </si>
+  <si>
+    <t>Submitted, awaiting MyStatus</t>
   </si>
 </sst>
 </file>
@@ -3252,7 +3315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132F7052-85E4-E84F-9E71-39A4BFB15A06}">
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" style="5" bestFit="1" customWidth="1"/>
@@ -3929,61 +3992,52 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="B35" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="B36" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B37" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C37" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D37" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E37" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -3991,53 +4045,56 @@
         <v>138</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>303</v>
+        <v>143</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>304</v>
+        <v>142</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>450</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>30</v>
+      <c r="A39" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>485</v>
+        <v>138</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>489</v>
+        <v>81</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>303</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>490</v>
+        <v>304</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -4048,13 +4105,13 @@
         <v>486</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -4065,13 +4122,13 @@
         <v>486</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -4082,13 +4139,13 @@
         <v>486</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -4099,13 +4156,13 @@
         <v>486</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -4116,87 +4173,81 @@
         <v>486</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>214</v>
+      <c r="B49" s="13" t="s">
+        <v>215</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F49" s="33" t="s">
-        <v>57</v>
+      <c r="F49" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -4204,104 +4255,119 @@
         <v>45</v>
       </c>
       <c r="B50" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C52" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D52" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E52" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F52" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="33" t="s">
+      <c r="F53" s="33" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>424</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>511</v>
+        <v>45</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="B55" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>516</v>
+      <c r="C55" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -4312,7 +4378,10 @@
         <v>5</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>517</v>
+        <v>512</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
@@ -4323,13 +4392,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>28</v>
+        <v>516</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -4340,13 +4403,7 @@
         <v>5</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>29</v>
+        <v>517</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
@@ -4357,343 +4414,346 @@
         <v>5</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E60" s="12" t="s">
+      <c r="A60" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B62" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C62" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="15" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="15" t="s">
         <v>629</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B65" s="16" t="s">
         <v>609</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C65" s="17" t="s">
         <v>605</v>
       </c>
-      <c r="D63" s="16" t="s">
+      <c r="D65" s="16" t="s">
         <v>606</v>
       </c>
-      <c r="E63" s="16" t="s">
+      <c r="E65" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F65" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="14" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="14" t="s">
         <v>629</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B66" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C66" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D66" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E66" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F66" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="5" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F67" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="5" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="14" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="14" t="s">
         <v>629</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B69" s="12" t="s">
         <v>617</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C69" s="13" t="s">
         <v>616</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D69" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E69" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F69" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="15" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="15" t="s">
         <v>629</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B70" s="16" t="s">
         <v>617</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C70" s="17" t="s">
         <v>619</v>
       </c>
-      <c r="D68" s="16" t="s">
+      <c r="D70" s="16" t="s">
         <v>618</v>
       </c>
-      <c r="E68" s="16" t="s">
+      <c r="E70" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="5" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="5" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="18" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="B73" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C73" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D71" s="19" t="s">
+      <c r="D73" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="E71" s="19" t="s">
+      <c r="E73" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73" s="33" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>754</v>
+      </c>
+      <c r="E74" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F71" s="33" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="18" t="s">
+      <c r="F74" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B75" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C75" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="D75" s="70" t="s">
+        <v>761</v>
+      </c>
+      <c r="E75" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>756</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D72" s="19" t="s">
+      <c r="D77" s="19" t="s">
         <v>434</v>
       </c>
-      <c r="E72" s="19" t="s">
+      <c r="E77" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F77" s="6" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>546</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>553</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
@@ -4701,56 +4761,50 @@
         <v>60</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B80" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>704</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>706</v>
-      </c>
-      <c r="E79" s="12" t="s">
+      <c r="C80" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>22</v>
@@ -4758,68 +4812,59 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>701</v>
+        <v>547</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>705</v>
+        <v>548</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F81" s="33" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C82" s="17" t="s">
-        <v>510</v>
-      </c>
-      <c r="D82" s="16" t="s">
-        <v>707</v>
-      </c>
-      <c r="E82" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F82" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -4830,10 +4875,10 @@
         <v>5</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>7</v>
+        <v>704</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>29</v>
@@ -4847,18 +4892,18 @@
         <v>4</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>9</v>
+        <v>702</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>10</v>
+        <v>703</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4867,39 +4912,39 @@
         <v>4</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>701</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>12</v>
+        <v>705</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F86" s="34" t="s">
-        <v>20</v>
+      <c r="F86" s="33" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B87" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F87" s="33" t="s">
-        <v>426</v>
+      <c r="B87" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>707</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -4907,19 +4952,25 @@
         <v>4</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>24</v>
+        <v>363</v>
       </c>
       <c r="E88" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F88" s="33" t="s">
-        <v>426</v>
+      <c r="F88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -4927,36 +4978,36 @@
         <v>4</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>405</v>
+        <v>5</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>18</v>
+        <v>708</v>
       </c>
       <c r="E89" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F89" s="33" t="s">
-        <v>426</v>
+      <c r="F89" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B90" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>29</v>
+      <c r="B90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>22</v>
@@ -4964,518 +5015,521 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>365</v>
+        <v>12</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="F91" s="34" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="14" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>459</v>
+        <v>16</v>
       </c>
       <c r="E92" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F92" s="33" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="14" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E93" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>22</v>
+      <c r="F93" s="33" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="14" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>5</v>
+        <v>405</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E94" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>430</v>
+      <c r="F94" s="33" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="14" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>458</v>
+        <v>21</v>
       </c>
       <c r="E95" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F95" s="33" t="s">
+      <c r="F95" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97" s="33" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100" s="33" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="14" t="s">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B101" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C101" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D101" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="E101" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F96" s="33" t="s">
+      <c r="F101" s="33" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" s="5" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F102" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="5" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F103" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="5" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="F104" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A100" s="15" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="B100" s="16" t="s">
+      <c r="B105" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C100" s="17" t="s">
+      <c r="C105" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="D100" s="16" t="s">
+      <c r="D105" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="E100" s="16" t="s">
+      <c r="E105" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F100" s="6" t="s">
+      <c r="F105" s="6" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" s="15" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B106" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="17" t="s">
+      <c r="C106" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="D101" s="16" t="s">
+      <c r="D106" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="E101" s="16" t="s">
+      <c r="E106" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="F106" s="6" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" s="18" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B102" s="19" t="s">
+      <c r="B107" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="C102" s="20" t="s">
+      <c r="C107" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="D102" s="19" t="s">
+      <c r="D107" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="E102" s="19" t="s">
+      <c r="E107" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F102" s="6" t="s">
+      <c r="F107" s="6" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A104" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B104" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C104" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E104" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A105" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A106" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B107" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C107" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E107" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F107" s="33" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="14" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>182</v>
+        <v>92</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>577</v>
+        <v>91</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>578</v>
+        <v>93</v>
       </c>
       <c r="E108" s="12" t="s">
         <v>29</v>
       </c>
+      <c r="F108" s="6" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A109" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B109" s="1" t="s">
+      <c r="A109" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="E109" s="1" t="s">
+      <c r="C110" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A110" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="B110" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="C110" s="53" t="s">
-        <v>581</v>
-      </c>
-      <c r="D110" s="52" t="s">
-        <v>582</v>
-      </c>
-      <c r="E110" s="52" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>265</v>
+        <v>90</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>8</v>
+        <v>182</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>266</v>
+        <v>526</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>308</v>
+        <v>527</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F111" s="6" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A112" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B112" s="1" t="s">
+      <c r="A112" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B112" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="C112" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112" s="33" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F112" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A113" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C113" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="E113" s="19" t="s">
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="C115" s="53" t="s">
+        <v>581</v>
+      </c>
+      <c r="D115" s="52" t="s">
+        <v>582</v>
+      </c>
+      <c r="E115" s="52" t="s">
         <v>128</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B114" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C114" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E114" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F114" s="33" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A115" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>532</v>
+        <v>8</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>523</v>
+        <v>266</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>533</v>
+        <v>308</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="F116" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>410</v>
+        <v>265</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>411</v>
+        <v>8</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>412</v>
+        <v>267</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>413</v>
+        <v>268</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>28</v>
@@ -5485,94 +5539,94 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A118" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>30</v>
+      <c r="A118" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C118" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="14" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E119" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F119" s="6" t="s">
-        <v>22</v>
+      <c r="F119" s="33" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>105</v>
+        <v>530</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>531</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>106</v>
+        <v>534</v>
       </c>
       <c r="E120" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A121" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C121" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D121" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="E121" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>97</v>
+        <v>410</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>105</v>
+        <v>412</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>28</v>
@@ -5582,214 +5636,211 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A123" s="14" t="s">
+      <c r="A123" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B123" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C123" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="E123" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>22</v>
+      <c r="B123" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="14" t="s">
-        <v>414</v>
+        <v>97</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>415</v>
+        <v>104</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>416</v>
+        <v>102</v>
       </c>
       <c r="E124" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>457</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>414</v>
+        <v>97</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>470</v>
+        <v>105</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>471</v>
+        <v>106</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="F125" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A126" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>476</v>
+      <c r="A126" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C126" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E126" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>414</v>
+        <v>97</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>8</v>
+        <v>442</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>474</v>
+        <v>105</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="14" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>256</v>
+        <v>445</v>
       </c>
       <c r="E128" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F128" s="6" t="s">
+      <c r="F128" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>22</v>
+      <c r="A129" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>124</v>
+        <v>414</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>131</v>
+        <v>470</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>132</v>
+        <v>471</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F130" s="3" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B133" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C131" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F131" s="6" t="s">
+      <c r="C133" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F133" s="6" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B132" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="C132" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="D132" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E132" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F132" s="33" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B133" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="C133" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="D133" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="E133" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F133" s="33" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
@@ -5797,39 +5848,39 @@
         <v>124</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>249</v>
+        <v>127</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>251</v>
+        <v>130</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F134" s="6" t="s">
+      <c r="F134" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" s="18" t="s">
+      <c r="A135" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B135" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="C135" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="D135" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="E135" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>22</v>
+      <c r="B135" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
@@ -5837,13 +5888,13 @@
         <v>124</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>257</v>
+        <v>127</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>30</v>
@@ -5854,239 +5905,239 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="14" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>8</v>
+        <v>246</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>151</v>
+        <v>248</v>
       </c>
       <c r="E137" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F137" s="33" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="15" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>153</v>
+        <v>482</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>157</v>
+        <v>483</v>
       </c>
       <c r="E138" s="16" t="s">
         <v>128</v>
       </c>
       <c r="F138" s="33" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A139" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C139" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="D139" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="E139" s="16" t="s">
+      <c r="A139" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="C140" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="D140" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E140" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F139" s="33" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F140" s="6" t="s">
-        <v>437</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B142" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="C142" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F142" s="33" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C143" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D143" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="E143" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F143" s="33" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C144" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D144" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E144" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F144" s="33" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="E141" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F141" s="31" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B142" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="C142" s="17" t="s">
-        <v>591</v>
-      </c>
-      <c r="D142" s="16" t="s">
-        <v>592</v>
-      </c>
-      <c r="E142" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="B143" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="C143" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D143" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E143" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A144" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C145" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D145" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E145" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F145" s="33" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B146" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C146" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>403</v>
       </c>
       <c r="E146" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F146" s="33" t="s">
-        <v>441</v>
+      <c r="F146" s="31" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>22</v>
+      <c r="A147" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B147" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C147" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="D147" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="E147" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B148" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C148" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D148" s="22" t="s">
-        <v>402</v>
-      </c>
-      <c r="E148" s="22" t="s">
-        <v>128</v>
+      <c r="A148" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>22</v>
@@ -6094,13 +6145,22 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>528</v>
+        <v>165</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
@@ -6111,227 +6171,235 @@
         <v>8</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>529</v>
+        <v>84</v>
       </c>
       <c r="E150" s="12" t="s">
         <v>29</v>
       </c>
+      <c r="F150" s="33" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" s="55" t="s">
+      <c r="A151" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B151" s="56" t="s">
+      <c r="B151" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C151" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D151" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F151" s="33" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B153" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C151" s="54" t="s">
+      <c r="C153" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D153" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="E153" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B155" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C155" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="B156" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="54" t="s">
         <v>535</v>
       </c>
-      <c r="D151" s="56" t="s">
+      <c r="D156" s="56" t="s">
         <v>536</v>
       </c>
-      <c r="E151" s="56" t="s">
+      <c r="E156" s="56" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" s="51" t="s">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="B152" s="52" t="s">
+      <c r="B157" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C152" s="53" t="s">
+      <c r="C157" s="53" t="s">
         <v>537</v>
       </c>
-      <c r="D152" s="52" t="s">
+      <c r="D157" s="52" t="s">
         <v>538</v>
       </c>
-      <c r="E152" s="52" t="s">
+      <c r="E157" s="52" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="B154" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C154" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="D154" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="E154" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F154" s="33" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="B155" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C155" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D155" s="16" t="s">
-        <v>419</v>
-      </c>
-      <c r="E155" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="B157" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C157" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="D157" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="E157" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F157" s="33" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>380</v>
+        <v>5</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>539</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>379</v>
+        <v>540</v>
       </c>
       <c r="E158" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C159" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="D159" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="E159" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F158" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A159" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="B159" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C159" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="D159" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="E159" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>22</v>
+      <c r="F159" s="33" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A160" s="58" t="s">
-        <v>374</v>
-      </c>
-      <c r="B160" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="C160" s="50" t="s">
-        <v>571</v>
-      </c>
-      <c r="D160" s="59"/>
-      <c r="E160" s="59" t="s">
+      <c r="A160" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="B160" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C160" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="D160" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="E160" s="16" t="s">
         <v>128</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>30</v>
+      <c r="B162" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C162" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F162" s="33" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
@@ -6339,30 +6407,33 @@
         <v>374</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>575</v>
+        <v>92</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>380</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>576</v>
+        <v>379</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>30</v>
+        <v>128</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" s="14" t="s">
-        <v>628</v>
+        <v>374</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="C164" s="13" t="s">
-        <v>168</v>
+        <v>377</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>169</v>
+        <v>378</v>
       </c>
       <c r="E164" s="12" t="s">
         <v>29</v>
@@ -6372,148 +6443,228 @@
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A165" s="14" t="s">
-        <v>628</v>
-      </c>
-      <c r="B165" s="12" t="s">
+      <c r="A165" s="58" t="s">
+        <v>374</v>
+      </c>
+      <c r="B165" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="C165" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="D165" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="E165" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F165" s="6" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="69" t="s">
-        <v>628</v>
-      </c>
-      <c r="B166" s="70" t="s">
+      <c r="C165" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="D165" s="59"/>
+      <c r="E165" s="59" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C166" s="6" t="s">
-        <v>730</v>
-      </c>
-      <c r="D166" s="70" t="s">
-        <v>731</v>
-      </c>
-      <c r="F166" s="6"/>
+      <c r="C166" s="3" t="s">
+        <v>572</v>
+      </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A167" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B167" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C167" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D167" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="E167" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F167" s="33" t="s">
-        <v>452</v>
+      <c r="A167" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C169" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C170" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="69" t="s">
+        <v>628</v>
+      </c>
+      <c r="B171" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="D171" s="70" t="s">
+        <v>731</v>
+      </c>
+      <c r="F171" s="6"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B172" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D172" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E172" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F172" s="33" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B173" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="C168" s="3" t="s">
+      <c r="C173" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="F168" s="3" t="s">
+      <c r="F173" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B169" s="1" t="s">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B174" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="C174" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="E169" s="1" t="s">
+      <c r="E174" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F169" s="3" t="s">
+      <c r="F174" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C170" s="3" t="s">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C175" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="F170" s="3" t="s">
+      <c r="F175" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C171" s="3" t="s">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C176" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="F171" s="3" t="s">
+      <c r="F176" s="3" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C172" s="3" t="s">
+    <row r="177" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C177" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="F172" s="3" t="s">
+      <c r="F177" s="3" t="s">
         <v>720</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B168" xr:uid="{132F7052-85E4-E84F-9E71-39A4BFB15A06}"/>
+  <autoFilter ref="B1:B173" xr:uid="{132F7052-85E4-E84F-9E71-39A4BFB15A06}"/>
   <hyperlinks>
-    <hyperlink ref="C83" r:id="rId1" xr:uid="{37811C14-1E8A-824B-A884-5D27D40716EF}"/>
-    <hyperlink ref="C84" r:id="rId2" xr:uid="{4DB6FFDB-CBCA-8F40-B2E7-E5258DF17DCB}"/>
-    <hyperlink ref="C85" r:id="rId3" xr:uid="{60E02B82-4983-0844-A558-59C7981074DB}"/>
-    <hyperlink ref="C86" r:id="rId4" location="publications" xr:uid="{25E44166-B5BC-A049-995A-9ED68E851C37}"/>
-    <hyperlink ref="C90" r:id="rId5" xr:uid="{2D44903F-FEAE-4240-809A-EEAA193BE228}"/>
-    <hyperlink ref="C87" r:id="rId6" location="people" xr:uid="{4B9D6F3B-BAB9-494E-82B0-0BD07470A89C}"/>
-    <hyperlink ref="C89" r:id="rId7" xr:uid="{B3A8E9BD-E781-8243-855D-117BF1174B02}"/>
-    <hyperlink ref="C88" r:id="rId8" xr:uid="{5C6D8E4D-C69F-A546-95DE-EE42D8AB8089}"/>
-    <hyperlink ref="C91" r:id="rId9" xr:uid="{A9020D64-DAB9-3E47-AED5-6AE7F10D93A8}"/>
-    <hyperlink ref="C92" r:id="rId10" xr:uid="{9FE9E8C0-9671-FD4F-88A9-79291BC64D5A}"/>
-    <hyperlink ref="F92" r:id="rId11" xr:uid="{66F59F4B-9B01-7546-AFBB-CA1740AC4F67}"/>
-    <hyperlink ref="C93" r:id="rId12" xr:uid="{7A0A8504-2B7E-8346-B9B4-6FA6C3FB59FE}"/>
-    <hyperlink ref="C94" r:id="rId13" xr:uid="{A233F54A-7B3B-BF49-A4DB-C70550B00017}"/>
-    <hyperlink ref="C96" r:id="rId14" xr:uid="{5327D505-B7E7-AB42-A864-D87C1C130843}"/>
-    <hyperlink ref="F96" r:id="rId15" display="Yes" xr:uid="{7D4005A3-151D-DD46-A15F-D83D01E657AD}"/>
-    <hyperlink ref="F97" r:id="rId16" xr:uid="{A04EC1EA-D533-8D41-8207-24B50E7927DD}"/>
-    <hyperlink ref="F98" r:id="rId17" xr:uid="{E4A60B9C-4533-BA49-AD0B-F4AA55DBD473}"/>
-    <hyperlink ref="C98" r:id="rId18" xr:uid="{88BA93F9-325B-1949-A84B-841920F3AC87}"/>
-    <hyperlink ref="C97" r:id="rId19" xr:uid="{B81D9CC2-9D59-FB40-BF26-550E35A86B3E}"/>
-    <hyperlink ref="C99" r:id="rId20" xr:uid="{DC62901E-0D49-2C46-BBB6-DFCA02929FC3}"/>
-    <hyperlink ref="C47" r:id="rId21" xr:uid="{A7425927-15C9-2B47-B442-D6622AB3DD92}"/>
-    <hyperlink ref="F47" r:id="rId22" xr:uid="{CB83AE0D-0C3B-CC42-B83C-BDBD28D88240}"/>
-    <hyperlink ref="B47" r:id="rId23" display="ME, ROBO(preferred)" xr:uid="{35C45632-B60B-C64F-9579-4518F537C884}"/>
-    <hyperlink ref="C48" r:id="rId24" xr:uid="{4332801B-5602-114C-BE41-15DDA2A562E6}"/>
-    <hyperlink ref="F48" r:id="rId25" xr:uid="{F29BDC9E-0153-1448-AA28-33241D6A26BB}"/>
-    <hyperlink ref="C49" r:id="rId26" xr:uid="{77807196-58B3-1740-9207-03DFFAE42BC7}"/>
-    <hyperlink ref="F49" r:id="rId27" display="Yes" xr:uid="{0B091E55-ADC9-6B48-99BF-94530DA49108}"/>
-    <hyperlink ref="C51" r:id="rId28" xr:uid="{6C3CEE39-37EF-8643-9408-7143832EE6CC}"/>
-    <hyperlink ref="F51" r:id="rId29" location="heading=h.o56b04aeo1c9" display="No" xr:uid="{4A448277-35FA-D54B-878F-7884D25EF08A}"/>
-    <hyperlink ref="C52" r:id="rId30" location="content4-e" xr:uid="{68DAC647-2FF5-7D40-9B3F-A7CFDE9F9724}"/>
-    <hyperlink ref="C72" r:id="rId31" xr:uid="{39872464-0223-E74D-B0EB-E1DD076A4CD2}"/>
-    <hyperlink ref="C74" r:id="rId32" xr:uid="{B0DEBDAF-2E75-E74D-8BE7-D41D17A6F850}"/>
-    <hyperlink ref="C73" r:id="rId33" xr:uid="{BBC8B767-1512-6649-8B7F-9F2D824F0F9D}"/>
+    <hyperlink ref="C88" r:id="rId1" xr:uid="{37811C14-1E8A-824B-A884-5D27D40716EF}"/>
+    <hyperlink ref="C89" r:id="rId2" xr:uid="{4DB6FFDB-CBCA-8F40-B2E7-E5258DF17DCB}"/>
+    <hyperlink ref="C90" r:id="rId3" xr:uid="{60E02B82-4983-0844-A558-59C7981074DB}"/>
+    <hyperlink ref="C91" r:id="rId4" location="publications" xr:uid="{25E44166-B5BC-A049-995A-9ED68E851C37}"/>
+    <hyperlink ref="C95" r:id="rId5" xr:uid="{2D44903F-FEAE-4240-809A-EEAA193BE228}"/>
+    <hyperlink ref="C92" r:id="rId6" location="people" xr:uid="{4B9D6F3B-BAB9-494E-82B0-0BD07470A89C}"/>
+    <hyperlink ref="C94" r:id="rId7" xr:uid="{B3A8E9BD-E781-8243-855D-117BF1174B02}"/>
+    <hyperlink ref="C93" r:id="rId8" xr:uid="{5C6D8E4D-C69F-A546-95DE-EE42D8AB8089}"/>
+    <hyperlink ref="C96" r:id="rId9" xr:uid="{A9020D64-DAB9-3E47-AED5-6AE7F10D93A8}"/>
+    <hyperlink ref="C97" r:id="rId10" xr:uid="{9FE9E8C0-9671-FD4F-88A9-79291BC64D5A}"/>
+    <hyperlink ref="F97" r:id="rId11" xr:uid="{66F59F4B-9B01-7546-AFBB-CA1740AC4F67}"/>
+    <hyperlink ref="C98" r:id="rId12" xr:uid="{7A0A8504-2B7E-8346-B9B4-6FA6C3FB59FE}"/>
+    <hyperlink ref="C99" r:id="rId13" xr:uid="{A233F54A-7B3B-BF49-A4DB-C70550B00017}"/>
+    <hyperlink ref="C101" r:id="rId14" xr:uid="{5327D505-B7E7-AB42-A864-D87C1C130843}"/>
+    <hyperlink ref="F101" r:id="rId15" display="Yes" xr:uid="{7D4005A3-151D-DD46-A15F-D83D01E657AD}"/>
+    <hyperlink ref="F102" r:id="rId16" xr:uid="{A04EC1EA-D533-8D41-8207-24B50E7927DD}"/>
+    <hyperlink ref="F103" r:id="rId17" xr:uid="{E4A60B9C-4533-BA49-AD0B-F4AA55DBD473}"/>
+    <hyperlink ref="C103" r:id="rId18" xr:uid="{88BA93F9-325B-1949-A84B-841920F3AC87}"/>
+    <hyperlink ref="C102" r:id="rId19" xr:uid="{B81D9CC2-9D59-FB40-BF26-550E35A86B3E}"/>
+    <hyperlink ref="C104" r:id="rId20" xr:uid="{DC62901E-0D49-2C46-BBB6-DFCA02929FC3}"/>
+    <hyperlink ref="C49" r:id="rId21" xr:uid="{A7425927-15C9-2B47-B442-D6622AB3DD92}"/>
+    <hyperlink ref="F49" r:id="rId22" xr:uid="{CB83AE0D-0C3B-CC42-B83C-BDBD28D88240}"/>
+    <hyperlink ref="B49" r:id="rId23" display="ME, ROBO(preferred)" xr:uid="{35C45632-B60B-C64F-9579-4518F537C884}"/>
+    <hyperlink ref="C50" r:id="rId24" xr:uid="{4332801B-5602-114C-BE41-15DDA2A562E6}"/>
+    <hyperlink ref="F50" r:id="rId25" xr:uid="{F29BDC9E-0153-1448-AA28-33241D6A26BB}"/>
+    <hyperlink ref="C51" r:id="rId26" xr:uid="{77807196-58B3-1740-9207-03DFFAE42BC7}"/>
+    <hyperlink ref="F51" r:id="rId27" display="Yes" xr:uid="{0B091E55-ADC9-6B48-99BF-94530DA49108}"/>
+    <hyperlink ref="C53" r:id="rId28" xr:uid="{6C3CEE39-37EF-8643-9408-7143832EE6CC}"/>
+    <hyperlink ref="F53" r:id="rId29" location="heading=h.o56b04aeo1c9" display="No" xr:uid="{4A448277-35FA-D54B-878F-7884D25EF08A}"/>
+    <hyperlink ref="C54" r:id="rId30" location="content4-e" xr:uid="{68DAC647-2FF5-7D40-9B3F-A7CFDE9F9724}"/>
+    <hyperlink ref="C77" r:id="rId31" xr:uid="{39872464-0223-E74D-B0EB-E1DD076A4CD2}"/>
+    <hyperlink ref="C79" r:id="rId32" xr:uid="{B0DEBDAF-2E75-E74D-8BE7-D41D17A6F850}"/>
+    <hyperlink ref="C78" r:id="rId33" xr:uid="{BBC8B767-1512-6649-8B7F-9F2D824F0F9D}"/>
     <hyperlink ref="C10" r:id="rId34" location="projects" xr:uid="{FFF4F158-9F83-CE48-9808-B7D6B356CC4F}"/>
     <hyperlink ref="F10" r:id="rId35" xr:uid="{BFC1CA03-B547-7042-BAFD-B8F6E90D8427}"/>
     <hyperlink ref="C12" r:id="rId36" xr:uid="{EC3E5B97-7A3C-5A49-931B-B173E87B0151}"/>
@@ -6521,86 +6672,86 @@
     <hyperlink ref="C11" r:id="rId38" xr:uid="{78B13E7E-1127-A547-8244-FA6E5002698A}"/>
     <hyperlink ref="C19" r:id="rId39" xr:uid="{7E848999-856A-A849-B657-521AADD30D66}"/>
     <hyperlink ref="F19" r:id="rId40" xr:uid="{4C566A0A-64A5-BA44-A80B-CCB366CCF7AD}"/>
-    <hyperlink ref="C114" r:id="rId41" xr:uid="{3DD32363-C20D-0F48-A8AB-04A87B8806EB}"/>
-    <hyperlink ref="C145" r:id="rId42" xr:uid="{79D9D827-AAB5-2D4B-99E3-474BC0B9AA4E}"/>
-    <hyperlink ref="F145" r:id="rId43" display="No" xr:uid="{12ACB131-F843-B04E-B2C8-B048573A0F61}"/>
-    <hyperlink ref="F114" r:id="rId44" xr:uid="{9BAD156A-7083-9041-ABF4-2FF0E51F57B4}"/>
-    <hyperlink ref="C146" r:id="rId45" xr:uid="{121EFBFF-EE3D-C34F-8C33-A880AD30A609}"/>
-    <hyperlink ref="F146" r:id="rId46" display="Form" xr:uid="{39D7A72A-DF53-1742-94F2-6C1949649485}"/>
-    <hyperlink ref="C148" r:id="rId47" xr:uid="{58A1494B-6445-E54C-B70A-94BCC8E76B48}"/>
-    <hyperlink ref="F148" r:id="rId48" xr:uid="{F2B34C73-0BB9-804C-82A8-83FD1428FCF4}"/>
-    <hyperlink ref="C147" r:id="rId49" xr:uid="{B5BEFC2B-5EBE-AF43-A956-2C83591CC3A1}"/>
-    <hyperlink ref="F147" r:id="rId50" xr:uid="{C7BA0F10-763D-C044-AC03-318F8F3912C1}"/>
-    <hyperlink ref="C103" r:id="rId51" location="_ri" xr:uid="{398354CA-7B5B-9149-A6A1-EA339C4F9153}"/>
-    <hyperlink ref="C104" r:id="rId52" xr:uid="{D4E488D7-008C-7041-89A3-A142D3179430}"/>
-    <hyperlink ref="C118" r:id="rId53" xr:uid="{7525C0C7-0476-1844-80BD-C64A1FD08428}"/>
-    <hyperlink ref="C119" r:id="rId54" location="Publications-Section" xr:uid="{D2E4E0C6-3578-7842-9B7B-3D4E15B431D2}"/>
-    <hyperlink ref="C120" r:id="rId55" xr:uid="{9493C1D5-873A-914C-B90E-FEEDC858E63A}"/>
-    <hyperlink ref="C123" r:id="rId56" xr:uid="{903CD93B-52AB-4244-9247-F63FFBC2B66E}"/>
+    <hyperlink ref="C119" r:id="rId41" xr:uid="{3DD32363-C20D-0F48-A8AB-04A87B8806EB}"/>
+    <hyperlink ref="C150" r:id="rId42" xr:uid="{79D9D827-AAB5-2D4B-99E3-474BC0B9AA4E}"/>
+    <hyperlink ref="F150" r:id="rId43" display="No" xr:uid="{12ACB131-F843-B04E-B2C8-B048573A0F61}"/>
+    <hyperlink ref="F119" r:id="rId44" xr:uid="{9BAD156A-7083-9041-ABF4-2FF0E51F57B4}"/>
+    <hyperlink ref="C151" r:id="rId45" xr:uid="{121EFBFF-EE3D-C34F-8C33-A880AD30A609}"/>
+    <hyperlink ref="F151" r:id="rId46" display="Form" xr:uid="{39D7A72A-DF53-1742-94F2-6C1949649485}"/>
+    <hyperlink ref="C153" r:id="rId47" xr:uid="{58A1494B-6445-E54C-B70A-94BCC8E76B48}"/>
+    <hyperlink ref="F153" r:id="rId48" xr:uid="{F2B34C73-0BB9-804C-82A8-83FD1428FCF4}"/>
+    <hyperlink ref="C152" r:id="rId49" xr:uid="{B5BEFC2B-5EBE-AF43-A956-2C83591CC3A1}"/>
+    <hyperlink ref="F152" r:id="rId50" xr:uid="{C7BA0F10-763D-C044-AC03-318F8F3912C1}"/>
+    <hyperlink ref="C108" r:id="rId51" location="_ri" xr:uid="{398354CA-7B5B-9149-A6A1-EA339C4F9153}"/>
+    <hyperlink ref="C109" r:id="rId52" xr:uid="{D4E488D7-008C-7041-89A3-A142D3179430}"/>
+    <hyperlink ref="C123" r:id="rId53" xr:uid="{7525C0C7-0476-1844-80BD-C64A1FD08428}"/>
+    <hyperlink ref="C124" r:id="rId54" location="Publications-Section" xr:uid="{D2E4E0C6-3578-7842-9B7B-3D4E15B431D2}"/>
+    <hyperlink ref="C125" r:id="rId55" xr:uid="{9493C1D5-873A-914C-B90E-FEEDC858E63A}"/>
+    <hyperlink ref="C128" r:id="rId56" xr:uid="{903CD93B-52AB-4244-9247-F63FFBC2B66E}"/>
     <hyperlink ref="C26" r:id="rId57" xr:uid="{E11FE763-70DE-C843-98C2-D0666AEC11CB}"/>
     <hyperlink ref="F26" r:id="rId58" xr:uid="{578842D3-A5E6-9A4D-A12F-433FEB4AA4A9}"/>
     <hyperlink ref="F27" r:id="rId59" display="No..?" xr:uid="{6857B64A-8193-8C49-B5DE-EF672F9FE0C8}"/>
     <hyperlink ref="C27" r:id="rId60" location="teaching-section" xr:uid="{3FEB6C00-AB64-8848-A2BB-19CE73970FA2}"/>
-    <hyperlink ref="C69" r:id="rId61" xr:uid="{6888BF5B-E86F-B943-B6F3-8320FAFA1445}"/>
-    <hyperlink ref="C70" r:id="rId62" xr:uid="{4950B2C5-F17D-624A-AE62-9834277190C0}"/>
-    <hyperlink ref="C107" r:id="rId63" xr:uid="{EB00FB88-140C-FF4E-97F0-7A534D9127FD}"/>
-    <hyperlink ref="F107" r:id="rId64" display="No..?" xr:uid="{C81212D7-0A6B-AC4F-A3BB-87C0DF2B141B}"/>
-    <hyperlink ref="C128" r:id="rId65" xr:uid="{28FD696E-AA3D-5340-9AEE-9B33DAA9100D}"/>
-    <hyperlink ref="F128" r:id="rId66" xr:uid="{301665C9-748B-B74C-8E22-3C2BE315B9A0}"/>
-    <hyperlink ref="C129" r:id="rId67" xr:uid="{9BEA1D4E-E0E9-7F4D-95FF-AA1E5A0A38A7}"/>
-    <hyperlink ref="C130" r:id="rId68" xr:uid="{C54146DC-1962-304A-9ADE-27C93D064A33}"/>
-    <hyperlink ref="F130" r:id="rId69" xr:uid="{BB877229-AE13-9D41-B111-355DE3218E1F}"/>
+    <hyperlink ref="C71" r:id="rId61" xr:uid="{6888BF5B-E86F-B943-B6F3-8320FAFA1445}"/>
+    <hyperlink ref="C72" r:id="rId62" xr:uid="{4950B2C5-F17D-624A-AE62-9834277190C0}"/>
+    <hyperlink ref="C112" r:id="rId63" xr:uid="{EB00FB88-140C-FF4E-97F0-7A534D9127FD}"/>
+    <hyperlink ref="F112" r:id="rId64" display="No..?" xr:uid="{C81212D7-0A6B-AC4F-A3BB-87C0DF2B141B}"/>
+    <hyperlink ref="C133" r:id="rId65" xr:uid="{28FD696E-AA3D-5340-9AEE-9B33DAA9100D}"/>
+    <hyperlink ref="F133" r:id="rId66" xr:uid="{301665C9-748B-B74C-8E22-3C2BE315B9A0}"/>
+    <hyperlink ref="C134" r:id="rId67" xr:uid="{9BEA1D4E-E0E9-7F4D-95FF-AA1E5A0A38A7}"/>
+    <hyperlink ref="C135" r:id="rId68" xr:uid="{C54146DC-1962-304A-9ADE-27C93D064A33}"/>
+    <hyperlink ref="F135" r:id="rId69" xr:uid="{BB877229-AE13-9D41-B111-355DE3218E1F}"/>
     <hyperlink ref="C21" r:id="rId70" xr:uid="{CAE1FF08-3B4A-AF4B-A8FA-73AF2979DDFB}"/>
     <hyperlink ref="C22" r:id="rId71" xr:uid="{FD5EA699-A473-E14B-A007-8B39747A7B97}"/>
     <hyperlink ref="F22" r:id="rId72" xr:uid="{2F58E973-C7F1-6F4F-992D-3FE73FC1921B}"/>
-    <hyperlink ref="C35" r:id="rId73" xr:uid="{908C7485-2276-F845-B011-956C90745E36}"/>
-    <hyperlink ref="C36" r:id="rId74" xr:uid="{56CA5437-DF65-7741-BCB4-0097BF46AF5A}"/>
+    <hyperlink ref="C37" r:id="rId73" xr:uid="{908C7485-2276-F845-B011-956C90745E36}"/>
+    <hyperlink ref="C38" r:id="rId74" xr:uid="{56CA5437-DF65-7741-BCB4-0097BF46AF5A}"/>
     <hyperlink ref="C33" r:id="rId75" xr:uid="{E3A4C8BD-C578-CD47-ACE1-48F233318094}"/>
     <hyperlink ref="C34" r:id="rId76" xr:uid="{BB02585E-E4AF-7B40-A5E2-FA20343B6B7D}"/>
     <hyperlink ref="F34" r:id="rId77" xr:uid="{11068305-3E64-9847-B25B-E7B4232FDC83}"/>
-    <hyperlink ref="F35" r:id="rId78" xr:uid="{E1F068DF-7982-B140-891F-18371252BEE9}"/>
+    <hyperlink ref="F37" r:id="rId78" xr:uid="{E1F068DF-7982-B140-891F-18371252BEE9}"/>
     <hyperlink ref="F33" r:id="rId79" xr:uid="{4857BCFA-63F9-D343-996F-B0086015D867}"/>
-    <hyperlink ref="C137" r:id="rId80" xr:uid="{8478D9E5-A9E7-1F41-9E1F-E87F15560F85}"/>
-    <hyperlink ref="F137" r:id="rId81" display="No..?" xr:uid="{F208C5E3-A0C4-1D4B-91C0-2BDC60993E9E}"/>
-    <hyperlink ref="C138" r:id="rId82" xr:uid="{45834B70-B9CF-874E-BDDD-07DC65A97A82}"/>
-    <hyperlink ref="C139" r:id="rId83" xr:uid="{5999988D-62DD-7740-8281-D4A8476498DF}"/>
-    <hyperlink ref="C140" r:id="rId84" xr:uid="{D4D3BD11-6490-B646-B302-20BFB3D7DF5F}"/>
-    <hyperlink ref="C141" r:id="rId85" xr:uid="{923B455F-766D-1245-B440-3E155C36EB08}"/>
-    <hyperlink ref="F141" r:id="rId86" xr:uid="{13585F3B-4D88-FD44-80C6-27534407E6B3}"/>
-    <hyperlink ref="C143" r:id="rId87" location="conference-publications" xr:uid="{1A804911-E79D-9141-A167-60595CEE1F71}"/>
-    <hyperlink ref="C144" r:id="rId88" xr:uid="{3D2271F2-C077-F646-9F3C-5EB7256C0CF2}"/>
-    <hyperlink ref="C164" r:id="rId89" xr:uid="{51A16F76-2C2A-6C41-8E1D-A56F68000383}"/>
-    <hyperlink ref="F165" r:id="rId90" display="No..?" xr:uid="{CFB38AB7-6FFD-7543-9665-38F4AF916308}"/>
-    <hyperlink ref="C167" r:id="rId91" xr:uid="{6E550245-9521-014D-B426-EDEBB6147E4A}"/>
+    <hyperlink ref="C142" r:id="rId80" xr:uid="{8478D9E5-A9E7-1F41-9E1F-E87F15560F85}"/>
+    <hyperlink ref="F142" r:id="rId81" display="No..?" xr:uid="{F208C5E3-A0C4-1D4B-91C0-2BDC60993E9E}"/>
+    <hyperlink ref="C143" r:id="rId82" xr:uid="{45834B70-B9CF-874E-BDDD-07DC65A97A82}"/>
+    <hyperlink ref="C144" r:id="rId83" xr:uid="{5999988D-62DD-7740-8281-D4A8476498DF}"/>
+    <hyperlink ref="C145" r:id="rId84" xr:uid="{D4D3BD11-6490-B646-B302-20BFB3D7DF5F}"/>
+    <hyperlink ref="C146" r:id="rId85" xr:uid="{923B455F-766D-1245-B440-3E155C36EB08}"/>
+    <hyperlink ref="F146" r:id="rId86" xr:uid="{13585F3B-4D88-FD44-80C6-27534407E6B3}"/>
+    <hyperlink ref="C148" r:id="rId87" location="conference-publications" xr:uid="{1A804911-E79D-9141-A167-60595CEE1F71}"/>
+    <hyperlink ref="C149" r:id="rId88" xr:uid="{3D2271F2-C077-F646-9F3C-5EB7256C0CF2}"/>
+    <hyperlink ref="C169" r:id="rId89" xr:uid="{51A16F76-2C2A-6C41-8E1D-A56F68000383}"/>
+    <hyperlink ref="F170" r:id="rId90" display="No..?" xr:uid="{CFB38AB7-6FFD-7543-9665-38F4AF916308}"/>
+    <hyperlink ref="C172" r:id="rId91" xr:uid="{6E550245-9521-014D-B426-EDEBB6147E4A}"/>
     <hyperlink ref="C7" r:id="rId92" xr:uid="{E81A1570-9990-814E-A1D5-C6962C1806DF}"/>
     <hyperlink ref="C8" r:id="rId93" xr:uid="{D7C55900-5024-034A-80F6-B1670134D8A0}"/>
     <hyperlink ref="C9" r:id="rId94" xr:uid="{7A00C4FC-9BB4-A242-A1B2-00F729E0EA3E}"/>
     <hyperlink ref="F9" r:id="rId95" display="Little picky" xr:uid="{59CA0194-3E75-0C43-B43E-0C657B6C82D9}"/>
-    <hyperlink ref="F60" r:id="rId96" display="Yes..?" xr:uid="{CB8A4941-FC1A-754C-A7FD-599935DB3F31}"/>
-    <hyperlink ref="C60" r:id="rId97" location="publications" xr:uid="{8EFA9C06-FE89-7447-91CE-180A9ED16794}"/>
+    <hyperlink ref="F62" r:id="rId96" display="Yes..?" xr:uid="{CB8A4941-FC1A-754C-A7FD-599935DB3F31}"/>
+    <hyperlink ref="C62" r:id="rId97" location="publications" xr:uid="{8EFA9C06-FE89-7447-91CE-180A9ED16794}"/>
     <hyperlink ref="C2" r:id="rId98" xr:uid="{1855347E-1501-8D43-99C6-EDC1CFB4E3C1}"/>
     <hyperlink ref="C3" r:id="rId99" xr:uid="{E744FF8F-6454-894D-BD61-E9C957C07630}"/>
     <hyperlink ref="C4" r:id="rId100" xr:uid="{7BFC847F-6034-004A-AE72-78A60552C37F}"/>
-    <hyperlink ref="C132" r:id="rId101" xr:uid="{3CAB4899-21CA-0746-9AC4-6377AFF983C9}"/>
-    <hyperlink ref="F132" r:id="rId102" xr:uid="{03AA3462-3833-5642-8AD2-02DEA2EB7DBF}"/>
-    <hyperlink ref="C134" r:id="rId103" xr:uid="{0AFF4185-421E-A044-8B14-063F232DF23C}"/>
-    <hyperlink ref="C135" r:id="rId104" xr:uid="{29B84BC6-13E1-D044-A869-EB5134497CD6}"/>
-    <hyperlink ref="C131" r:id="rId105" xr:uid="{B013B9EF-FD6B-4A41-9F39-38433F1DCC01}"/>
-    <hyperlink ref="C136" r:id="rId106" location="publications" xr:uid="{5E9B8B5B-7402-A34B-99E6-3C227D4F15CC}"/>
-    <hyperlink ref="C100" r:id="rId107" xr:uid="{C0F1ADC4-2A51-C345-9349-4003E44424D3}"/>
-    <hyperlink ref="C101" r:id="rId108" xr:uid="{1DE714D0-AA68-304E-8CCC-E3DEACD98304}"/>
-    <hyperlink ref="C111" r:id="rId109" display="https://adaptive-robotics-lab.github.io/publications/" xr:uid="{E2444A72-A995-5841-989A-59F8AF15478C}"/>
-    <hyperlink ref="C112" r:id="rId110" xr:uid="{3FD7C805-92F3-A749-8523-B5D649B8F890}"/>
+    <hyperlink ref="C137" r:id="rId101" xr:uid="{3CAB4899-21CA-0746-9AC4-6377AFF983C9}"/>
+    <hyperlink ref="F137" r:id="rId102" xr:uid="{03AA3462-3833-5642-8AD2-02DEA2EB7DBF}"/>
+    <hyperlink ref="C139" r:id="rId103" xr:uid="{0AFF4185-421E-A044-8B14-063F232DF23C}"/>
+    <hyperlink ref="C140" r:id="rId104" xr:uid="{29B84BC6-13E1-D044-A869-EB5134497CD6}"/>
+    <hyperlink ref="C136" r:id="rId105" xr:uid="{B013B9EF-FD6B-4A41-9F39-38433F1DCC01}"/>
+    <hyperlink ref="C141" r:id="rId106" location="publications" xr:uid="{5E9B8B5B-7402-A34B-99E6-3C227D4F15CC}"/>
+    <hyperlink ref="C105" r:id="rId107" xr:uid="{C0F1ADC4-2A51-C345-9349-4003E44424D3}"/>
+    <hyperlink ref="C106" r:id="rId108" xr:uid="{1DE714D0-AA68-304E-8CCC-E3DEACD98304}"/>
+    <hyperlink ref="C116" r:id="rId109" display="https://adaptive-robotics-lab.github.io/publications/" xr:uid="{E2444A72-A995-5841-989A-59F8AF15478C}"/>
+    <hyperlink ref="C117" r:id="rId110" xr:uid="{3FD7C805-92F3-A749-8523-B5D649B8F890}"/>
     <hyperlink ref="C23" r:id="rId111" xr:uid="{40710B08-AA99-674E-A8D0-57AD1EC6F7F0}"/>
     <hyperlink ref="F23" r:id="rId112" xr:uid="{7723E8AA-A3DD-F942-9BD3-714A761F568E}"/>
-    <hyperlink ref="C37" r:id="rId113" xr:uid="{90C16231-A7FD-A64F-9A5A-23E4BF55CB78}"/>
-    <hyperlink ref="C38" r:id="rId114" xr:uid="{7D14C868-8C11-F341-893C-8FA380BE026F}"/>
+    <hyperlink ref="C39" r:id="rId113" xr:uid="{90C16231-A7FD-A64F-9A5A-23E4BF55CB78}"/>
+    <hyperlink ref="C40" r:id="rId114" xr:uid="{7D14C868-8C11-F341-893C-8FA380BE026F}"/>
     <hyperlink ref="C20" r:id="rId115" xr:uid="{69317078-8695-5A49-99D1-8B4E2BC4589E}"/>
     <hyperlink ref="F8" r:id="rId116" display="After Submission" xr:uid="{C41937AD-C8AA-6949-BD93-5A3AAC89257A}"/>
-    <hyperlink ref="C157" r:id="rId117" xr:uid="{949E7CA5-065E-0649-9348-614FE6505218}"/>
-    <hyperlink ref="F157" r:id="rId118" display="After Admission" xr:uid="{994371A4-342D-F348-B88E-265C6A27BF72}"/>
-    <hyperlink ref="C159" r:id="rId119" xr:uid="{05889E0F-3F97-D04C-9B20-AAD392054221}"/>
-    <hyperlink ref="C158" r:id="rId120" xr:uid="{33DBF5E1-B81D-2142-83D8-9C7A127864C4}"/>
+    <hyperlink ref="C162" r:id="rId117" xr:uid="{949E7CA5-065E-0649-9348-614FE6505218}"/>
+    <hyperlink ref="F162" r:id="rId118" display="After Admission" xr:uid="{994371A4-342D-F348-B88E-265C6A27BF72}"/>
+    <hyperlink ref="C164" r:id="rId119" xr:uid="{05889E0F-3F97-D04C-9B20-AAD392054221}"/>
+    <hyperlink ref="C163" r:id="rId120" xr:uid="{33DBF5E1-B81D-2142-83D8-9C7A127864C4}"/>
     <hyperlink ref="C18" r:id="rId121" xr:uid="{70A5B074-FE39-E04D-AFDE-543B180584E3}"/>
     <hyperlink ref="F18" r:id="rId122" display="No" xr:uid="{7DF036FC-9EA0-5E45-8FE0-AF7D834D24A5}"/>
     <hyperlink ref="C17" r:id="rId123" xr:uid="{CFCA4AD5-6D8E-CB44-A671-333BE022437B}"/>
@@ -6609,158 +6760,166 @@
     <hyperlink ref="C15" r:id="rId126" display="https://r-pad.github.io/publications/" xr:uid="{4DA529A4-12B5-7D4F-B712-E4D97CFDAEDB}"/>
     <hyperlink ref="C14" r:id="rId127" xr:uid="{B5109ACE-0258-1F44-836F-DF406D7A1D75}"/>
     <hyperlink ref="C13" r:id="rId128" xr:uid="{0A1707DB-8872-0648-B9E4-B8A0B8B1F90C}"/>
-    <hyperlink ref="C154" r:id="rId129" xr:uid="{5FFFB542-20CD-D44B-89B3-96A8A16DBC55}"/>
-    <hyperlink ref="C117" r:id="rId130" xr:uid="{CFA370B5-79A6-4A41-AF90-E9894E531D42}"/>
-    <hyperlink ref="F124" r:id="rId131" xr:uid="{EA5CBE3C-DFC3-374F-865A-D0252E2A2DCB}"/>
-    <hyperlink ref="C155" r:id="rId132" xr:uid="{735F21D3-12C3-8246-B974-D051B982625C}"/>
-    <hyperlink ref="C156" r:id="rId133" xr:uid="{4A5FEC95-F3F6-334E-9E89-0B03889995EB}"/>
-    <hyperlink ref="C53" r:id="rId134" xr:uid="{2EE01EE5-3A04-534B-BFE5-EAB18816D082}"/>
-    <hyperlink ref="F83" r:id="rId135" display="Not mentioned" xr:uid="{945FBC30-5CEB-424C-9D78-0B7E11F08E89}"/>
-    <hyperlink ref="F88" r:id="rId136" xr:uid="{8E501F13-5237-BB49-A5AD-C5F6AD88218F}"/>
-    <hyperlink ref="F87" r:id="rId137" location="contact" xr:uid="{3F0E09B4-19AF-3A48-85EA-7A7DC6686FB4}"/>
-    <hyperlink ref="C102" r:id="rId138" xr:uid="{E99926AE-00F4-AD41-9D8A-24CAB858B2FE}"/>
-    <hyperlink ref="F89" r:id="rId139" xr:uid="{AB30AB90-2D8C-FA4A-8E71-DA50CA4E22A7}"/>
-    <hyperlink ref="F94" r:id="rId140" xr:uid="{C1CFADFE-12B7-994A-B16E-3F6AD565E21B}"/>
-    <hyperlink ref="C50" r:id="rId141" xr:uid="{BE76FDC1-465C-4F4B-A40C-F4F0BA7AACC2}"/>
-    <hyperlink ref="C71" r:id="rId142" xr:uid="{6124BD60-DE89-E04A-B3F5-390F2315CBAA}"/>
-    <hyperlink ref="F71" r:id="rId143" location="join" xr:uid="{A750D1F5-A848-F743-8E23-3832B5596DCE}"/>
-    <hyperlink ref="F72" r:id="rId144" xr:uid="{26D2091C-C6A1-1E4F-A0F0-D71C15084E5A}"/>
+    <hyperlink ref="C159" r:id="rId129" xr:uid="{5FFFB542-20CD-D44B-89B3-96A8A16DBC55}"/>
+    <hyperlink ref="C122" r:id="rId130" xr:uid="{CFA370B5-79A6-4A41-AF90-E9894E531D42}"/>
+    <hyperlink ref="F129" r:id="rId131" xr:uid="{EA5CBE3C-DFC3-374F-865A-D0252E2A2DCB}"/>
+    <hyperlink ref="C160" r:id="rId132" xr:uid="{735F21D3-12C3-8246-B974-D051B982625C}"/>
+    <hyperlink ref="C161" r:id="rId133" xr:uid="{4A5FEC95-F3F6-334E-9E89-0B03889995EB}"/>
+    <hyperlink ref="C55" r:id="rId134" xr:uid="{2EE01EE5-3A04-534B-BFE5-EAB18816D082}"/>
+    <hyperlink ref="F88" r:id="rId135" display="Not mentioned" xr:uid="{945FBC30-5CEB-424C-9D78-0B7E11F08E89}"/>
+    <hyperlink ref="F93" r:id="rId136" xr:uid="{8E501F13-5237-BB49-A5AD-C5F6AD88218F}"/>
+    <hyperlink ref="F92" r:id="rId137" location="contact" xr:uid="{3F0E09B4-19AF-3A48-85EA-7A7DC6686FB4}"/>
+    <hyperlink ref="C107" r:id="rId138" xr:uid="{E99926AE-00F4-AD41-9D8A-24CAB858B2FE}"/>
+    <hyperlink ref="F94" r:id="rId139" xr:uid="{AB30AB90-2D8C-FA4A-8E71-DA50CA4E22A7}"/>
+    <hyperlink ref="F99" r:id="rId140" xr:uid="{C1CFADFE-12B7-994A-B16E-3F6AD565E21B}"/>
+    <hyperlink ref="C52" r:id="rId141" xr:uid="{BE76FDC1-465C-4F4B-A40C-F4F0BA7AACC2}"/>
+    <hyperlink ref="C73" r:id="rId142" xr:uid="{6124BD60-DE89-E04A-B3F5-390F2315CBAA}"/>
+    <hyperlink ref="F73" r:id="rId143" location="join" xr:uid="{A750D1F5-A848-F743-8E23-3832B5596DCE}"/>
+    <hyperlink ref="F77" r:id="rId144" xr:uid="{26D2091C-C6A1-1E4F-A0F0-D71C15084E5A}"/>
     <hyperlink ref="F13" r:id="rId145" xr:uid="{E99E2298-7017-A047-B3BD-4472343CDD0B}"/>
     <hyperlink ref="F16" r:id="rId146" xr:uid="{54121DDB-5B4A-024C-9715-F3B5F3D34B7D}"/>
     <hyperlink ref="F15" r:id="rId147" xr:uid="{B1E5435C-6261-F94A-AB9E-18E85110B5F9}"/>
     <hyperlink ref="F17" r:id="rId148" xr:uid="{51B6C597-6715-A547-A972-7D01EB1DFD3A}"/>
     <hyperlink ref="F20" r:id="rId149" xr:uid="{F951ECEC-1BEF-D543-A034-9B5EB7CACF17}"/>
-    <hyperlink ref="F158" r:id="rId150" xr:uid="{C958B7E0-4842-F241-A83E-6A2D49C1F1BF}"/>
-    <hyperlink ref="F159" r:id="rId151" xr:uid="{E17F42DF-7DFF-224E-94B1-67029A85337E}"/>
-    <hyperlink ref="F102" r:id="rId152" xr:uid="{5011C913-565B-C94C-8151-F93A1234C732}"/>
-    <hyperlink ref="F103" r:id="rId153" xr:uid="{9560BA90-E86C-5F4C-B19C-112CCBE2DE66}"/>
-    <hyperlink ref="F104" r:id="rId154" display="Yes" xr:uid="{27135B7B-7AD5-D345-AFCC-E2140680F4C3}"/>
-    <hyperlink ref="F119" r:id="rId155" xr:uid="{B45135B3-2794-FB4A-AB7C-BD309B78A26A}"/>
-    <hyperlink ref="C122" r:id="rId156" display="https://scholar.google.com/citations?hl=en&amp;user=g9bV-_sAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{4F6AE197-5746-404B-8769-4EE7E276C903}"/>
-    <hyperlink ref="C121" r:id="rId157" xr:uid="{1F444EB0-204F-7C49-A6CC-703D102B53BF}"/>
-    <hyperlink ref="F121" r:id="rId158" xr:uid="{64D5B3CB-331B-3448-B9BD-7128151E70CD}"/>
-    <hyperlink ref="F122" r:id="rId159" xr:uid="{BE30AA51-3EBF-954D-8B74-233C8AE3B7CB}"/>
-    <hyperlink ref="A113" r:id="rId160" display="Saurabh Gupta" xr:uid="{97643B95-EFA8-1140-AB11-805B406DB3DD}"/>
-    <hyperlink ref="C113" r:id="rId161" xr:uid="{D5A6EDD9-7B0A-DF48-BAAF-F75C4255559D}"/>
-    <hyperlink ref="F113" r:id="rId162" xr:uid="{2E2B510D-51C4-F141-AA3F-5E508EA52EBE}"/>
-    <hyperlink ref="F131" r:id="rId163" xr:uid="{F4275B35-6C02-384F-B465-2B40F9902EA5}"/>
-    <hyperlink ref="F134" r:id="rId164" xr:uid="{2F527CCC-CE9E-C543-BCF3-9B1B1B430985}"/>
-    <hyperlink ref="F135" r:id="rId165" xr:uid="{1FDD1B1F-2127-424B-88C6-DF5433C40969}"/>
-    <hyperlink ref="F136" r:id="rId166" location="contact" xr:uid="{994856F7-7861-B348-B765-4A7A4EB58B2D}"/>
-    <hyperlink ref="F37" r:id="rId167" xr:uid="{129EBEC2-9896-CA4A-AA98-A1AABC252688}"/>
-    <hyperlink ref="F38" r:id="rId168" xr:uid="{7099098B-9801-324A-9F12-C1DDE138B9EF}"/>
-    <hyperlink ref="F138" r:id="rId169" xr:uid="{9CD28BF9-1DFB-6C49-9CDF-BC08937EE939}"/>
-    <hyperlink ref="F139" r:id="rId170" xr:uid="{CC4F20FD-36B4-FA4B-8A4A-6A5B989C6573}"/>
-    <hyperlink ref="F140" r:id="rId171" xr:uid="{B18B63C2-1FD2-564D-91AD-DF48E52B84B4}"/>
-    <hyperlink ref="F143" r:id="rId172" xr:uid="{B95E39AC-29F4-C749-A281-DAE1BA48DAB7}"/>
-    <hyperlink ref="F164" r:id="rId173" xr:uid="{18AEE6CC-8D1E-2E46-B870-68ED2D0832B5}"/>
-    <hyperlink ref="F167" r:id="rId174" xr:uid="{0FF872C9-2AD5-074E-93E4-55865CE4A81A}"/>
+    <hyperlink ref="F163" r:id="rId150" xr:uid="{C958B7E0-4842-F241-A83E-6A2D49C1F1BF}"/>
+    <hyperlink ref="F164" r:id="rId151" xr:uid="{E17F42DF-7DFF-224E-94B1-67029A85337E}"/>
+    <hyperlink ref="F107" r:id="rId152" xr:uid="{5011C913-565B-C94C-8151-F93A1234C732}"/>
+    <hyperlink ref="F108" r:id="rId153" xr:uid="{9560BA90-E86C-5F4C-B19C-112CCBE2DE66}"/>
+    <hyperlink ref="F109" r:id="rId154" display="Yes" xr:uid="{27135B7B-7AD5-D345-AFCC-E2140680F4C3}"/>
+    <hyperlink ref="F124" r:id="rId155" xr:uid="{B45135B3-2794-FB4A-AB7C-BD309B78A26A}"/>
+    <hyperlink ref="C127" r:id="rId156" display="https://scholar.google.com/citations?hl=en&amp;user=g9bV-_sAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{4F6AE197-5746-404B-8769-4EE7E276C903}"/>
+    <hyperlink ref="C126" r:id="rId157" xr:uid="{1F444EB0-204F-7C49-A6CC-703D102B53BF}"/>
+    <hyperlink ref="F126" r:id="rId158" xr:uid="{64D5B3CB-331B-3448-B9BD-7128151E70CD}"/>
+    <hyperlink ref="F127" r:id="rId159" xr:uid="{BE30AA51-3EBF-954D-8B74-233C8AE3B7CB}"/>
+    <hyperlink ref="A118" r:id="rId160" display="Saurabh Gupta" xr:uid="{97643B95-EFA8-1140-AB11-805B406DB3DD}"/>
+    <hyperlink ref="C118" r:id="rId161" xr:uid="{D5A6EDD9-7B0A-DF48-BAAF-F75C4255559D}"/>
+    <hyperlink ref="F118" r:id="rId162" xr:uid="{2E2B510D-51C4-F141-AA3F-5E508EA52EBE}"/>
+    <hyperlink ref="F136" r:id="rId163" xr:uid="{F4275B35-6C02-384F-B465-2B40F9902EA5}"/>
+    <hyperlink ref="F139" r:id="rId164" xr:uid="{2F527CCC-CE9E-C543-BCF3-9B1B1B430985}"/>
+    <hyperlink ref="F140" r:id="rId165" xr:uid="{1FDD1B1F-2127-424B-88C6-DF5433C40969}"/>
+    <hyperlink ref="F141" r:id="rId166" location="contact" xr:uid="{994856F7-7861-B348-B765-4A7A4EB58B2D}"/>
+    <hyperlink ref="F39" r:id="rId167" xr:uid="{129EBEC2-9896-CA4A-AA98-A1AABC252688}"/>
+    <hyperlink ref="F40" r:id="rId168" xr:uid="{7099098B-9801-324A-9F12-C1DDE138B9EF}"/>
+    <hyperlink ref="F143" r:id="rId169" xr:uid="{9CD28BF9-1DFB-6C49-9CDF-BC08937EE939}"/>
+    <hyperlink ref="F144" r:id="rId170" xr:uid="{CC4F20FD-36B4-FA4B-8A4A-6A5B989C6573}"/>
+    <hyperlink ref="F145" r:id="rId171" xr:uid="{B18B63C2-1FD2-564D-91AD-DF48E52B84B4}"/>
+    <hyperlink ref="F148" r:id="rId172" xr:uid="{B95E39AC-29F4-C749-A281-DAE1BA48DAB7}"/>
+    <hyperlink ref="F169" r:id="rId173" xr:uid="{18AEE6CC-8D1E-2E46-B870-68ED2D0832B5}"/>
+    <hyperlink ref="F172" r:id="rId174" xr:uid="{0FF872C9-2AD5-074E-93E4-55865CE4A81A}"/>
     <hyperlink ref="F7" r:id="rId175" xr:uid="{4EC9CF74-9C72-B045-893B-C3456A860A92}"/>
     <hyperlink ref="F2" r:id="rId176" location="contact" xr:uid="{C8215F07-1913-394E-A17D-CEA30B1C30C2}"/>
     <hyperlink ref="F3" r:id="rId177" xr:uid="{5FF07C5B-E6B2-D745-B6A1-001FCB6CF8AB}"/>
     <hyperlink ref="F4" r:id="rId178" xr:uid="{C267F854-4600-C949-BB34-3C61ADA7D51A}"/>
-    <hyperlink ref="F100" r:id="rId179" xr:uid="{FC2865FB-7FF7-6D49-9A82-9D1E512981D9}"/>
-    <hyperlink ref="F101" r:id="rId180" xr:uid="{2B3F3304-CE72-E048-AEA1-908D2AC74C41}"/>
-    <hyperlink ref="F111" r:id="rId181" xr:uid="{12826E40-D942-D644-984A-09E0983C2BF1}"/>
-    <hyperlink ref="F112" r:id="rId182" xr:uid="{0F348FD7-AD57-8243-8D22-13815A1AEE73}"/>
-    <hyperlink ref="F154" r:id="rId183" xr:uid="{769BF1AD-B98A-844E-9E8F-6E2F030E8FFD}"/>
-    <hyperlink ref="F117" r:id="rId184" xr:uid="{89472F04-5E91-D540-95CC-42F3C6631B21}"/>
-    <hyperlink ref="F155" r:id="rId185" xr:uid="{E84DFB70-6A83-FB48-BE73-EF22E66C660B}"/>
-    <hyperlink ref="F156" r:id="rId186" xr:uid="{E38E8E60-9D8D-4344-A9B8-EF8E11166022}"/>
-    <hyperlink ref="F53" r:id="rId187" location="contact" xr:uid="{2A7486D0-C44F-EA47-9CF0-583B629E3B6A}"/>
-    <hyperlink ref="C95" r:id="rId188" xr:uid="{D884EE9B-5EB4-A640-A5D1-664B23E3D668}"/>
-    <hyperlink ref="F95" r:id="rId189" xr:uid="{A8BDAE9A-3D13-B447-B08B-9F1E06C4F226}"/>
-    <hyperlink ref="C125" r:id="rId190" xr:uid="{944E2B70-7ED0-0B48-A661-183172C34786}"/>
-    <hyperlink ref="C126" r:id="rId191" xr:uid="{E1D81CAD-2789-A744-BF00-C20B0D4F3371}"/>
-    <hyperlink ref="C127" r:id="rId192" xr:uid="{E0F82B46-BE27-944C-9FF4-60500F713D4D}"/>
-    <hyperlink ref="C133" r:id="rId193" xr:uid="{174C16F0-EC22-1447-856B-6DCD32D98D97}"/>
-    <hyperlink ref="F133" r:id="rId194" xr:uid="{52730D5B-CD37-A042-8617-3B0E0E4D3AF3}"/>
-    <hyperlink ref="C39" r:id="rId195" xr:uid="{B1C6C311-A9D3-064B-9792-2FDC9A4ECB08}"/>
-    <hyperlink ref="C40" r:id="rId196" xr:uid="{254AE5FA-D2D2-A740-9F75-CB61B079791D}"/>
-    <hyperlink ref="C41" r:id="rId197" xr:uid="{A7D4BFDA-D594-8D46-A990-6979B96FD9CA}"/>
-    <hyperlink ref="C124" r:id="rId198" xr:uid="{ABC72816-BD2A-0B41-852C-A1EBC5A6508E}"/>
-    <hyperlink ref="C42" r:id="rId199" xr:uid="{134E9A26-ED28-B447-A20D-0D611DD17CA4}"/>
-    <hyperlink ref="C43" r:id="rId200" xr:uid="{D7045999-7E75-C44B-BFC5-4FC81E231AA0}"/>
-    <hyperlink ref="C44" r:id="rId201" xr:uid="{492CFA21-EE5B-3049-886B-26E7E6E9CBE1}"/>
-    <hyperlink ref="C45" r:id="rId202" display="https://scholar.google.com/citations?hl=en&amp;user=Y1xCzE0AAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{43615B61-C773-6640-BE45-507F9C490663}"/>
-    <hyperlink ref="B46" r:id="rId203" xr:uid="{F9347A3E-EC5D-CA49-905D-E9EA3C2938BA}"/>
-    <hyperlink ref="D46" r:id="rId204" xr:uid="{F879BE0A-0EEF-C84E-AD10-5A1CD418A99F}"/>
-    <hyperlink ref="C55" r:id="rId205" xr:uid="{6FF87D8D-06C4-1B44-BF26-49DE63E95D97}"/>
-    <hyperlink ref="C56" r:id="rId206" xr:uid="{85F1FB79-9A0A-3248-9933-B924D6237F4E}"/>
-    <hyperlink ref="C54" r:id="rId207" xr:uid="{25497B39-3697-9644-BD65-EF06C07D18C3}"/>
-    <hyperlink ref="C58" r:id="rId208" xr:uid="{CCF2F5E7-03A8-0345-899D-E326F21815FF}"/>
-    <hyperlink ref="C57" r:id="rId209" xr:uid="{43EFD672-8D47-C44D-83DC-4010226BF9E7}"/>
-    <hyperlink ref="C59" r:id="rId210" xr:uid="{D3DD8597-D143-7C49-8809-5429C1C0276E}"/>
-    <hyperlink ref="C116" r:id="rId211" xr:uid="{C3A24C58-E761-104A-813A-99BF22DE9650}"/>
-    <hyperlink ref="C105" r:id="rId212" xr:uid="{CF2BB5BE-A36B-4242-848A-323A52FAA6CC}"/>
-    <hyperlink ref="C106" r:id="rId213" xr:uid="{88F5B5FD-3889-9144-B1F5-833971BFBB5F}"/>
-    <hyperlink ref="C149" r:id="rId214" xr:uid="{6DD86311-42F6-8842-82F1-2CB147553528}"/>
-    <hyperlink ref="C150" r:id="rId215" xr:uid="{ABB3121C-D2DE-0B46-B23F-AFA3618994E9}"/>
-    <hyperlink ref="C115" r:id="rId216" xr:uid="{92B13E7A-EB66-444B-A54F-A654933B463E}"/>
-    <hyperlink ref="C82" r:id="rId217" xr:uid="{D3135F62-3A25-3F43-944F-4C954582D549}"/>
-    <hyperlink ref="C151" r:id="rId218" display="https://scholar.google.com/citations?hl=en&amp;user=Zks0hIUAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{B2E8D4E2-52D5-174E-B712-A914360AEEA6}"/>
-    <hyperlink ref="C152" r:id="rId219" xr:uid="{C888B173-7216-064C-9201-46C2F6C225BD}"/>
-    <hyperlink ref="C153" r:id="rId220" xr:uid="{6C80741A-C0A3-254E-8E5B-224B12615E8E}"/>
-    <hyperlink ref="C165" r:id="rId221" display="https://tealab.ai/publications/" xr:uid="{4C95FEB9-D796-854D-AE2B-9FD7F4E06985}"/>
-    <hyperlink ref="F82" r:id="rId222" xr:uid="{8AA04E82-3F9F-F041-8901-8156D3FC3B58}"/>
-    <hyperlink ref="C75" r:id="rId223" xr:uid="{71818168-992F-4C47-B82D-1BE825D5906F}"/>
-    <hyperlink ref="C76" r:id="rId224" xr:uid="{4EE6B58F-716C-EF4D-9E3B-E614F44E6489}"/>
-    <hyperlink ref="C77" r:id="rId225" xr:uid="{BCD79DA4-CA2C-7F46-9DC0-F680659819FC}"/>
-    <hyperlink ref="C78" r:id="rId226" xr:uid="{39DFA628-E2DD-F741-9C67-3041D4F6A369}"/>
-    <hyperlink ref="F75" r:id="rId227" xr:uid="{CC3D3B51-95D4-534B-8E3C-25DC87E5CE90}"/>
-    <hyperlink ref="F76" r:id="rId228" xr:uid="{84A9E8BE-849D-D34D-900A-5408A960575E}"/>
-    <hyperlink ref="F78" r:id="rId229" xr:uid="{73F1F837-90C9-624B-ABC5-0CF9A5F9D337}"/>
+    <hyperlink ref="F105" r:id="rId179" xr:uid="{FC2865FB-7FF7-6D49-9A82-9D1E512981D9}"/>
+    <hyperlink ref="F106" r:id="rId180" xr:uid="{2B3F3304-CE72-E048-AEA1-908D2AC74C41}"/>
+    <hyperlink ref="F116" r:id="rId181" xr:uid="{12826E40-D942-D644-984A-09E0983C2BF1}"/>
+    <hyperlink ref="F117" r:id="rId182" xr:uid="{0F348FD7-AD57-8243-8D22-13815A1AEE73}"/>
+    <hyperlink ref="F159" r:id="rId183" xr:uid="{769BF1AD-B98A-844E-9E8F-6E2F030E8FFD}"/>
+    <hyperlink ref="F122" r:id="rId184" xr:uid="{89472F04-5E91-D540-95CC-42F3C6631B21}"/>
+    <hyperlink ref="F160" r:id="rId185" xr:uid="{E84DFB70-6A83-FB48-BE73-EF22E66C660B}"/>
+    <hyperlink ref="F161" r:id="rId186" xr:uid="{E38E8E60-9D8D-4344-A9B8-EF8E11166022}"/>
+    <hyperlink ref="F55" r:id="rId187" location="contact" xr:uid="{2A7486D0-C44F-EA47-9CF0-583B629E3B6A}"/>
+    <hyperlink ref="C100" r:id="rId188" xr:uid="{D884EE9B-5EB4-A640-A5D1-664B23E3D668}"/>
+    <hyperlink ref="F100" r:id="rId189" xr:uid="{A8BDAE9A-3D13-B447-B08B-9F1E06C4F226}"/>
+    <hyperlink ref="C130" r:id="rId190" xr:uid="{944E2B70-7ED0-0B48-A661-183172C34786}"/>
+    <hyperlink ref="C131" r:id="rId191" xr:uid="{E1D81CAD-2789-A744-BF00-C20B0D4F3371}"/>
+    <hyperlink ref="C132" r:id="rId192" xr:uid="{E0F82B46-BE27-944C-9FF4-60500F713D4D}"/>
+    <hyperlink ref="C138" r:id="rId193" xr:uid="{174C16F0-EC22-1447-856B-6DCD32D98D97}"/>
+    <hyperlink ref="F138" r:id="rId194" xr:uid="{52730D5B-CD37-A042-8617-3B0E0E4D3AF3}"/>
+    <hyperlink ref="C41" r:id="rId195" xr:uid="{B1C6C311-A9D3-064B-9792-2FDC9A4ECB08}"/>
+    <hyperlink ref="C42" r:id="rId196" xr:uid="{254AE5FA-D2D2-A740-9F75-CB61B079791D}"/>
+    <hyperlink ref="C43" r:id="rId197" xr:uid="{A7D4BFDA-D594-8D46-A990-6979B96FD9CA}"/>
+    <hyperlink ref="C129" r:id="rId198" xr:uid="{ABC72816-BD2A-0B41-852C-A1EBC5A6508E}"/>
+    <hyperlink ref="C44" r:id="rId199" xr:uid="{134E9A26-ED28-B447-A20D-0D611DD17CA4}"/>
+    <hyperlink ref="C45" r:id="rId200" xr:uid="{D7045999-7E75-C44B-BFC5-4FC81E231AA0}"/>
+    <hyperlink ref="C46" r:id="rId201" xr:uid="{492CFA21-EE5B-3049-886B-26E7E6E9CBE1}"/>
+    <hyperlink ref="C47" r:id="rId202" display="https://scholar.google.com/citations?hl=en&amp;user=Y1xCzE0AAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{43615B61-C773-6640-BE45-507F9C490663}"/>
+    <hyperlink ref="B48" r:id="rId203" xr:uid="{F9347A3E-EC5D-CA49-905D-E9EA3C2938BA}"/>
+    <hyperlink ref="D48" r:id="rId204" xr:uid="{F879BE0A-0EEF-C84E-AD10-5A1CD418A99F}"/>
+    <hyperlink ref="C57" r:id="rId205" xr:uid="{6FF87D8D-06C4-1B44-BF26-49DE63E95D97}"/>
+    <hyperlink ref="C58" r:id="rId206" xr:uid="{85F1FB79-9A0A-3248-9933-B924D6237F4E}"/>
+    <hyperlink ref="C56" r:id="rId207" xr:uid="{25497B39-3697-9644-BD65-EF06C07D18C3}"/>
+    <hyperlink ref="C60" r:id="rId208" xr:uid="{CCF2F5E7-03A8-0345-899D-E326F21815FF}"/>
+    <hyperlink ref="C59" r:id="rId209" xr:uid="{43EFD672-8D47-C44D-83DC-4010226BF9E7}"/>
+    <hyperlink ref="C61" r:id="rId210" xr:uid="{D3DD8597-D143-7C49-8809-5429C1C0276E}"/>
+    <hyperlink ref="C121" r:id="rId211" xr:uid="{C3A24C58-E761-104A-813A-99BF22DE9650}"/>
+    <hyperlink ref="C110" r:id="rId212" xr:uid="{CF2BB5BE-A36B-4242-848A-323A52FAA6CC}"/>
+    <hyperlink ref="C111" r:id="rId213" xr:uid="{88F5B5FD-3889-9144-B1F5-833971BFBB5F}"/>
+    <hyperlink ref="C154" r:id="rId214" xr:uid="{6DD86311-42F6-8842-82F1-2CB147553528}"/>
+    <hyperlink ref="C155" r:id="rId215" xr:uid="{ABB3121C-D2DE-0B46-B23F-AFA3618994E9}"/>
+    <hyperlink ref="C120" r:id="rId216" xr:uid="{92B13E7A-EB66-444B-A54F-A654933B463E}"/>
+    <hyperlink ref="C87" r:id="rId217" xr:uid="{D3135F62-3A25-3F43-944F-4C954582D549}"/>
+    <hyperlink ref="C156" r:id="rId218" display="https://scholar.google.com/citations?hl=en&amp;user=Zks0hIUAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{B2E8D4E2-52D5-174E-B712-A914360AEEA6}"/>
+    <hyperlink ref="C157" r:id="rId219" xr:uid="{C888B173-7216-064C-9201-46C2F6C225BD}"/>
+    <hyperlink ref="C158" r:id="rId220" xr:uid="{6C80741A-C0A3-254E-8E5B-224B12615E8E}"/>
+    <hyperlink ref="C170" r:id="rId221" display="https://tealab.ai/publications/" xr:uid="{4C95FEB9-D796-854D-AE2B-9FD7F4E06985}"/>
+    <hyperlink ref="F87" r:id="rId222" xr:uid="{8AA04E82-3F9F-F041-8901-8156D3FC3B58}"/>
+    <hyperlink ref="C80" r:id="rId223" xr:uid="{71818168-992F-4C47-B82D-1BE825D5906F}"/>
+    <hyperlink ref="C81" r:id="rId224" xr:uid="{4EE6B58F-716C-EF4D-9E3B-E614F44E6489}"/>
+    <hyperlink ref="C82" r:id="rId225" xr:uid="{BCD79DA4-CA2C-7F46-9DC0-F680659819FC}"/>
+    <hyperlink ref="C83" r:id="rId226" xr:uid="{39DFA628-E2DD-F741-9C67-3041D4F6A369}"/>
+    <hyperlink ref="F80" r:id="rId227" xr:uid="{CC3D3B51-95D4-534B-8E3C-25DC87E5CE90}"/>
+    <hyperlink ref="F81" r:id="rId228" xr:uid="{84A9E8BE-849D-D34D-900A-5408A960575E}"/>
+    <hyperlink ref="F83" r:id="rId229" xr:uid="{73F1F837-90C9-624B-ABC5-0CF9A5F9D337}"/>
     <hyperlink ref="C28" r:id="rId230" xr:uid="{C236BEFD-4050-0C44-8B4F-23DAE594504E}"/>
     <hyperlink ref="C29" r:id="rId231" xr:uid="{89B5A370-66BA-9C4E-B86A-743111C8DE59}"/>
     <hyperlink ref="C30" r:id="rId232" xr:uid="{5B2489EE-3E33-9F41-9D9E-895A61905B9A}"/>
     <hyperlink ref="C31" r:id="rId233" xr:uid="{E7027968-182C-CB4E-930B-8BAC0A346045}"/>
     <hyperlink ref="C32" r:id="rId234" xr:uid="{487D7215-D974-BA42-92C1-0498D0277D31}"/>
     <hyperlink ref="F32" r:id="rId235" xr:uid="{D26F82DC-8D68-9442-9302-E628012B0C73}"/>
-    <hyperlink ref="F115" r:id="rId236" xr:uid="{A390F5B1-319E-E748-97A0-6D6FBF47A30E}"/>
+    <hyperlink ref="F120" r:id="rId236" xr:uid="{A390F5B1-319E-E748-97A0-6D6FBF47A30E}"/>
     <hyperlink ref="C24" r:id="rId237" xr:uid="{53B4FB06-E5DE-534E-ACE5-084D67950043}"/>
     <hyperlink ref="C25" r:id="rId238" xr:uid="{2F2F32F1-9776-BB43-8570-8101CC7FB213}"/>
-    <hyperlink ref="C160" r:id="rId239" xr:uid="{59BC2097-3FAD-5747-A748-81ABD73B9F44}"/>
-    <hyperlink ref="C161" r:id="rId240" xr:uid="{818CDE33-50F2-1E49-9C0A-64D3A5B77FC3}"/>
-    <hyperlink ref="C162" r:id="rId241" xr:uid="{EE28EAAA-7648-A84C-99C5-37358456D485}"/>
-    <hyperlink ref="C163" r:id="rId242" xr:uid="{79CEC276-241F-2748-8511-62D73F50A3D4}"/>
-    <hyperlink ref="C108" r:id="rId243" xr:uid="{0C6AFE75-5E41-0542-BDFF-9D5592AA51CA}"/>
-    <hyperlink ref="C109" r:id="rId244" xr:uid="{60396B5E-95D4-E54F-B715-25464BE39AE2}"/>
-    <hyperlink ref="C110" r:id="rId245" xr:uid="{81D8DBCC-FE1A-7A4B-814B-446960FD626C}"/>
-    <hyperlink ref="F93" r:id="rId246" xr:uid="{8E096469-0271-654F-94AC-F8B981BCEDC4}"/>
-    <hyperlink ref="C142" r:id="rId247" xr:uid="{9DA2478C-B101-A14E-93DD-979724A72066}"/>
-    <hyperlink ref="F144" r:id="rId248" xr:uid="{0B5F14D2-A771-9848-AEF4-6A1E06E7BE0C}"/>
-    <hyperlink ref="F142" r:id="rId249" xr:uid="{D3F0AEBB-B0D1-CE44-9BF6-8679AC3988A4}"/>
+    <hyperlink ref="C165" r:id="rId239" xr:uid="{59BC2097-3FAD-5747-A748-81ABD73B9F44}"/>
+    <hyperlink ref="C166" r:id="rId240" xr:uid="{818CDE33-50F2-1E49-9C0A-64D3A5B77FC3}"/>
+    <hyperlink ref="C167" r:id="rId241" xr:uid="{EE28EAAA-7648-A84C-99C5-37358456D485}"/>
+    <hyperlink ref="C168" r:id="rId242" xr:uid="{79CEC276-241F-2748-8511-62D73F50A3D4}"/>
+    <hyperlink ref="C113" r:id="rId243" xr:uid="{0C6AFE75-5E41-0542-BDFF-9D5592AA51CA}"/>
+    <hyperlink ref="C114" r:id="rId244" xr:uid="{60396B5E-95D4-E54F-B715-25464BE39AE2}"/>
+    <hyperlink ref="C115" r:id="rId245" xr:uid="{81D8DBCC-FE1A-7A4B-814B-446960FD626C}"/>
+    <hyperlink ref="F98" r:id="rId246" xr:uid="{8E096469-0271-654F-94AC-F8B981BCEDC4}"/>
+    <hyperlink ref="C147" r:id="rId247" xr:uid="{9DA2478C-B101-A14E-93DD-979724A72066}"/>
+    <hyperlink ref="F149" r:id="rId248" xr:uid="{0B5F14D2-A771-9848-AEF4-6A1E06E7BE0C}"/>
+    <hyperlink ref="F147" r:id="rId249" xr:uid="{D3F0AEBB-B0D1-CE44-9BF6-8679AC3988A4}"/>
     <hyperlink ref="F5" r:id="rId250" xr:uid="{0CC56FC3-9211-5D4C-9994-E001A3DDD4C4}"/>
     <hyperlink ref="C5" r:id="rId251" xr:uid="{EB46886A-11BC-A142-9201-BCC273AEFB45}"/>
     <hyperlink ref="F6" r:id="rId252" xr:uid="{42EB0C14-6491-454C-9816-054D0FCA8AF6}"/>
     <hyperlink ref="C6" r:id="rId253" xr:uid="{C56108EF-77E0-6649-A3E2-C3516D24A43D}"/>
-    <hyperlink ref="F63" r:id="rId254" xr:uid="{E3C45527-B881-C945-A858-C3D43CEA521B}"/>
-    <hyperlink ref="C63" r:id="rId255" xr:uid="{BCE33E6A-EEC6-6045-BD23-AC35FFE9F450}"/>
-    <hyperlink ref="C64" r:id="rId256" xr:uid="{4F7C4ECA-F59A-1A44-84C9-308C34EC9CE6}"/>
-    <hyperlink ref="F64" r:id="rId257" xr:uid="{E3055903-13F9-D44C-A38D-DFE63300E29A}"/>
-    <hyperlink ref="F65" r:id="rId258" xr:uid="{157FC4AD-3D42-2B40-A115-243F94F80A52}"/>
-    <hyperlink ref="C65" r:id="rId259" xr:uid="{C71D7CBA-5902-C348-B0ED-272BF02B77D1}"/>
-    <hyperlink ref="C66" r:id="rId260" xr:uid="{F6894A5B-40B3-A141-A186-38B94C911585}"/>
-    <hyperlink ref="F67" r:id="rId261" xr:uid="{0606F726-8C2E-374D-B0B0-71F6F38B02F7}"/>
-    <hyperlink ref="C67" r:id="rId262" xr:uid="{711E4927-9843-1048-BCF4-322958D04C50}"/>
-    <hyperlink ref="F68" r:id="rId263" xr:uid="{1AD4C701-5EF2-AD4E-8E72-8A6951AAD18B}"/>
-    <hyperlink ref="C68" r:id="rId264" xr:uid="{10FC8ADC-C42A-9B41-8E5E-09FBEC94ECC0}"/>
-    <hyperlink ref="C81" r:id="rId265" display="https://scholar.google.com/citations?user=eF5vfBAAAAAJ&amp;hl=en" xr:uid="{85984968-1F36-7D41-9950-B6DD1A527558}"/>
-    <hyperlink ref="F81" r:id="rId266" xr:uid="{91DBA4A3-B48C-EF4E-AD32-E1C86BB8426D}"/>
-    <hyperlink ref="C80" r:id="rId267" xr:uid="{FE3D74B6-ED0D-F34B-B177-F3130A660063}"/>
-    <hyperlink ref="C79" r:id="rId268" xr:uid="{BF354B3A-6E56-A848-84A4-C4F9C93A54ED}"/>
-    <hyperlink ref="F79" r:id="rId269" xr:uid="{F71F4573-174A-4149-82E5-7C239855A270}"/>
-    <hyperlink ref="F84" r:id="rId270" xr:uid="{2E03E2DB-5FB6-2A4F-84E0-3AF3C60AC0A1}"/>
-    <hyperlink ref="F168" r:id="rId271" xr:uid="{DF0B6B65-A748-1F45-88AB-C9035E97B11B}"/>
-    <hyperlink ref="C168" r:id="rId272" xr:uid="{FCB3030C-AD60-6346-A0D7-E470FD70E4E7}"/>
-    <hyperlink ref="C169" r:id="rId273" xr:uid="{9E5CE605-3386-0840-ACFA-2A2D09DB9D1B}"/>
-    <hyperlink ref="F170" r:id="rId274" xr:uid="{8E15B1CD-1528-2243-B09F-23DCDFEFED57}"/>
-    <hyperlink ref="C170" r:id="rId275" xr:uid="{57788FCB-5B1B-1C45-AE73-DD84C667625D}"/>
-    <hyperlink ref="F171" r:id="rId276" display="send CV" xr:uid="{707AE07C-5262-BC4D-9265-6EC0ED3CFCF6}"/>
-    <hyperlink ref="C171" r:id="rId277" xr:uid="{438ECEE0-7A39-284A-8F4B-C6F391DFF9A8}"/>
-    <hyperlink ref="F169" r:id="rId278" xr:uid="{E68B122E-F14A-A24B-A499-AE91A7682F39}"/>
-    <hyperlink ref="F172" r:id="rId279" xr:uid="{8A081B22-2061-F946-9B77-5847925A3209}"/>
-    <hyperlink ref="C172" r:id="rId280" xr:uid="{38E64B0E-B235-ED43-B078-7D53B4306871}"/>
+    <hyperlink ref="F65" r:id="rId254" xr:uid="{E3C45527-B881-C945-A858-C3D43CEA521B}"/>
+    <hyperlink ref="C65" r:id="rId255" xr:uid="{BCE33E6A-EEC6-6045-BD23-AC35FFE9F450}"/>
+    <hyperlink ref="C66" r:id="rId256" xr:uid="{4F7C4ECA-F59A-1A44-84C9-308C34EC9CE6}"/>
+    <hyperlink ref="F66" r:id="rId257" xr:uid="{E3055903-13F9-D44C-A38D-DFE63300E29A}"/>
+    <hyperlink ref="F67" r:id="rId258" xr:uid="{157FC4AD-3D42-2B40-A115-243F94F80A52}"/>
+    <hyperlink ref="C67" r:id="rId259" xr:uid="{C71D7CBA-5902-C348-B0ED-272BF02B77D1}"/>
+    <hyperlink ref="C68" r:id="rId260" xr:uid="{F6894A5B-40B3-A141-A186-38B94C911585}"/>
+    <hyperlink ref="F69" r:id="rId261" xr:uid="{0606F726-8C2E-374D-B0B0-71F6F38B02F7}"/>
+    <hyperlink ref="C69" r:id="rId262" xr:uid="{711E4927-9843-1048-BCF4-322958D04C50}"/>
+    <hyperlink ref="F70" r:id="rId263" xr:uid="{1AD4C701-5EF2-AD4E-8E72-8A6951AAD18B}"/>
+    <hyperlink ref="C70" r:id="rId264" xr:uid="{10FC8ADC-C42A-9B41-8E5E-09FBEC94ECC0}"/>
+    <hyperlink ref="C86" r:id="rId265" display="https://scholar.google.com/citations?user=eF5vfBAAAAAJ&amp;hl=en" xr:uid="{85984968-1F36-7D41-9950-B6DD1A527558}"/>
+    <hyperlink ref="F86" r:id="rId266" xr:uid="{91DBA4A3-B48C-EF4E-AD32-E1C86BB8426D}"/>
+    <hyperlink ref="C85" r:id="rId267" xr:uid="{FE3D74B6-ED0D-F34B-B177-F3130A660063}"/>
+    <hyperlink ref="C84" r:id="rId268" xr:uid="{BF354B3A-6E56-A848-84A4-C4F9C93A54ED}"/>
+    <hyperlink ref="F84" r:id="rId269" xr:uid="{F71F4573-174A-4149-82E5-7C239855A270}"/>
+    <hyperlink ref="F89" r:id="rId270" xr:uid="{2E03E2DB-5FB6-2A4F-84E0-3AF3C60AC0A1}"/>
+    <hyperlink ref="F173" r:id="rId271" xr:uid="{DF0B6B65-A748-1F45-88AB-C9035E97B11B}"/>
+    <hyperlink ref="C173" r:id="rId272" xr:uid="{FCB3030C-AD60-6346-A0D7-E470FD70E4E7}"/>
+    <hyperlink ref="C174" r:id="rId273" xr:uid="{9E5CE605-3386-0840-ACFA-2A2D09DB9D1B}"/>
+    <hyperlink ref="F175" r:id="rId274" xr:uid="{8E15B1CD-1528-2243-B09F-23DCDFEFED57}"/>
+    <hyperlink ref="C175" r:id="rId275" xr:uid="{57788FCB-5B1B-1C45-AE73-DD84C667625D}"/>
+    <hyperlink ref="F176" r:id="rId276" display="send CV" xr:uid="{707AE07C-5262-BC4D-9265-6EC0ED3CFCF6}"/>
+    <hyperlink ref="C176" r:id="rId277" xr:uid="{438ECEE0-7A39-284A-8F4B-C6F391DFF9A8}"/>
+    <hyperlink ref="F174" r:id="rId278" xr:uid="{E68B122E-F14A-A24B-A499-AE91A7682F39}"/>
+    <hyperlink ref="F177" r:id="rId279" xr:uid="{8A081B22-2061-F946-9B77-5847925A3209}"/>
+    <hyperlink ref="C177" r:id="rId280" xr:uid="{38E64B0E-B235-ED43-B078-7D53B4306871}"/>
+    <hyperlink ref="F36" r:id="rId281" xr:uid="{8CAC4DB3-6685-1742-8DD4-088232AB5DEE}"/>
+    <hyperlink ref="C36" r:id="rId282" xr:uid="{5E8E9F35-4AE3-DB47-BBA4-2801359318F9}"/>
+    <hyperlink ref="F35" r:id="rId283" xr:uid="{832D9369-E813-A74A-A0B6-82B3FA920394}"/>
+    <hyperlink ref="C74" r:id="rId284" xr:uid="{9E6596A6-27C3-044E-A543-69C81527E0B1}"/>
+    <hyperlink ref="F74" r:id="rId285" display="https://joe-campbell.github.io/website/" xr:uid="{ED659EA7-EBEC-0C4D-A81E-05F33C052924}"/>
+    <hyperlink ref="C76" r:id="rId286" xr:uid="{9A5DB3D4-9E7F-4E4F-8FD1-1C53D9174029}"/>
+    <hyperlink ref="F76" r:id="rId287" display="Yes" xr:uid="{2DFC89E2-23AF-E34C-8638-EF037FE8110A}"/>
+    <hyperlink ref="F75" r:id="rId288" xr:uid="{9467102C-D9A3-D34D-8F48-BC279E982807}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10979,34 +11138,37 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD80D363-78A3-684E-A61F-F8E4560DFD43}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="35.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="73.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="10.83203125" style="1"/>
+    <col min="25" max="25" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
@@ -11034,53 +11196,53 @@
       <c r="H1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
@@ -11103,48 +11265,48 @@
         <v>201</v>
       </c>
       <c r="H2" s="70" t="s">
-        <v>734</v>
-      </c>
-      <c r="I2" s="70" t="s">
+        <v>733</v>
+      </c>
+      <c r="I2" s="71">
+        <v>125</v>
+      </c>
+      <c r="J2" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="L2" s="44" t="s">
+        <v>508</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V2" s="70" t="s">
         <v>206</v>
       </c>
-      <c r="J2" s="70">
+      <c r="W2" s="70">
         <v>4704</v>
       </c>
-      <c r="K2" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L2" s="71">
-        <v>125</v>
-      </c>
-      <c r="M2" s="70" t="s">
-        <v>205</v>
-      </c>
-      <c r="N2" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="O2" s="44" t="s">
-        <v>508</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11170,43 +11332,43 @@
       <c r="H3" s="27" t="s">
         <v>350</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="71">
+        <v>155</v>
+      </c>
+      <c r="J3" s="70" t="s">
+        <v>207</v>
+      </c>
+      <c r="K3" s="44" t="s">
+        <v>222</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="N3" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V3" s="70" t="s">
         <v>208</v>
       </c>
-      <c r="J3" s="70">
+      <c r="W3" s="70">
         <v>4833</v>
       </c>
-      <c r="K3" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L3" s="71">
-        <v>155</v>
-      </c>
-      <c r="M3" s="70" t="s">
-        <v>207</v>
-      </c>
-      <c r="N3" s="44" t="s">
-        <v>222</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="Q3" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11228,49 +11390,49 @@
         <v>384</v>
       </c>
       <c r="H4" s="70" t="s">
-        <v>735</v>
-      </c>
-      <c r="I4" s="27" t="s">
+        <v>734</v>
+      </c>
+      <c r="I4" s="71">
+        <v>105</v>
+      </c>
+      <c r="J4" s="70"/>
+      <c r="K4" s="74" t="s">
+        <v>225</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="N4" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q4" s="48" t="s">
+        <v>515</v>
+      </c>
+      <c r="R4" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="48" t="s">
+        <v>514</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V4" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="J4" s="70" t="s">
+      <c r="W4" s="70" t="s">
         <v>211</v>
       </c>
-      <c r="K4" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L4" s="71">
-        <v>105</v>
-      </c>
-      <c r="M4" s="70"/>
-      <c r="N4" s="74" t="s">
-        <v>225</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="Q4" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" s="48" t="s">
-        <v>479</v>
-      </c>
-      <c r="T4" s="48" t="s">
-        <v>515</v>
-      </c>
-      <c r="U4" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="V4" s="48" t="s">
-        <v>514</v>
-      </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11292,45 +11454,45 @@
         <v>243</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>736</v>
-      </c>
-      <c r="I5" s="27" t="s">
+        <v>735</v>
+      </c>
+      <c r="I5" s="71">
+        <v>90</v>
+      </c>
+      <c r="J5" s="70" t="s">
+        <v>275</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="O5" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="P5" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V5" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="W5" s="70" t="s">
         <v>284</v>
       </c>
-      <c r="K5" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L5" s="71">
-        <v>90</v>
-      </c>
-      <c r="M5" s="70" t="s">
-        <v>275</v>
-      </c>
-      <c r="N5" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q5" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="R5" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="S5" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11354,41 +11516,41 @@
       <c r="H6" s="70" t="s">
         <v>662</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="I6" s="71">
+        <v>75</v>
+      </c>
+      <c r="J6" s="70" t="s">
+        <v>226</v>
+      </c>
+      <c r="K6" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="L6" s="44"/>
+      <c r="M6" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="N6" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="P6" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V6" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="J6" s="70" t="s">
+      <c r="W6" s="70" t="s">
         <v>227</v>
       </c>
-      <c r="K6" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L6" s="71">
-        <v>75</v>
-      </c>
-      <c r="M6" s="70" t="s">
-        <v>226</v>
-      </c>
-      <c r="N6" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="O6" s="44"/>
-      <c r="P6" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="Q6" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="R6" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="S6" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="T6" s="30" t="s">
-        <v>397</v>
-      </c>
-      <c r="W6" s="1" t="s">
+      <c r="X6" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11410,37 +11572,37 @@
         <v>201</v>
       </c>
       <c r="H7" s="70" t="s">
-        <v>737</v>
-      </c>
-      <c r="I7" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="I7" s="71">
+        <v>90</v>
+      </c>
+      <c r="J7" s="70"/>
+      <c r="K7" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="L7" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V7" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="J7" s="70">
+      <c r="W7" s="70">
         <v>1836</v>
       </c>
-      <c r="K7" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L7" s="71">
-        <v>90</v>
-      </c>
-      <c r="M7" s="70"/>
-      <c r="N7" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="O7" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="R7" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="W7" s="1" t="s">
+      <c r="X7" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11462,37 +11624,38 @@
         <v>638</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>738</v>
-      </c>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70" t="s">
+        <v>737</v>
+      </c>
+      <c r="I8" s="71">
+        <v>105</v>
+      </c>
+      <c r="J8" s="70"/>
+      <c r="K8" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N8" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="O8" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="P8" s="45" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="7"/>
+      <c r="T8" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V8" s="70"/>
+      <c r="W8" s="70" t="s">
         <v>652</v>
       </c>
-      <c r="K8" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L8" s="71">
-        <v>105</v>
-      </c>
-      <c r="M8" s="70"/>
-      <c r="N8" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q8" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="R8" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="S8" s="45" t="s">
-        <v>563</v>
-      </c>
-      <c r="T8" s="45"/>
-      <c r="U8" s="7"/>
-      <c r="W8" s="1" t="s">
+      <c r="X8" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11516,42 +11679,42 @@
         <v>201</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>739</v>
-      </c>
-      <c r="I9" s="70" t="s">
+        <v>738</v>
+      </c>
+      <c r="I9" s="71">
+        <v>90</v>
+      </c>
+      <c r="J9" s="70" t="s">
+        <v>404</v>
+      </c>
+      <c r="K9" s="70" t="s">
+        <v>299</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="P9" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V9" s="70" t="s">
         <v>382</v>
       </c>
-      <c r="J9" s="70">
+      <c r="W9" s="70">
         <v>4854</v>
       </c>
-      <c r="K9" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L9" s="71">
-        <v>90</v>
-      </c>
-      <c r="M9" s="70" t="s">
-        <v>404</v>
-      </c>
-      <c r="N9" s="70" t="s">
-        <v>299</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="S9" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="W9" s="1" t="s">
+      <c r="X9" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11577,44 +11740,47 @@
       <c r="H10" s="27" t="s">
         <v>594</v>
       </c>
-      <c r="I10" s="70" t="s">
+      <c r="I10" s="71">
+        <v>90</v>
+      </c>
+      <c r="J10" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="L10" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="N10" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V10" s="70" t="s">
         <v>241</v>
       </c>
-      <c r="J10" s="70">
+      <c r="W10" s="70">
         <v>6882</v>
       </c>
-      <c r="K10" s="70" t="s">
+      <c r="X10" s="70" t="s">
         <v>597</v>
       </c>
-      <c r="L10" s="71">
-        <v>90</v>
-      </c>
-      <c r="M10" s="70" t="s">
-        <v>205</v>
-      </c>
-      <c r="N10" s="44" t="s">
-        <v>244</v>
-      </c>
-      <c r="O10" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="Q10" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="R10" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="S10" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>597</v>
-      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>767</v>
+      </c>
       <c r="B11" s="69" t="s">
         <v>82</v>
       </c>
@@ -11634,34 +11800,41 @@
       <c r="H11" s="27" t="s">
         <v>594</v>
       </c>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70">
-        <v>6882</v>
-      </c>
-      <c r="K11" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L11" s="71">
+      <c r="I11" s="71">
         <v>90</v>
       </c>
-      <c r="M11" s="70"/>
-      <c r="N11" s="44" t="s">
+      <c r="J11" s="70"/>
+      <c r="K11" s="44" t="s">
         <v>369</v>
       </c>
-      <c r="O11" s="44"/>
-      <c r="P11" s="7" t="s">
+      <c r="L11" s="44"/>
+      <c r="M11" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="Q11" s="45" t="s">
+      <c r="N11" s="45" t="s">
         <v>87</v>
+      </c>
+      <c r="O11" s="67" t="s">
+        <v>537</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>766</v>
       </c>
       <c r="R11" s="28" t="s">
         <v>535</v>
       </c>
-      <c r="S11" s="67" t="s">
-        <v>537</v>
-      </c>
-      <c r="W11" s="1" t="s">
+      <c r="S11" s="3"/>
+      <c r="T11" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V11" s="70"/>
+      <c r="W11" s="70">
+        <v>6882</v>
+      </c>
+      <c r="X11" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11687,40 +11860,40 @@
       <c r="H12" s="70" t="s">
         <v>662</v>
       </c>
-      <c r="I12" s="70" t="s">
+      <c r="I12" s="71">
+        <v>155</v>
+      </c>
+      <c r="J12" s="70" t="s">
+        <v>271</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>728</v>
+      </c>
+      <c r="L12" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="N12" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="O12" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V12" s="70" t="s">
         <v>270</v>
       </c>
-      <c r="J12" s="70">
+      <c r="W12" s="70">
         <v>4836</v>
       </c>
-      <c r="K12" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L12" s="71">
-        <v>155</v>
-      </c>
-      <c r="M12" s="70" t="s">
-        <v>271</v>
-      </c>
-      <c r="N12" s="44" t="s">
-        <v>728</v>
-      </c>
-      <c r="O12" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="Q12" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="R12" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="S12" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="W12" s="1" t="s">
+      <c r="X12" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11744,45 +11917,45 @@
         <v>296</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>740</v>
-      </c>
-      <c r="I13" s="70" t="s">
+        <v>752</v>
+      </c>
+      <c r="I13" s="71">
+        <v>90</v>
+      </c>
+      <c r="J13" s="70" t="s">
+        <v>298</v>
+      </c>
+      <c r="K13" s="70" t="s">
+        <v>299</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="N13" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="O13" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q13" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V13" s="70" t="s">
         <v>294</v>
       </c>
-      <c r="J13" s="70">
+      <c r="W13" s="70">
         <v>2888</v>
       </c>
-      <c r="K13" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L13" s="71">
-        <v>90</v>
-      </c>
-      <c r="M13" s="70" t="s">
-        <v>298</v>
-      </c>
-      <c r="N13" s="70" t="s">
-        <v>299</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="Q13" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="R13" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="T13" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="W13" s="1" t="s">
+      <c r="X13" s="70" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11804,43 +11977,46 @@
         <v>201</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>739</v>
-      </c>
-      <c r="I14" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="I14" s="71">
+        <v>85</v>
+      </c>
+      <c r="J14" s="70" t="s">
+        <v>299</v>
+      </c>
+      <c r="K14" s="70" t="s">
+        <v>299</v>
+      </c>
+      <c r="L14" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V14" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="J14" s="70">
+      <c r="W14" s="70">
         <v>2111</v>
       </c>
-      <c r="K14" s="71" t="s">
+      <c r="X14" s="71" t="s">
         <v>597</v>
       </c>
-      <c r="L14" s="71">
-        <v>85</v>
-      </c>
-      <c r="M14" s="70" t="s">
-        <v>299</v>
-      </c>
-      <c r="N14" s="70" t="s">
-        <v>299</v>
-      </c>
-      <c r="O14" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="Q14" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="R14" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>597</v>
-      </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>763</v>
+      </c>
       <c r="B15" s="69" t="s">
         <v>60</v>
       </c>
@@ -11858,55 +12034,64 @@
         <v>201</v>
       </c>
       <c r="H15" s="70" t="s">
-        <v>741</v>
-      </c>
-      <c r="I15" s="70" t="s">
-        <v>461</v>
-      </c>
-      <c r="J15" s="70" t="s">
-        <v>462</v>
-      </c>
-      <c r="K15" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L15" s="71">
+        <v>739</v>
+      </c>
+      <c r="I15" s="71">
         <v>60</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="N15" s="26" t="s">
+      <c r="K15" s="26" t="s">
         <v>590</v>
       </c>
-      <c r="O15" s="44" t="s">
+      <c r="L15" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="Q15" s="20" t="s">
+      <c r="N15" s="13" t="s">
+        <v>756</v>
+      </c>
+      <c r="O15" s="13" t="s">
         <v>67</v>
+      </c>
+      <c r="P15" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>758</v>
       </c>
       <c r="R15" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="S15" s="3"/>
-      <c r="W15" s="1" t="s">
+      <c r="S15" s="6"/>
+      <c r="T15" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V15" s="70" t="s">
+        <v>461</v>
+      </c>
+      <c r="W15" s="70" t="s">
+        <v>462</v>
+      </c>
+      <c r="X15" s="70" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B16" s="69" t="s">
-        <v>342</v>
+        <v>138</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="D16" s="70" t="s">
         <v>334</v>
       </c>
-      <c r="E16" s="64" t="s">
-        <v>344</v>
+      <c r="E16" s="73">
+        <v>46002</v>
       </c>
       <c r="F16" s="70" t="s">
         <v>297</v>
@@ -11915,315 +12100,328 @@
         <v>201</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>742</v>
-      </c>
-      <c r="I16" s="27" t="s">
-        <v>340</v>
+        <v>740</v>
+      </c>
+      <c r="I16" s="71">
+        <v>105</v>
       </c>
       <c r="J16" s="70" t="s">
-        <v>345</v>
-      </c>
-      <c r="K16" s="70" t="s">
+        <v>310</v>
+      </c>
+      <c r="K16" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="L16" s="44"/>
+      <c r="M16" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="N16" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="O16" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="T16" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="L16" s="71">
-        <v>80</v>
-      </c>
-      <c r="M16" s="70"/>
-      <c r="N16" s="44" t="s">
-        <v>360</v>
-      </c>
-      <c r="O16" s="44" t="s">
-        <v>509</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q16" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="R16" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="W16" s="1" t="s">
+      <c r="V16" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="W16" s="70">
+        <v>5156</v>
+      </c>
+      <c r="X16" s="70" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B17" s="69" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>143</v>
+        <v>245</v>
       </c>
       <c r="D17" s="70" t="s">
         <v>334</v>
       </c>
-      <c r="E17" s="73">
-        <v>46002</v>
+      <c r="E17" s="72">
+        <v>46006</v>
       </c>
       <c r="F17" s="70" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="G17" s="70" t="s">
         <v>201</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>743</v>
-      </c>
-      <c r="I17" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="J17" s="70">
-        <v>5156</v>
-      </c>
-      <c r="K17" s="70" t="s">
+        <v>738</v>
+      </c>
+      <c r="I17" s="71">
+        <v>105</v>
+      </c>
+      <c r="J17" s="70"/>
+      <c r="K17" s="44" t="s">
+        <v>315</v>
+      </c>
+      <c r="L17" s="44"/>
+      <c r="M17" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="N17" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="O17" s="48" t="s">
+        <v>591</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="T17" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="L17" s="71">
-        <v>105</v>
-      </c>
-      <c r="M17" s="70" t="s">
-        <v>310</v>
-      </c>
-      <c r="N17" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="O17" s="44"/>
-      <c r="P17" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q17" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="R17" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="W17" s="1" t="s">
+      <c r="V17" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="W17" s="70">
+        <v>4852</v>
+      </c>
+      <c r="X17" s="70" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B18" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>245</v>
+        <v>414</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="D18" s="70" t="s">
-        <v>334</v>
-      </c>
-      <c r="E18" s="72">
-        <v>46006</v>
+        <v>323</v>
+      </c>
+      <c r="E18" s="77">
+        <v>46007</v>
       </c>
       <c r="F18" s="70" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="G18" s="70" t="s">
         <v>201</v>
       </c>
-      <c r="H18" s="27" t="s">
-        <v>739</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="J18" s="70">
-        <v>4852</v>
-      </c>
-      <c r="K18" s="70" t="s">
+      <c r="H18" s="70" t="s">
+        <v>662</v>
+      </c>
+      <c r="I18" s="71">
+        <v>95</v>
+      </c>
+      <c r="J18" s="71"/>
+      <c r="K18" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="N18" s="29" t="s">
+        <v>415</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="T18" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="L18" s="71">
-        <v>105</v>
-      </c>
-      <c r="M18" s="70"/>
-      <c r="N18" s="44" t="s">
-        <v>315</v>
-      </c>
-      <c r="O18" s="44"/>
-      <c r="P18" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="Q18" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="R18" s="48" t="s">
-        <v>591</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="W18" s="1" t="s">
+      <c r="V18" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="W18" s="70">
+        <v>5816</v>
+      </c>
+      <c r="X18" s="70" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>764</v>
+      </c>
       <c r="B19" s="69" t="s">
-        <v>414</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>8</v>
+        <v>628</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>5</v>
       </c>
       <c r="D19" s="70" t="s">
-        <v>323</v>
-      </c>
-      <c r="E19" s="77">
-        <v>46007</v>
-      </c>
-      <c r="F19" s="70" t="s">
-        <v>297</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="E19" s="64">
+        <v>45992</v>
+      </c>
+      <c r="F19" s="70"/>
       <c r="G19" s="70" t="s">
         <v>201</v>
       </c>
-      <c r="H19" s="70" t="s">
-        <v>662</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="J19" s="70">
-        <v>5816</v>
-      </c>
-      <c r="K19" s="70" t="s">
+      <c r="H19" s="27" t="s">
+        <v>741</v>
+      </c>
+      <c r="I19" s="71" t="s">
+        <v>698</v>
+      </c>
+      <c r="J19" s="70"/>
+      <c r="K19" s="44" t="s">
+        <v>359</v>
+      </c>
+      <c r="L19" s="44"/>
+      <c r="M19" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="N19" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="O19" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="L19" s="71">
-        <v>95</v>
-      </c>
-      <c r="M19" s="71"/>
-      <c r="N19" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="Q19" s="29" t="s">
-        <v>415</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="W19" s="1" t="s">
+      <c r="V19" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="W19" s="70">
+        <v>5859</v>
+      </c>
+      <c r="X19" s="70" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>733</v>
+        <v>751</v>
       </c>
       <c r="B20" s="69" t="s">
-        <v>628</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>5</v>
+        <v>342</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="D20" s="70" t="s">
-        <v>465</v>
-      </c>
-      <c r="E20" s="64">
-        <v>45992</v>
-      </c>
-      <c r="F20" s="70"/>
+        <v>324</v>
+      </c>
+      <c r="E20" s="77">
+        <v>46006</v>
+      </c>
+      <c r="F20" s="70" t="s">
+        <v>749</v>
+      </c>
       <c r="G20" s="70" t="s">
         <v>201</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>744</v>
-      </c>
-      <c r="I20" s="27" t="s">
-        <v>352</v>
-      </c>
-      <c r="J20" s="70">
-        <v>5859</v>
-      </c>
-      <c r="K20" s="70" t="s">
+        <v>750</v>
+      </c>
+      <c r="I20" s="71">
+        <v>80</v>
+      </c>
+      <c r="J20" s="70"/>
+      <c r="K20" s="44" t="s">
+        <v>360</v>
+      </c>
+      <c r="L20" s="44" t="s">
+        <v>509</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N20" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="O20" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="T20" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="L20" s="71" t="s">
-        <v>698</v>
-      </c>
-      <c r="M20" s="70"/>
-      <c r="N20" s="44" t="s">
-        <v>359</v>
-      </c>
-      <c r="O20" s="44"/>
-      <c r="P20" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="Q20" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="R20" s="48" t="s">
-        <v>170</v>
-      </c>
-      <c r="W20" s="1" t="s">
+      <c r="V20" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="W20" s="70" t="s">
+        <v>345</v>
+      </c>
+      <c r="X20" s="70" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B21" s="69" t="s">
-        <v>629</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="70" t="s">
-        <v>613</v>
-      </c>
-      <c r="E21" s="76">
-        <v>46006</v>
-      </c>
-      <c r="F21" s="70"/>
-      <c r="G21" s="78" t="s">
-        <v>621</v>
-      </c>
-      <c r="H21" s="70" t="s">
-        <v>745</v>
-      </c>
-      <c r="I21" s="70" t="s">
-        <v>620</v>
-      </c>
-      <c r="J21" s="70">
-        <v>4586</v>
-      </c>
-      <c r="K21" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="L21" s="71">
-        <v>85</v>
-      </c>
-      <c r="M21" s="70"/>
-      <c r="N21" s="70" t="s">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E21" s="25">
+        <v>46022</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H21" s="27"/>
+      <c r="I21" s="11">
+        <v>115</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="O21" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q21" s="45" t="s">
-        <v>616</v>
-      </c>
-      <c r="R21" s="45" t="s">
-        <v>607</v>
-      </c>
-      <c r="S21" s="48" t="s">
-        <v>605</v>
-      </c>
-      <c r="T21" s="7" t="s">
-        <v>619</v>
+      <c r="K21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="N21" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="O21" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="T21" s="34" t="s">
+        <v>760</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+      <c r="X21" s="34" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="I22" s="11"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="I23" s="11"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B24" s="69" t="s">
         <v>4</v>
       </c>
@@ -12243,36 +12441,36 @@
       <c r="H24" s="70" t="s">
         <v>203</v>
       </c>
-      <c r="I24" s="70" t="s">
+      <c r="I24" s="71">
+        <v>125</v>
+      </c>
+      <c r="J24" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="L24" s="44"/>
+      <c r="M24" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="N24" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="O24" s="68" t="s">
+        <v>510</v>
+      </c>
+      <c r="V24" s="70" t="s">
         <v>206</v>
       </c>
-      <c r="J24" s="70">
+      <c r="W24" s="70">
         <v>4704</v>
       </c>
-      <c r="K24" s="70" t="s">
+      <c r="X24" s="70" t="s">
         <v>597</v>
       </c>
-      <c r="L24" s="71">
-        <v>125</v>
-      </c>
-      <c r="M24" s="70" t="s">
-        <v>205</v>
-      </c>
-      <c r="N24" s="44" t="s">
-        <v>220</v>
-      </c>
-      <c r="O24" s="44"/>
-      <c r="P24" s="7" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q24" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="R24" s="68" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B25" s="69" t="s">
         <v>109</v>
       </c>
@@ -12292,31 +12490,32 @@
       <c r="H25" s="70" t="s">
         <v>639</v>
       </c>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70" t="s">
+      <c r="I25" s="71">
+        <v>105</v>
+      </c>
+      <c r="J25" s="70"/>
+      <c r="K25" s="27" t="s">
+        <v>564</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N25" s="45" t="s">
+        <v>560</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="V25" s="70"/>
+      <c r="W25" s="70" t="s">
         <v>652</v>
       </c>
-      <c r="K25" s="70" t="s">
+      <c r="X25" s="70" t="s">
         <v>597</v>
       </c>
-      <c r="L25" s="71">
-        <v>105</v>
-      </c>
-      <c r="M25" s="70"/>
-      <c r="N25" s="27" t="s">
-        <v>564</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q25" s="45" t="s">
-        <v>560</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B26" s="69" t="s">
         <v>133</v>
       </c>
@@ -12336,199 +12535,372 @@
       <c r="H26" s="70" t="s">
         <v>587</v>
       </c>
-      <c r="I26" s="70"/>
-      <c r="J26" s="70">
+      <c r="I26" s="71">
+        <v>85</v>
+      </c>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70" t="s">
+        <v>299</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="N26" s="45" t="s">
+        <v>567</v>
+      </c>
+      <c r="O26" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="V26" s="70"/>
+      <c r="W26" s="70">
         <v>2111</v>
       </c>
-      <c r="K26" s="70" t="s">
+      <c r="X26" s="70" t="s">
         <v>597</v>
       </c>
-      <c r="L26" s="71">
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B27" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>334</v>
+      </c>
+      <c r="E27" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="F27" s="70" t="s">
+        <v>297</v>
+      </c>
+      <c r="G27" s="70" t="s">
+        <v>201</v>
+      </c>
+      <c r="H27" s="66" t="s">
+        <v>748</v>
+      </c>
+      <c r="I27" s="71">
+        <v>80</v>
+      </c>
+      <c r="J27" s="70"/>
+      <c r="K27" s="44" t="s">
+        <v>360</v>
+      </c>
+      <c r="L27" s="44" t="s">
+        <v>509</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N27" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="O27" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V27" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="W27" s="70" t="s">
+        <v>345</v>
+      </c>
+      <c r="X27" s="70" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B28" s="69" t="s">
+        <v>629</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="70" t="s">
+        <v>613</v>
+      </c>
+      <c r="E28" s="76">
+        <v>46006</v>
+      </c>
+      <c r="F28" s="70"/>
+      <c r="G28" s="78" t="s">
+        <v>621</v>
+      </c>
+      <c r="H28" s="70" t="s">
+        <v>742</v>
+      </c>
+      <c r="I28" s="71">
         <v>85</v>
       </c>
-      <c r="M26" s="70"/>
-      <c r="N26" s="70" t="s">
+      <c r="J28" s="70"/>
+      <c r="K28" s="70" t="s">
         <v>299</v>
       </c>
-      <c r="P26" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="Q26" s="45" t="s">
-        <v>567</v>
-      </c>
-      <c r="R26" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="S26" s="7" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="L28" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="N28" s="45" t="s">
+        <v>616</v>
+      </c>
+      <c r="O28" s="45" t="s">
+        <v>607</v>
+      </c>
+      <c r="P28" s="48" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V28" s="70" t="s">
+        <v>620</v>
+      </c>
+      <c r="W28" s="70">
+        <v>4586</v>
+      </c>
+      <c r="X28" s="70" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="I29" s="11"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="I30" s="11"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="H31" s="1" t="s">
-        <v>746</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="I31" s="11"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="I32" s="11"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" spans="9:18" x14ac:dyDescent="0.2">
+      <c r="I33" s="11"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+    </row>
+    <row r="34" spans="9:18" x14ac:dyDescent="0.2">
+      <c r="I34" s="11"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+    </row>
+    <row r="35" spans="9:18" x14ac:dyDescent="0.2">
+      <c r="I35" s="11"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="40" spans="9:18" x14ac:dyDescent="0.2">
+      <c r="R40" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C24" r:id="rId1" xr:uid="{51B5B240-F127-424D-934E-35581681C3C1}"/>
-    <hyperlink ref="N24" r:id="rId2" display="?" xr:uid="{B55DD6F4-6DFA-F748-B417-2D6FE5C2C5B6}"/>
-    <hyperlink ref="Q24" r:id="rId3" xr:uid="{6ACA983C-1371-ED47-902A-15D9AD890924}"/>
+    <hyperlink ref="K24" r:id="rId2" display="?" xr:uid="{B55DD6F4-6DFA-F748-B417-2D6FE5C2C5B6}"/>
+    <hyperlink ref="N24" r:id="rId3" xr:uid="{6ACA983C-1371-ED47-902A-15D9AD890924}"/>
     <hyperlink ref="C3" r:id="rId4" xr:uid="{909FEFB2-4956-204A-843C-00B985B282CB}"/>
-    <hyperlink ref="N3" r:id="rId5" display="https://www.universityofcalifornia.edu/about-us/information-center/doctoral-program" xr:uid="{2D6345EB-9B56-6047-8029-A392A00D013F}"/>
+    <hyperlink ref="K3" r:id="rId5" display="https://www.universityofcalifornia.edu/about-us/information-center/doctoral-program" xr:uid="{2D6345EB-9B56-6047-8029-A392A00D013F}"/>
     <hyperlink ref="H3" r:id="rId6" display="Personal History Statement (~1,2p)" xr:uid="{3553C041-D267-DC43-BD94-E0A93A537FD3}"/>
-    <hyperlink ref="S3" r:id="rId7" xr:uid="{32CC98E5-9EC2-F44C-804D-69AD1F718EEC}"/>
-    <hyperlink ref="Q3" r:id="rId8" xr:uid="{F75C852E-05FD-D54C-9FC5-5EF584B2AA69}"/>
-    <hyperlink ref="T3" r:id="rId9" xr:uid="{7B1B1F33-8288-8D4D-B524-2BFE5A49C3A3}"/>
+    <hyperlink ref="P3" r:id="rId7" xr:uid="{32CC98E5-9EC2-F44C-804D-69AD1F718EEC}"/>
+    <hyperlink ref="N3" r:id="rId8" xr:uid="{F75C852E-05FD-D54C-9FC5-5EF584B2AA69}"/>
+    <hyperlink ref="Q3" r:id="rId9" xr:uid="{7B1B1F33-8288-8D4D-B524-2BFE5A49C3A3}"/>
     <hyperlink ref="C4" r:id="rId10" display="SIC-ROBO(ME)" xr:uid="{D8BCAA83-29FE-3647-8102-66A647B1531A}"/>
-    <hyperlink ref="N4" r:id="rId11" display="https://lite.gatech.edu/lite_script/dashboards/doctoral_program_stats.html" xr:uid="{9390A562-699D-2A46-A160-7AC482EB3A03}"/>
-    <hyperlink ref="U4" r:id="rId12" xr:uid="{8FB685FF-AE6B-0C41-BF39-761A111794EE}"/>
-    <hyperlink ref="Q4" r:id="rId13" xr:uid="{59C1680A-468E-6B48-A323-12069CB6CF61}"/>
-    <hyperlink ref="R4" r:id="rId14" xr:uid="{C08BD256-6B38-4342-9543-1CC294D49DBC}"/>
-    <hyperlink ref="I4" r:id="rId15" xr:uid="{13AB94D5-357E-B642-ACC2-E56A142CFA5F}"/>
+    <hyperlink ref="K4" r:id="rId11" display="https://lite.gatech.edu/lite_script/dashboards/doctoral_program_stats.html" xr:uid="{9390A562-699D-2A46-A160-7AC482EB3A03}"/>
+    <hyperlink ref="R4" r:id="rId12" xr:uid="{8FB685FF-AE6B-0C41-BF39-761A111794EE}"/>
+    <hyperlink ref="N4" r:id="rId13" xr:uid="{59C1680A-468E-6B48-A323-12069CB6CF61}"/>
+    <hyperlink ref="O4" r:id="rId14" xr:uid="{C08BD256-6B38-4342-9543-1CC294D49DBC}"/>
+    <hyperlink ref="V4" r:id="rId15" xr:uid="{13AB94D5-357E-B642-ACC2-E56A142CFA5F}"/>
     <hyperlink ref="C6" r:id="rId16" xr:uid="{F6F24D35-1B13-3A49-BB24-719EAD2120A9}"/>
-    <hyperlink ref="I6" r:id="rId17" xr:uid="{887AED41-C476-9A49-86CA-1773FC7DBFF7}"/>
-    <hyperlink ref="N6" r:id="rId18" display="8 accepted (2023)" xr:uid="{31A85C00-BA68-724B-8E64-55038D818B32}"/>
-    <hyperlink ref="Q6" r:id="rId19" location="projects" xr:uid="{E67D1436-CE90-FD40-9D9C-412FE73DE2BC}"/>
-    <hyperlink ref="R6" r:id="rId20" xr:uid="{2F325FFA-EECA-1B44-87C0-E4DDAA725FA4}"/>
-    <hyperlink ref="S6" r:id="rId21" display="Gunya Shi" xr:uid="{12CFD204-DA9D-EF44-A772-82E385A2A45F}"/>
-    <hyperlink ref="T6" r:id="rId22" xr:uid="{1F3D192D-81DC-5A42-B9EF-4B6DAC65BC60}"/>
+    <hyperlink ref="V6" r:id="rId17" xr:uid="{887AED41-C476-9A49-86CA-1773FC7DBFF7}"/>
+    <hyperlink ref="K6" r:id="rId18" display="8 accepted (2023)" xr:uid="{31A85C00-BA68-724B-8E64-55038D818B32}"/>
+    <hyperlink ref="N6" r:id="rId19" location="projects" xr:uid="{E67D1436-CE90-FD40-9D9C-412FE73DE2BC}"/>
+    <hyperlink ref="O6" r:id="rId20" xr:uid="{2F325FFA-EECA-1B44-87C0-E4DDAA725FA4}"/>
+    <hyperlink ref="P6" r:id="rId21" display="Gunya Shi" xr:uid="{12CFD204-DA9D-EF44-A772-82E385A2A45F}"/>
+    <hyperlink ref="Q6" r:id="rId22" xr:uid="{1F3D192D-81DC-5A42-B9EF-4B6DAC65BC60}"/>
     <hyperlink ref="C11" r:id="rId23" xr:uid="{0E72A31D-DBCE-5347-A3A1-6B9847260D96}"/>
-    <hyperlink ref="Q11" r:id="rId24" xr:uid="{681A5B45-5964-064F-8AD0-4194BE9DDB76}"/>
+    <hyperlink ref="N11" r:id="rId24" xr:uid="{681A5B45-5964-064F-8AD0-4194BE9DDB76}"/>
     <hyperlink ref="C5" r:id="rId25" xr:uid="{8D92587D-6263-3942-8DFB-83E4E948AE49}"/>
-    <hyperlink ref="I5" r:id="rId26" xr:uid="{3F04115C-1393-6A4D-ADE3-94B61E5D9F94}"/>
+    <hyperlink ref="V5" r:id="rId26" xr:uid="{3F04115C-1393-6A4D-ADE3-94B61E5D9F94}"/>
     <hyperlink ref="H5" r:id="rId27" display="Personal Statement" xr:uid="{05F21152-4837-9249-94A0-04DD3F92FCAC}"/>
-    <hyperlink ref="N5" r:id="rId28" xr:uid="{5E571075-206D-2C48-BA80-6D94D2BA6D4F}"/>
-    <hyperlink ref="R5" r:id="rId29" location="Publications-Section" xr:uid="{3B4E6347-E950-AA47-A69D-F6C6CEAB2E5C}"/>
-    <hyperlink ref="S5" r:id="rId30" xr:uid="{672C72FB-796B-9A47-840E-F2B8B5714226}"/>
-    <hyperlink ref="T5" r:id="rId31" display="https://scholar.google.com/citations?hl=en&amp;user=g9bV-_sAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{8E974455-DCFD-9847-92B8-EEC1D51A82ED}"/>
+    <hyperlink ref="K5" r:id="rId28" xr:uid="{5E571075-206D-2C48-BA80-6D94D2BA6D4F}"/>
+    <hyperlink ref="O5" r:id="rId29" location="Publications-Section" xr:uid="{3B4E6347-E950-AA47-A69D-F6C6CEAB2E5C}"/>
+    <hyperlink ref="P5" r:id="rId30" xr:uid="{672C72FB-796B-9A47-840E-F2B8B5714226}"/>
+    <hyperlink ref="Q5" r:id="rId31" display="https://scholar.google.com/citations?hl=en&amp;user=g9bV-_sAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{8E974455-DCFD-9847-92B8-EEC1D51A82ED}"/>
     <hyperlink ref="C13" r:id="rId32" xr:uid="{20166705-0366-CA40-9920-63F41193C573}"/>
-    <hyperlink ref="Q13" r:id="rId33" xr:uid="{DB93B9F5-595B-3E46-A63E-1D9A2ABBB3D9}"/>
-    <hyperlink ref="S13" r:id="rId34" xr:uid="{6C939CAF-856D-A34B-AFD0-39E18C00FE09}"/>
-    <hyperlink ref="C17" r:id="rId35" xr:uid="{66FF43C6-7FF2-334F-A250-FCA0A32C9AEF}"/>
-    <hyperlink ref="I17" r:id="rId36" location="tests" xr:uid="{7E5AD4FA-FE45-DA49-8016-09E09B1BFEAB}"/>
-    <hyperlink ref="N17" r:id="rId37" xr:uid="{B2DCC8C3-A62D-0B48-BC56-674E8A057697}"/>
-    <hyperlink ref="H17" r:id="rId38" display="Life Experiences Statement, Supplementary " xr:uid="{81108888-C4A5-774F-8B21-770121B2B922}"/>
-    <hyperlink ref="N18" r:id="rId39" xr:uid="{8E3AEB08-4CE8-4249-967E-021A85CF562E}"/>
-    <hyperlink ref="I18" r:id="rId40" xr:uid="{F6175592-B77A-4E49-9556-2C0D3208416E}"/>
-    <hyperlink ref="C18" r:id="rId41" location="phdmaterials" xr:uid="{A7E2D835-C903-1A4D-93DD-5B65FE5D79FC}"/>
-    <hyperlink ref="H18" r:id="rId42" location="phdmaterials" display="Personal Statement" xr:uid="{62596068-88B0-6442-9F3D-9407BC10636C}"/>
-    <hyperlink ref="Q18" r:id="rId43" location="conference-publications" xr:uid="{3842EB66-0441-F240-9E92-32B026F6C8A8}"/>
-    <hyperlink ref="E20" r:id="rId44" display="https://me.vt.edu/for-students/graduate/admissions-funding.html" xr:uid="{BD8784D8-A1DC-1B45-8B2A-61A2F935A29D}"/>
-    <hyperlink ref="H20" r:id="rId45" display="Supplementary mat., 2025-01-02 final deadline," xr:uid="{73C7CE62-0059-9C46-9776-A334F003C718}"/>
-    <hyperlink ref="I20" r:id="rId46" xr:uid="{08E28CD1-4474-5F4E-B88A-3947CF7DA9A4}"/>
-    <hyperlink ref="C20" r:id="rId47" xr:uid="{225821D0-7605-1545-9705-2120BC3530BB}"/>
-    <hyperlink ref="N20" r:id="rId48" xr:uid="{E94A0EC0-5F48-DC48-86F5-3ECCA2AE7653}"/>
-    <hyperlink ref="C16" r:id="rId49" xr:uid="{E424A793-6DC0-FF45-BAE2-B6C3F5D21DE0}"/>
-    <hyperlink ref="I16" r:id="rId50" xr:uid="{8D2D9448-581A-F847-83AC-D1B7CBBD2BC1}"/>
-    <hyperlink ref="E16" r:id="rId51" location="ucb-accordion-id--4-content3" xr:uid="{33E91ABB-936A-4347-9475-57250E16E800}"/>
-    <hyperlink ref="N16" r:id="rId52" xr:uid="{2CF29F4A-1C29-E845-9FA2-54E8FDCE0405}"/>
-    <hyperlink ref="Q16" r:id="rId53" xr:uid="{DC3FB0B1-E230-354D-A013-F499E9AC647F}"/>
-    <hyperlink ref="R16" r:id="rId54" xr:uid="{6068DEEF-DC1D-1F40-84C9-3981C109DAAB}"/>
-    <hyperlink ref="Q17" r:id="rId55" xr:uid="{37DBE5A8-E6F5-DC4D-81CE-4CC709BE147A}"/>
-    <hyperlink ref="R17" r:id="rId56" xr:uid="{35090968-56CB-D644-B0A4-2AC13205A24F}"/>
-    <hyperlink ref="S4" r:id="rId57" xr:uid="{4EFEB2E8-7C5A-0C45-A079-11A3F7EBDE8C}"/>
-    <hyperlink ref="P17" r:id="rId58" xr:uid="{939EA6F2-A5FF-F54A-B97B-9EF282057260}"/>
-    <hyperlink ref="R13" r:id="rId59" xr:uid="{E36F0A35-05EC-F646-8ECE-DBB0CF1BC225}"/>
-    <hyperlink ref="T13" r:id="rId60" xr:uid="{99641881-100C-3A45-B659-61094BD36B26}"/>
-    <hyperlink ref="P13" r:id="rId61" display="GRASP" xr:uid="{DE823A40-C140-DE43-950E-CCA09F47F0EB}"/>
-    <hyperlink ref="V4" r:id="rId62" xr:uid="{3107D36A-7816-0540-96C4-74EF2B6CB421}"/>
-    <hyperlink ref="T4" r:id="rId63" xr:uid="{188C7A52-FE43-754F-8376-B52B3291F058}"/>
-    <hyperlink ref="R24" r:id="rId64" xr:uid="{8303D648-D25D-C24E-BEE7-80701D18D5AB}"/>
+    <hyperlink ref="N13" r:id="rId33" xr:uid="{DB93B9F5-595B-3E46-A63E-1D9A2ABBB3D9}"/>
+    <hyperlink ref="P13" r:id="rId34" xr:uid="{6C939CAF-856D-A34B-AFD0-39E18C00FE09}"/>
+    <hyperlink ref="C16" r:id="rId35" xr:uid="{66FF43C6-7FF2-334F-A250-FCA0A32C9AEF}"/>
+    <hyperlink ref="V16" r:id="rId36" location="tests" xr:uid="{7E5AD4FA-FE45-DA49-8016-09E09B1BFEAB}"/>
+    <hyperlink ref="K16" r:id="rId37" xr:uid="{B2DCC8C3-A62D-0B48-BC56-674E8A057697}"/>
+    <hyperlink ref="H16" r:id="rId38" display="Life Experiences Statement, Supplementary " xr:uid="{81108888-C4A5-774F-8B21-770121B2B922}"/>
+    <hyperlink ref="K17" r:id="rId39" xr:uid="{8E3AEB08-4CE8-4249-967E-021A85CF562E}"/>
+    <hyperlink ref="V17" r:id="rId40" xr:uid="{F6175592-B77A-4E49-9556-2C0D3208416E}"/>
+    <hyperlink ref="C17" r:id="rId41" location="phdmaterials" xr:uid="{A7E2D835-C903-1A4D-93DD-5B65FE5D79FC}"/>
+    <hyperlink ref="H17" r:id="rId42" location="phdmaterials" display="Personal Statement" xr:uid="{62596068-88B0-6442-9F3D-9407BC10636C}"/>
+    <hyperlink ref="N17" r:id="rId43" location="conference-publications" xr:uid="{3842EB66-0441-F240-9E92-32B026F6C8A8}"/>
+    <hyperlink ref="E19" r:id="rId44" display="https://me.vt.edu/for-students/graduate/admissions-funding.html" xr:uid="{BD8784D8-A1DC-1B45-8B2A-61A2F935A29D}"/>
+    <hyperlink ref="H19" r:id="rId45" display="Supplementary mat., 2025-01-02 final deadline," xr:uid="{73C7CE62-0059-9C46-9776-A334F003C718}"/>
+    <hyperlink ref="V19" r:id="rId46" xr:uid="{08E28CD1-4474-5F4E-B88A-3947CF7DA9A4}"/>
+    <hyperlink ref="C19" r:id="rId47" xr:uid="{225821D0-7605-1545-9705-2120BC3530BB}"/>
+    <hyperlink ref="K19" r:id="rId48" xr:uid="{E94A0EC0-5F48-DC48-86F5-3ECCA2AE7653}"/>
+    <hyperlink ref="C27" r:id="rId49" xr:uid="{E424A793-6DC0-FF45-BAE2-B6C3F5D21DE0}"/>
+    <hyperlink ref="V27" r:id="rId50" xr:uid="{8D2D9448-581A-F847-83AC-D1B7CBBD2BC1}"/>
+    <hyperlink ref="E27" r:id="rId51" location="ucb-accordion-id--4-content3" xr:uid="{33E91ABB-936A-4347-9475-57250E16E800}"/>
+    <hyperlink ref="K27" r:id="rId52" xr:uid="{2CF29F4A-1C29-E845-9FA2-54E8FDCE0405}"/>
+    <hyperlink ref="N27" r:id="rId53" xr:uid="{DC3FB0B1-E230-354D-A013-F499E9AC647F}"/>
+    <hyperlink ref="O27" r:id="rId54" xr:uid="{6068DEEF-DC1D-1F40-84C9-3981C109DAAB}"/>
+    <hyperlink ref="N16" r:id="rId55" xr:uid="{37DBE5A8-E6F5-DC4D-81CE-4CC709BE147A}"/>
+    <hyperlink ref="O16" r:id="rId56" xr:uid="{35090968-56CB-D644-B0A4-2AC13205A24F}"/>
+    <hyperlink ref="P4" r:id="rId57" xr:uid="{4EFEB2E8-7C5A-0C45-A079-11A3F7EBDE8C}"/>
+    <hyperlink ref="M16" r:id="rId58" xr:uid="{939EA6F2-A5FF-F54A-B97B-9EF282057260}"/>
+    <hyperlink ref="O13" r:id="rId59" xr:uid="{E36F0A35-05EC-F646-8ECE-DBB0CF1BC225}"/>
+    <hyperlink ref="Q13" r:id="rId60" xr:uid="{99641881-100C-3A45-B659-61094BD36B26}"/>
+    <hyperlink ref="M13" r:id="rId61" display="GRASP" xr:uid="{DE823A40-C140-DE43-950E-CCA09F47F0EB}"/>
+    <hyperlink ref="S4" r:id="rId62" xr:uid="{3107D36A-7816-0540-96C4-74EF2B6CB421}"/>
+    <hyperlink ref="Q4" r:id="rId63" xr:uid="{188C7A52-FE43-754F-8376-B52B3291F058}"/>
+    <hyperlink ref="O24" r:id="rId64" xr:uid="{8303D648-D25D-C24E-BEE7-80701D18D5AB}"/>
     <hyperlink ref="R11" r:id="rId65" xr:uid="{C466F216-F9DD-E043-B5E3-FA91388CB9DA}"/>
-    <hyperlink ref="S11" r:id="rId66" xr:uid="{9A9F50B7-7E5C-A242-9AA0-8F4A93473724}"/>
-    <hyperlink ref="Q20" r:id="rId67" xr:uid="{CBE57E7C-0C01-E044-86D1-E1B8FB8205DF}"/>
-    <hyperlink ref="R20" r:id="rId68" xr:uid="{8BAE7FA6-10D0-8643-B1CF-3DA3BC0946B2}"/>
-    <hyperlink ref="Q25" r:id="rId69" xr:uid="{6AD7F0BF-4B94-BE43-9DD6-C9A6A33E82CA}"/>
-    <hyperlink ref="Q8" r:id="rId70" location="teaching-section" xr:uid="{2E211449-0C29-0343-A655-E61405C8A870}"/>
-    <hyperlink ref="R8" r:id="rId71" xr:uid="{3FF8296F-4D11-D340-8EE1-11413EE77D4B}"/>
-    <hyperlink ref="S8" r:id="rId72" xr:uid="{8CDA4B65-45C4-254F-9AD5-4CFE3505E554}"/>
-    <hyperlink ref="N25" r:id="rId73" xr:uid="{9AD8346F-78DE-9B45-BA37-9A9F83C3B3B5}"/>
-    <hyperlink ref="R25" r:id="rId74" xr:uid="{AE7EE058-DAC5-074A-98C0-8D7DE6071FC8}"/>
-    <hyperlink ref="R26" r:id="rId75" xr:uid="{5A689890-7308-EC47-96C3-69657114E4A5}"/>
-    <hyperlink ref="Q26" r:id="rId76" xr:uid="{1538D926-732C-B547-B5DD-7830DBBFA118}"/>
-    <hyperlink ref="S26" r:id="rId77" xr:uid="{56799967-8DB7-CF46-9677-3B4094EE03DF}"/>
+    <hyperlink ref="O11" r:id="rId66" xr:uid="{9A9F50B7-7E5C-A242-9AA0-8F4A93473724}"/>
+    <hyperlink ref="N19" r:id="rId67" xr:uid="{CBE57E7C-0C01-E044-86D1-E1B8FB8205DF}"/>
+    <hyperlink ref="O19" r:id="rId68" xr:uid="{8BAE7FA6-10D0-8643-B1CF-3DA3BC0946B2}"/>
+    <hyperlink ref="N25" r:id="rId69" xr:uid="{6AD7F0BF-4B94-BE43-9DD6-C9A6A33E82CA}"/>
+    <hyperlink ref="N8" r:id="rId70" location="teaching-section" xr:uid="{2E211449-0C29-0343-A655-E61405C8A870}"/>
+    <hyperlink ref="O8" r:id="rId71" xr:uid="{3FF8296F-4D11-D340-8EE1-11413EE77D4B}"/>
+    <hyperlink ref="P8" r:id="rId72" xr:uid="{8CDA4B65-45C4-254F-9AD5-4CFE3505E554}"/>
+    <hyperlink ref="K25" r:id="rId73" xr:uid="{9AD8346F-78DE-9B45-BA37-9A9F83C3B3B5}"/>
+    <hyperlink ref="O25" r:id="rId74" xr:uid="{AE7EE058-DAC5-074A-98C0-8D7DE6071FC8}"/>
+    <hyperlink ref="O26" r:id="rId75" xr:uid="{5A689890-7308-EC47-96C3-69657114E4A5}"/>
+    <hyperlink ref="N26" r:id="rId76" xr:uid="{1538D926-732C-B547-B5DD-7830DBBFA118}"/>
+    <hyperlink ref="P26" r:id="rId77" xr:uid="{56799967-8DB7-CF46-9677-3B4094EE03DF}"/>
     <hyperlink ref="C26" r:id="rId78" xr:uid="{B1850B21-A5A6-B74B-8247-A19048FA1F2F}"/>
     <hyperlink ref="G26" r:id="rId79" xr:uid="{411375C1-A4C4-974F-9F2F-9DE00DA17008}"/>
     <hyperlink ref="C25" r:id="rId80" location=":~:text=Ph.-,D.,Applicants" display="ME-ROBO" xr:uid="{D6189E8A-925D-E145-92A3-607DB472E37A}"/>
-    <hyperlink ref="R3" r:id="rId81" xr:uid="{21522587-3BFF-2F45-A95D-A670A4127A63}"/>
-    <hyperlink ref="R18" r:id="rId82" xr:uid="{C002861C-9677-7B4F-81B1-2A1A426930E3}"/>
+    <hyperlink ref="O3" r:id="rId81" xr:uid="{21522587-3BFF-2F45-A95D-A670A4127A63}"/>
+    <hyperlink ref="O17" r:id="rId82" xr:uid="{C002861C-9677-7B4F-81B1-2A1A426930E3}"/>
     <hyperlink ref="H11" r:id="rId83" xr:uid="{6069E40B-3C0F-4A49-BB1D-EF53A8BFF2F1}"/>
-    <hyperlink ref="S18" r:id="rId84" xr:uid="{C95D2403-4EB1-724F-86D7-179DDF0DB277}"/>
-    <hyperlink ref="S21" r:id="rId85" xr:uid="{4AB26DC7-8A93-764F-9936-DFAE1F2A5249}"/>
-    <hyperlink ref="R21" r:id="rId86" xr:uid="{B9AEBB72-571F-A14D-A15F-5EE62913D13C}"/>
-    <hyperlink ref="Q21" r:id="rId87" xr:uid="{EBBE0330-B4A8-F140-A788-1E449374F524}"/>
-    <hyperlink ref="T21" r:id="rId88" xr:uid="{C6ED7956-7ED7-DA44-82A2-ABB994FBE536}"/>
-    <hyperlink ref="C21" r:id="rId89" location="description" xr:uid="{B9CC155E-4E0A-2440-98B2-FEC67522639D}"/>
-    <hyperlink ref="E21" r:id="rId90" location="description" display="https://graduate.oregonstate.edu/programs/3250/robotics-phd-ms-minor - description" xr:uid="{3B8B1BBF-3596-7341-9232-C5AD33F2A1D2}"/>
+    <hyperlink ref="P17" r:id="rId84" xr:uid="{C95D2403-4EB1-724F-86D7-179DDF0DB277}"/>
+    <hyperlink ref="P28" r:id="rId85" xr:uid="{4AB26DC7-8A93-764F-9936-DFAE1F2A5249}"/>
+    <hyperlink ref="O28" r:id="rId86" xr:uid="{B9AEBB72-571F-A14D-A15F-5EE62913D13C}"/>
+    <hyperlink ref="N28" r:id="rId87" xr:uid="{EBBE0330-B4A8-F140-A788-1E449374F524}"/>
+    <hyperlink ref="Q28" r:id="rId88" xr:uid="{C6ED7956-7ED7-DA44-82A2-ABB994FBE536}"/>
+    <hyperlink ref="C28" r:id="rId89" location="description" xr:uid="{B9CC155E-4E0A-2440-98B2-FEC67522639D}"/>
+    <hyperlink ref="E28" r:id="rId90" location="description" display="https://graduate.oregonstate.edu/programs/3250/robotics-phd-ms-minor - description" xr:uid="{3B8B1BBF-3596-7341-9232-C5AD33F2A1D2}"/>
     <hyperlink ref="C10" r:id="rId91" xr:uid="{68DD901D-4E36-B146-83AF-B19962D69BA5}"/>
-    <hyperlink ref="N10" r:id="rId92" xr:uid="{B5F09303-1EF3-7941-91BC-6A348B653F7F}"/>
-    <hyperlink ref="Q10" r:id="rId93" xr:uid="{4BEEB0B5-CF17-C646-8EE8-D9B1370187E9}"/>
-    <hyperlink ref="R10" r:id="rId94" xr:uid="{5CCA3BFF-E781-5944-B1F6-EBE2FF87489C}"/>
-    <hyperlink ref="S10" r:id="rId95" xr:uid="{BE110D91-4DD6-BB45-B9AF-2539A03848AD}"/>
+    <hyperlink ref="K10" r:id="rId92" xr:uid="{B5F09303-1EF3-7941-91BC-6A348B653F7F}"/>
+    <hyperlink ref="N10" r:id="rId93" xr:uid="{4BEEB0B5-CF17-C646-8EE8-D9B1370187E9}"/>
+    <hyperlink ref="O10" r:id="rId94" xr:uid="{5CCA3BFF-E781-5944-B1F6-EBE2FF87489C}"/>
+    <hyperlink ref="P10" r:id="rId95" xr:uid="{BE110D91-4DD6-BB45-B9AF-2539A03848AD}"/>
     <hyperlink ref="C12" r:id="rId96" display="CSE" xr:uid="{B291DA6B-4EAE-EB42-B649-26F7D1B510CE}"/>
-    <hyperlink ref="N12" r:id="rId97" display="8%(35/404)" xr:uid="{38B5BBBB-36B8-B647-B6AD-380F7978BDEE}"/>
-    <hyperlink ref="R12" r:id="rId98" location="_ri" xr:uid="{D7FA602A-0538-004B-B8AC-EFF9E846EFF5}"/>
-    <hyperlink ref="S12" r:id="rId99" xr:uid="{9949A074-DDD8-0748-A3D5-D296EE2CB2E6}"/>
-    <hyperlink ref="Q12" r:id="rId100" xr:uid="{9CA5BC65-45BA-CA4B-BB50-70554955B512}"/>
+    <hyperlink ref="K12" r:id="rId97" display="8%(35/404)" xr:uid="{38B5BBBB-36B8-B647-B6AD-380F7978BDEE}"/>
+    <hyperlink ref="O12" r:id="rId98" location="_ri" xr:uid="{D7FA602A-0538-004B-B8AC-EFF9E846EFF5}"/>
+    <hyperlink ref="P12" r:id="rId99" xr:uid="{9949A074-DDD8-0748-A3D5-D296EE2CB2E6}"/>
+    <hyperlink ref="N12" r:id="rId100" xr:uid="{9CA5BC65-45BA-CA4B-BB50-70554955B512}"/>
     <hyperlink ref="H10" r:id="rId101" xr:uid="{68701F73-D566-3C4A-BAB4-5FF42E7B15B1}"/>
-    <hyperlink ref="P24" r:id="rId102" xr:uid="{81606837-51A2-4C4D-8F7C-74672D0A0AE7}"/>
-    <hyperlink ref="P3" r:id="rId103" xr:uid="{4A7FD456-BBDB-5C41-8E50-1899168920A1}"/>
-    <hyperlink ref="P4" r:id="rId104" display="IRIM" xr:uid="{07717B9D-4A30-2D46-A24F-29C2EC8A2F57}"/>
-    <hyperlink ref="P5" r:id="rId105" xr:uid="{C25FBFE7-937C-674B-8FB8-4203D37F3AFC}"/>
-    <hyperlink ref="P6" r:id="rId106" xr:uid="{FEF97170-022A-8E4C-ABCA-75F4A24D643F}"/>
-    <hyperlink ref="P25" r:id="rId107" xr:uid="{8322FFE9-389C-9244-BDA4-F87BA8633E36}"/>
-    <hyperlink ref="P10" r:id="rId108" xr:uid="{E672B8AF-C577-814A-887E-E02A53F58F2A}"/>
-    <hyperlink ref="P11" r:id="rId109" xr:uid="{06A94A8D-DC53-A44E-987C-05196AE1F6C7}"/>
-    <hyperlink ref="P12" r:id="rId110" display="CRI" xr:uid="{3AD3A895-2FF3-F94E-9144-9D3FB148BAE2}"/>
-    <hyperlink ref="P26" r:id="rId111" xr:uid="{CAD78BFD-D6F1-D047-B115-2B6688E29023}"/>
-    <hyperlink ref="P16" r:id="rId112" xr:uid="{699B37CC-33F9-D74A-8B33-52D7E87250AE}"/>
-    <hyperlink ref="P18" r:id="rId113" xr:uid="{95F268FF-37DB-B74E-8079-ECF6ECF61C3E}"/>
-    <hyperlink ref="P20" r:id="rId114" xr:uid="{331AE20E-1B62-D143-A72A-C622653807EE}"/>
-    <hyperlink ref="P21" r:id="rId115" xr:uid="{01A51E95-B8B6-A143-85F4-9567D29C1DA1}"/>
+    <hyperlink ref="M24" r:id="rId102" xr:uid="{81606837-51A2-4C4D-8F7C-74672D0A0AE7}"/>
+    <hyperlink ref="M3" r:id="rId103" xr:uid="{4A7FD456-BBDB-5C41-8E50-1899168920A1}"/>
+    <hyperlink ref="M4" r:id="rId104" display="IRIM" xr:uid="{07717B9D-4A30-2D46-A24F-29C2EC8A2F57}"/>
+    <hyperlink ref="M5" r:id="rId105" xr:uid="{C25FBFE7-937C-674B-8FB8-4203D37F3AFC}"/>
+    <hyperlink ref="M6" r:id="rId106" xr:uid="{FEF97170-022A-8E4C-ABCA-75F4A24D643F}"/>
+    <hyperlink ref="M25" r:id="rId107" xr:uid="{8322FFE9-389C-9244-BDA4-F87BA8633E36}"/>
+    <hyperlink ref="M10" r:id="rId108" xr:uid="{E672B8AF-C577-814A-887E-E02A53F58F2A}"/>
+    <hyperlink ref="M11" r:id="rId109" xr:uid="{06A94A8D-DC53-A44E-987C-05196AE1F6C7}"/>
+    <hyperlink ref="M12" r:id="rId110" display="CRI" xr:uid="{3AD3A895-2FF3-F94E-9144-9D3FB148BAE2}"/>
+    <hyperlink ref="M26" r:id="rId111" xr:uid="{CAD78BFD-D6F1-D047-B115-2B6688E29023}"/>
+    <hyperlink ref="M27" r:id="rId112" xr:uid="{699B37CC-33F9-D74A-8B33-52D7E87250AE}"/>
+    <hyperlink ref="M17" r:id="rId113" xr:uid="{95F268FF-37DB-B74E-8079-ECF6ECF61C3E}"/>
+    <hyperlink ref="M19" r:id="rId114" xr:uid="{331AE20E-1B62-D143-A72A-C622653807EE}"/>
+    <hyperlink ref="M28" r:id="rId115" xr:uid="{01A51E95-B8B6-A143-85F4-9567D29C1DA1}"/>
     <hyperlink ref="C7" r:id="rId116" xr:uid="{90372745-E046-3349-A8A9-3501D3F1C323}"/>
-    <hyperlink ref="N7" r:id="rId117" xr:uid="{29B5CCE1-EB58-2946-AEEF-1268D7BE6614}"/>
-    <hyperlink ref="I7" r:id="rId118" xr:uid="{538378EF-61C5-234E-AB9A-2056B925D76C}"/>
-    <hyperlink ref="Q7" r:id="rId119" xr:uid="{0F88190B-53A0-2142-ABA5-4F2CEDC7DB0E}"/>
-    <hyperlink ref="R7" r:id="rId120" xr:uid="{0612D716-32F3-BB49-866A-9DF152B4C831}"/>
+    <hyperlink ref="K7" r:id="rId117" xr:uid="{29B5CCE1-EB58-2946-AEEF-1268D7BE6614}"/>
+    <hyperlink ref="V7" r:id="rId118" xr:uid="{538378EF-61C5-234E-AB9A-2056B925D76C}"/>
+    <hyperlink ref="N7" r:id="rId119" xr:uid="{0F88190B-53A0-2142-ABA5-4F2CEDC7DB0E}"/>
+    <hyperlink ref="O7" r:id="rId120" xr:uid="{0612D716-32F3-BB49-866A-9DF152B4C831}"/>
     <hyperlink ref="C15" r:id="rId121" xr:uid="{DA216DB2-D275-6346-A4F9-C6289B0B12FB}"/>
-    <hyperlink ref="M15" r:id="rId122" xr:uid="{6C379FA5-413D-F047-9AB0-7B94F86A4F1F}"/>
-    <hyperlink ref="N15" r:id="rId123" xr:uid="{B87D9CA4-4293-2B42-B828-377CBA582F6D}"/>
-    <hyperlink ref="R15" r:id="rId124" xr:uid="{E71BA650-E4FC-8842-A2F4-DF8F7038129E}"/>
-    <hyperlink ref="Q15" r:id="rId125" xr:uid="{A8CB0918-5A8D-F443-9199-0338B58B84C1}"/>
-    <hyperlink ref="Q19" r:id="rId126" display="https://dingmyu.github.io/" xr:uid="{64E7AE76-381C-3849-AB51-45C03D55685F}"/>
-    <hyperlink ref="T19" r:id="rId127" display="https://scholar.google.com/citations?hl=en&amp;user=DN8QtscAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{19A5BC45-23E1-CD40-AB93-CD15DABCFD22}"/>
-    <hyperlink ref="R19" r:id="rId128" display="https://scholar.google.com/citations?hl=en&amp;user=WxmhtyMAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{71B15757-8A6D-BE4D-8F21-ACBFBF4601B1}"/>
-    <hyperlink ref="S19" r:id="rId129" display="https://scholar.google.com/citations?user=-XEZA0UAAAAJ&amp;hl=en" xr:uid="{F337616F-32C2-9748-AD7D-A8A959D52521}"/>
-    <hyperlink ref="S9" r:id="rId130" display="https://weirdlab.cs.washington.edu/publications.html" xr:uid="{D1C16875-51E2-9647-8CFE-7FAD87267A20}"/>
-    <hyperlink ref="R9" r:id="rId131" xr:uid="{B738DCC1-AF6D-0F4A-B0C3-4614DD9EFEF0}"/>
-    <hyperlink ref="Q9" r:id="rId132" xr:uid="{2870C02B-1EEC-A240-8002-DE9DA87F75B6}"/>
-    <hyperlink ref="C9" r:id="rId133" xr:uid="{93131157-5694-4B40-87DB-C809028D8ECD}"/>
-    <hyperlink ref="H9" r:id="rId134" display="Personal Statement (Unlimited)" xr:uid="{71E9B93E-CA71-924E-ABF3-1BF301BAF16A}"/>
-    <hyperlink ref="E19" r:id="rId135" display="https://cs.unc.edu/graduate/graduate-admissions/admissions-deadline/" xr:uid="{A8DA038C-62AF-7049-923E-C802B5D0F120}"/>
-    <hyperlink ref="C19" r:id="rId136" xr:uid="{1F11307D-180C-7F4E-8F58-3C796024EADC}"/>
-    <hyperlink ref="C2" r:id="rId137" xr:uid="{9BBA89A6-0F3B-DC48-9929-53F346B0AEC8}"/>
-    <hyperlink ref="N2" r:id="rId138" display="?" xr:uid="{44F0BD16-9489-304C-AA7B-73439E846FB2}"/>
-    <hyperlink ref="Q2" r:id="rId139" location="people" xr:uid="{8000CF1A-E833-7046-85A6-F8FD94F89DD6}"/>
-    <hyperlink ref="S2" r:id="rId140" xr:uid="{1020D82E-17AD-0843-92AB-4DEFC033D629}"/>
-    <hyperlink ref="R2" r:id="rId141" xr:uid="{47F0EA44-5277-5445-BB7A-BDDCF1050356}"/>
-    <hyperlink ref="T2" r:id="rId142" xr:uid="{44235266-313A-EB4D-822B-20B3417A492B}"/>
-    <hyperlink ref="U2" r:id="rId143" xr:uid="{0DA4B984-247B-014C-AF10-7B70DD5E6E5B}"/>
-    <hyperlink ref="P2" r:id="rId144" xr:uid="{CF22B631-12A1-DF4D-B5B5-DC93A74172A4}"/>
-    <hyperlink ref="Q5" r:id="rId145" xr:uid="{76506796-C1E0-6349-ABE0-0536ABD45091}"/>
-    <hyperlink ref="N8" r:id="rId146" display="12%(36/313)" xr:uid="{B150AADE-A14F-C24C-B2FF-F7650A150E11}"/>
-    <hyperlink ref="C8" r:id="rId147" xr:uid="{BEB53160-CC16-4B4F-8683-4043A3679F0E}"/>
-    <hyperlink ref="P8" r:id="rId148" xr:uid="{403AC756-4DC9-5749-A758-AB302FB4F2BA}"/>
-    <hyperlink ref="C14" r:id="rId149" xr:uid="{10250109-04DC-6440-8105-1037D9E87518}"/>
-    <hyperlink ref="G14" r:id="rId150" location="accordion0" xr:uid="{118FF7BE-9E94-8D44-B027-894752139F9F}"/>
-    <hyperlink ref="I14" r:id="rId151" location="accordion4" xr:uid="{B0920AC5-DC82-FE4C-8611-440F49C62D25}"/>
-    <hyperlink ref="Q14" r:id="rId152" xr:uid="{41CE533A-A3A2-7045-BC72-A7DA7B883646}"/>
-    <hyperlink ref="R14" r:id="rId153" xr:uid="{CFB02884-305D-8A4F-B9AD-A5FD63EEE249}"/>
-    <hyperlink ref="P7" r:id="rId154" xr:uid="{406E37A6-FF92-654F-AA7D-F0B853F5FF96}"/>
-    <hyperlink ref="P9" r:id="rId155" xr:uid="{7CC2DD5F-A881-014B-ADC0-CDC512AD50B2}"/>
-    <hyperlink ref="P14" r:id="rId156" xr:uid="{8BEED9EF-D2D2-AE4B-986F-3B993B288322}"/>
-    <hyperlink ref="P15" r:id="rId157" xr:uid="{6404535E-F308-B24E-8838-A6B2B9B78C82}"/>
-    <hyperlink ref="N19" r:id="rId158" xr:uid="{1BAE4FB2-D466-3247-A0CD-F4386B5F4CCB}"/>
-    <hyperlink ref="I19" r:id="rId159" location="intl" xr:uid="{565A0AEE-3EF2-FE41-AF6F-14077D092460}"/>
+    <hyperlink ref="J15" r:id="rId122" xr:uid="{6C379FA5-413D-F047-9AB0-7B94F86A4F1F}"/>
+    <hyperlink ref="K15" r:id="rId123" xr:uid="{B87D9CA4-4293-2B42-B828-377CBA582F6D}"/>
+    <hyperlink ref="N18" r:id="rId124" display="https://dingmyu.github.io/" xr:uid="{64E7AE76-381C-3849-AB51-45C03D55685F}"/>
+    <hyperlink ref="Q18" r:id="rId125" display="https://scholar.google.com/citations?hl=en&amp;user=DN8QtscAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{19A5BC45-23E1-CD40-AB93-CD15DABCFD22}"/>
+    <hyperlink ref="O18" r:id="rId126" display="https://scholar.google.com/citations?hl=en&amp;user=WxmhtyMAAAAJ&amp;view_op=list_works&amp;sortby=pubdate" xr:uid="{71B15757-8A6D-BE4D-8F21-ACBFBF4601B1}"/>
+    <hyperlink ref="P18" r:id="rId127" display="https://scholar.google.com/citations?user=-XEZA0UAAAAJ&amp;hl=en" xr:uid="{F337616F-32C2-9748-AD7D-A8A959D52521}"/>
+    <hyperlink ref="P9" r:id="rId128" display="https://weirdlab.cs.washington.edu/publications.html" xr:uid="{D1C16875-51E2-9647-8CFE-7FAD87267A20}"/>
+    <hyperlink ref="O9" r:id="rId129" xr:uid="{B738DCC1-AF6D-0F4A-B0C3-4614DD9EFEF0}"/>
+    <hyperlink ref="N9" r:id="rId130" xr:uid="{2870C02B-1EEC-A240-8002-DE9DA87F75B6}"/>
+    <hyperlink ref="C9" r:id="rId131" xr:uid="{93131157-5694-4B40-87DB-C809028D8ECD}"/>
+    <hyperlink ref="H9" r:id="rId132" display="Personal Statement (Unlimited)" xr:uid="{71E9B93E-CA71-924E-ABF3-1BF301BAF16A}"/>
+    <hyperlink ref="E18" r:id="rId133" display="https://cs.unc.edu/graduate/graduate-admissions/admissions-deadline/" xr:uid="{A8DA038C-62AF-7049-923E-C802B5D0F120}"/>
+    <hyperlink ref="C18" r:id="rId134" xr:uid="{1F11307D-180C-7F4E-8F58-3C796024EADC}"/>
+    <hyperlink ref="C2" r:id="rId135" xr:uid="{9BBA89A6-0F3B-DC48-9929-53F346B0AEC8}"/>
+    <hyperlink ref="K2" r:id="rId136" display="?" xr:uid="{44F0BD16-9489-304C-AA7B-73439E846FB2}"/>
+    <hyperlink ref="N2" r:id="rId137" location="people" xr:uid="{8000CF1A-E833-7046-85A6-F8FD94F89DD6}"/>
+    <hyperlink ref="P2" r:id="rId138" xr:uid="{1020D82E-17AD-0843-92AB-4DEFC033D629}"/>
+    <hyperlink ref="O2" r:id="rId139" xr:uid="{47F0EA44-5277-5445-BB7A-BDDCF1050356}"/>
+    <hyperlink ref="Q2" r:id="rId140" xr:uid="{44235266-313A-EB4D-822B-20B3417A492B}"/>
+    <hyperlink ref="R2" r:id="rId141" xr:uid="{0DA4B984-247B-014C-AF10-7B70DD5E6E5B}"/>
+    <hyperlink ref="M2" r:id="rId142" xr:uid="{CF22B631-12A1-DF4D-B5B5-DC93A74172A4}"/>
+    <hyperlink ref="N5" r:id="rId143" xr:uid="{76506796-C1E0-6349-ABE0-0536ABD45091}"/>
+    <hyperlink ref="K8" r:id="rId144" display="12%(36/313)" xr:uid="{B150AADE-A14F-C24C-B2FF-F7650A150E11}"/>
+    <hyperlink ref="C8" r:id="rId145" xr:uid="{BEB53160-CC16-4B4F-8683-4043A3679F0E}"/>
+    <hyperlink ref="M8" r:id="rId146" xr:uid="{403AC756-4DC9-5749-A758-AB302FB4F2BA}"/>
+    <hyperlink ref="C14" r:id="rId147" xr:uid="{10250109-04DC-6440-8105-1037D9E87518}"/>
+    <hyperlink ref="G14" r:id="rId148" location="accordion0" xr:uid="{118FF7BE-9E94-8D44-B027-894752139F9F}"/>
+    <hyperlink ref="V14" r:id="rId149" location="accordion4" xr:uid="{B0920AC5-DC82-FE4C-8611-440F49C62D25}"/>
+    <hyperlink ref="N14" r:id="rId150" xr:uid="{41CE533A-A3A2-7045-BC72-A7DA7B883646}"/>
+    <hyperlink ref="O14" r:id="rId151" xr:uid="{CFB02884-305D-8A4F-B9AD-A5FD63EEE249}"/>
+    <hyperlink ref="M7" r:id="rId152" xr:uid="{406E37A6-FF92-654F-AA7D-F0B853F5FF96}"/>
+    <hyperlink ref="M9" r:id="rId153" xr:uid="{7CC2DD5F-A881-014B-ADC0-CDC512AD50B2}"/>
+    <hyperlink ref="M14" r:id="rId154" xr:uid="{8BEED9EF-D2D2-AE4B-986F-3B993B288322}"/>
+    <hyperlink ref="M15" r:id="rId155" xr:uid="{6404535E-F308-B24E-8838-A6B2B9B78C82}"/>
+    <hyperlink ref="K18" r:id="rId156" xr:uid="{1BAE4FB2-D466-3247-A0CD-F4386B5F4CCB}"/>
+    <hyperlink ref="V18" r:id="rId157" location="intl" xr:uid="{565A0AEE-3EF2-FE41-AF6F-14077D092460}"/>
+    <hyperlink ref="C20" r:id="rId158" location="accordion-eef9ca50d354b86d6d837faa03991d073-1" xr:uid="{21AD0D30-7EF6-9940-ADAE-8F035813E157}"/>
+    <hyperlink ref="V20" r:id="rId159" xr:uid="{675B94B6-BE11-E74B-BE97-81D572D8AEC9}"/>
+    <hyperlink ref="E20" r:id="rId160" location="accordion-eef9ca50d354b86d6d837faa03991d073-1" display="https://www.colorado.edu/cs/admissions/graduate-admissions/how-apply - accordion-eef9ca50d354b86d6d837faa03991d073-1" xr:uid="{C7F85CD1-BF35-1741-847F-FE758E904521}"/>
+    <hyperlink ref="K20" r:id="rId161" xr:uid="{980B6426-298C-114F-8B06-35337D72BD64}"/>
+    <hyperlink ref="N20" r:id="rId162" xr:uid="{CA8ADAEC-E2E7-1149-8DB0-FD1006C24AE9}"/>
+    <hyperlink ref="O20" r:id="rId163" xr:uid="{B240D5EA-49E1-BE46-9090-987A20C21A43}"/>
+    <hyperlink ref="M20" r:id="rId164" xr:uid="{080E6F48-CCB2-F549-8395-6FB52F69ED92}"/>
+    <hyperlink ref="C21" r:id="rId165" display="SCAI" xr:uid="{7A84A69B-B51E-D044-A092-4DC7618E8BF8}"/>
+    <hyperlink ref="V21" r:id="rId166" xr:uid="{27857414-0A38-CC40-B279-72BE6CB6784B}"/>
+    <hyperlink ref="N21" r:id="rId167" xr:uid="{8F5C08FF-4853-6C4D-BE60-C09EBF1D8314}"/>
+    <hyperlink ref="O21" r:id="rId168" xr:uid="{16B29EF5-A460-FA4F-A6E3-343B5C7A46BE}"/>
+    <hyperlink ref="P21" r:id="rId169" xr:uid="{7B76634F-62A7-5E43-9B0C-972E8319DE0A}"/>
+    <hyperlink ref="N15" r:id="rId170" xr:uid="{F34860C7-9655-A842-A2A9-9CED9C0A92E3}"/>
+    <hyperlink ref="R15" r:id="rId171" xr:uid="{039D81C1-A768-E543-9C3A-78A1FE295C6C}"/>
+    <hyperlink ref="P15" r:id="rId172" xr:uid="{74E0468F-A597-7F45-AA76-982D85360024}"/>
+    <hyperlink ref="Q15" r:id="rId173" xr:uid="{E4DDFB7B-C44D-2641-98F9-8F64DE54243F}"/>
+    <hyperlink ref="O15" r:id="rId174" xr:uid="{1C8BE2D9-25D8-7040-AFBB-870B90C39D41}"/>
+    <hyperlink ref="P11" r:id="rId175" xr:uid="{5A0E2DC6-7112-CB42-8B13-0D714E7EE698}"/>
+    <hyperlink ref="Q11" r:id="rId176" xr:uid="{BC88C10D-785F-534A-B349-B2DA4E7086B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/PhD_PI_Listup.xlsx
+++ b/PhD_PI_Listup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyeonbeen/Git/LaTeX-Docs/MyResume/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D707683-0E5B-9F48-A192-AEE8C9A0360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BEB974-4D3A-2044-B5E8-A1B5D4BE715B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="22540" activeTab="4" xr2:uid="{422F52E5-BD25-DB4D-B83C-2D9AD22AB820}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="22540" xr2:uid="{422F52E5-BD25-DB4D-B83C-2D9AD22AB820}"/>
   </bookViews>
   <sheets>
     <sheet name="Professors" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2389" uniqueCount="783">
   <si>
     <t>PI</t>
   </si>
@@ -2440,9 +2440,6 @@
     <t>Control theory, Learning little, lots of robots</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
     <t>Supplementary form (500w)</t>
   </si>
   <si>
@@ -2510,9 +2507,6 @@
     <t>(SOP==PS, ~2p)</t>
   </si>
   <si>
-    <t>Additional Coursework</t>
-  </si>
-  <si>
     <t>(SOP==PS ~2p, +Community), +(Community 200w)</t>
   </si>
   <si>
@@ -2546,19 +2540,70 @@
     <t>LoR, TOEFL after deadline?</t>
   </si>
   <si>
-    <t>LoR받고 제출만</t>
-  </si>
-  <si>
-    <t>Video, LoR받고 제출만</t>
-  </si>
-  <si>
     <t>Ann Majewicz Fey</t>
   </si>
   <si>
     <t>Mitchell W Pryor</t>
   </si>
   <si>
-    <t>Submitted, awaiting MyStatus</t>
+    <t>Accept LoR after deadline, TOEFL within deadline</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>In progress, LoR</t>
+  </si>
+  <si>
+    <t>Submitted, LoR</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>AeroAstro</t>
+  </si>
+  <si>
+    <t>Marco Pavone</t>
+  </si>
+  <si>
+    <t>Physically grounded robot planning, physics-based digital twin, data-driven control</t>
+  </si>
+  <si>
+    <t>Safe AI, HJ reachability, MPC, Physics-informed ML, Safety guided IL</t>
+  </si>
+  <si>
+    <t>Somil Bansal</t>
+  </si>
+  <si>
+    <t>Safe AI, Navigation &amp; SLAM, sensor fusion</t>
+  </si>
+  <si>
+    <t>Grace Gao</t>
+  </si>
+  <si>
+    <t>AeroAstro, CS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision making in uncertainty, Safe AI, Navigation, Adaptive sampling, Constrained and domain-informed policy, </t>
+  </si>
+  <si>
+    <t>Mykel Kochenderfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-agent robots, vision-based perception, Geometry-embedded, differntiable simulator, </t>
+  </si>
+  <si>
+    <t>after admission</t>
+  </si>
+  <si>
+    <t>we accept students</t>
+  </si>
+  <si>
+    <t>Mac Schwager</t>
+  </si>
+  <si>
+    <t>AeroAstro, EE</t>
   </si>
 </sst>
 </file>
@@ -2974,10 +3019,10 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3315,7 +3360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132F7052-85E4-E84F-9E71-39A4BFB15A06}">
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" style="5" bestFit="1" customWidth="1"/>
@@ -4000,10 +4045,10 @@
         <v>86</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>746</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.2">
@@ -4014,10 +4059,10 @@
         <v>86</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -4684,10 +4729,10 @@
         <v>8</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E74" s="16" t="s">
         <v>128</v>
@@ -4704,10 +4749,10 @@
         <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D75" s="70" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E75" s="70" t="s">
         <v>28</v>
@@ -4724,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -6621,12 +6666,97 @@
         <v>718</v>
       </c>
     </row>
-    <row r="177" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C177" s="3" t="s">
         <v>721</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>720</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B179" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B180" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B181" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B182" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -6920,6 +7050,15 @@
     <hyperlink ref="C76" r:id="rId286" xr:uid="{9A5DB3D4-9E7F-4E4F-8FD1-1C53D9174029}"/>
     <hyperlink ref="F76" r:id="rId287" display="Yes" xr:uid="{2DFC89E2-23AF-E34C-8638-EF037FE8110A}"/>
     <hyperlink ref="F75" r:id="rId288" xr:uid="{9467102C-D9A3-D34D-8F48-BC279E982807}"/>
+    <hyperlink ref="C178" r:id="rId289" xr:uid="{03171C12-4519-3B41-A03E-DE3C397082EB}"/>
+    <hyperlink ref="C179" r:id="rId290" display="https://smlbansal.github.io/sia-lab/publications.html" xr:uid="{650F4A89-D858-CA4B-B4A6-B79D1A57D72C}"/>
+    <hyperlink ref="C180" r:id="rId291" xr:uid="{0D692EF2-94EF-B041-8E80-651E8BC65D8C}"/>
+    <hyperlink ref="C181" r:id="rId292" display="https://sisl.stanford.edu/publications/" xr:uid="{A6A553D8-9382-9E49-8240-B67BB7BAC09C}"/>
+    <hyperlink ref="C182" r:id="rId293" display="https://msl.stanford.edu/" xr:uid="{FB3B84C8-DC14-A94A-93B3-7406F17A9333}"/>
+    <hyperlink ref="F179" r:id="rId294" xr:uid="{B6C3342E-C53D-DD46-9391-94C758679435}"/>
+    <hyperlink ref="F180" r:id="rId295" xr:uid="{D210D5B9-A70F-3146-AE86-502C97F3E44D}"/>
+    <hyperlink ref="F178" r:id="rId296" display="I'll try best to respond" xr:uid="{37695FF8-F824-3D47-93CE-5D6F335DF153}"/>
+    <hyperlink ref="F181" r:id="rId297" xr:uid="{AAB6B7F7-C053-E343-A6A4-58E240818AAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11145,13 +11284,13 @@
     <col min="2" max="2" width="17.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="35.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="73.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.83203125" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.5" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -11172,8 +11311,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>732</v>
+      <c r="A1" s="4" t="s">
+        <v>764</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -11200,7 +11339,7 @@
         <v>199</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>219</v>
@@ -11246,67 +11385,43 @@
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="69" t="s">
+      <c r="A2" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>8</v>
+      <c r="C2" s="3" t="s">
+        <v>768</v>
       </c>
       <c r="D2" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E2" s="63">
+        <v>327</v>
+      </c>
+      <c r="E2" s="62">
         <v>45993</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="G2" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H2" s="70" t="s">
-        <v>733</v>
-      </c>
-      <c r="I2" s="71">
+      <c r="I2" s="11">
         <v>125</v>
       </c>
-      <c r="J2" s="70" t="s">
-        <v>205</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="L2" s="44" t="s">
-        <v>508</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>640</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>9</v>
+      <c r="J2" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="V2" s="70" t="s">
-        <v>206</v>
-      </c>
-      <c r="W2" s="70">
+      <c r="V2" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="W2" s="1">
         <v>4704</v>
       </c>
-      <c r="X2" s="70" t="s">
+      <c r="X2" s="1" t="s">
         <v>597</v>
       </c>
     </row>
@@ -11390,7 +11505,7 @@
         <v>384</v>
       </c>
       <c r="H4" s="70" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="I4" s="71">
         <v>105</v>
@@ -11437,6 +11552,9 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>765</v>
+      </c>
       <c r="B5" s="69" t="s">
         <v>97</v>
       </c>
@@ -11454,13 +11572,13 @@
         <v>243</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I5" s="71">
         <v>90</v>
       </c>
-      <c r="J5" s="70" t="s">
-        <v>275</v>
+      <c r="J5" s="27" t="s">
+        <v>763</v>
       </c>
       <c r="K5" s="44" t="s">
         <v>286</v>
@@ -11471,7 +11589,7 @@
       <c r="M5" s="7" t="s">
         <v>643</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="45" t="s">
         <v>107</v>
       </c>
       <c r="O5" s="45" t="s">
@@ -11558,7 +11676,7 @@
       <c r="B7" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="27" t="s">
         <v>65</v>
       </c>
       <c r="D7" s="70" t="s">
@@ -11572,31 +11690,31 @@
         <v>201</v>
       </c>
       <c r="H7" s="70" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I7" s="71">
         <v>90</v>
       </c>
       <c r="J7" s="70"/>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="44" t="s">
         <v>236</v>
       </c>
       <c r="L7" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="7" t="s">
         <v>723</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="N7" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="O7" s="20" t="s">
+      <c r="O7" s="28" t="s">
         <v>373</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="V7" s="6" t="s">
+      <c r="V7" s="27" t="s">
         <v>354</v>
       </c>
       <c r="W7" s="70">
@@ -11610,7 +11728,7 @@
       <c r="B8" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="27" t="s">
         <v>86</v>
       </c>
       <c r="D8" s="70" t="s">
@@ -11624,7 +11742,7 @@
         <v>638</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I8" s="71">
         <v>105</v>
@@ -11663,7 +11781,7 @@
       <c r="B9" s="69" t="s">
         <v>374</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="27" t="s">
         <v>92</v>
       </c>
       <c r="D9" s="70" t="s">
@@ -11678,8 +11796,8 @@
       <c r="G9" s="70" t="s">
         <v>201</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>738</v>
+      <c r="H9" s="27" t="s">
+        <v>737</v>
       </c>
       <c r="I9" s="71">
         <v>90</v>
@@ -11693,16 +11811,16 @@
       <c r="L9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="7" t="s">
         <v>724</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="27" t="s">
         <v>380</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="45" t="s">
         <v>377</v>
       </c>
-      <c r="P9" s="29" t="s">
+      <c r="P9" s="78" t="s">
         <v>375</v>
       </c>
       <c r="T9" s="1" t="s">
@@ -11779,7 +11897,7 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B11" s="69" t="s">
         <v>82</v>
@@ -11817,16 +11935,16 @@
       <c r="O11" s="67" t="s">
         <v>537</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>766</v>
+      <c r="P11" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>762</v>
       </c>
       <c r="R11" s="28" t="s">
         <v>535</v>
       </c>
-      <c r="S11" s="3"/>
+      <c r="S11" s="7"/>
       <c r="T11" s="1" t="s">
         <v>597</v>
       </c>
@@ -11917,7 +12035,7 @@
         <v>296</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="I13" s="71">
         <v>90</v>
@@ -11963,7 +12081,7 @@
       <c r="B14" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="70" t="s">
@@ -11973,11 +12091,11 @@
         <v>46006</v>
       </c>
       <c r="F14" s="70"/>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="27" t="s">
         <v>201</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I14" s="71">
         <v>85</v>
@@ -11994,16 +12112,16 @@
       <c r="M14" s="7" t="s">
         <v>649</v>
       </c>
-      <c r="N14" s="13" t="s">
+      <c r="N14" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="45" t="s">
         <v>305</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="V14" s="6" t="s">
+      <c r="V14" s="27" t="s">
         <v>294</v>
       </c>
       <c r="W14" s="70">
@@ -12015,12 +12133,12 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B15" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="70" t="s">
@@ -12034,39 +12152,39 @@
         <v>201</v>
       </c>
       <c r="H15" s="70" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="I15" s="71">
         <v>60</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="K15" s="26" t="s">
+      <c r="K15" s="44" t="s">
         <v>590</v>
       </c>
       <c r="L15" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="7" t="s">
         <v>725</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="N15" s="45" t="s">
+        <v>754</v>
+      </c>
+      <c r="O15" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="P15" s="48" t="s">
+        <v>751</v>
+      </c>
+      <c r="Q15" s="48" t="s">
         <v>756</v>
       </c>
-      <c r="O15" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="P15" s="17" t="s">
-        <v>753</v>
-      </c>
-      <c r="Q15" s="17" t="s">
-        <v>758</v>
-      </c>
-      <c r="R15" s="20" t="s">
+      <c r="R15" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="S15" s="6"/>
+      <c r="S15" s="27"/>
       <c r="T15" s="1" t="s">
         <v>597</v>
       </c>
@@ -12100,7 +12218,7 @@
         <v>201</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="I16" s="71">
         <v>105</v>
@@ -12154,7 +12272,7 @@
         <v>201</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I17" s="71">
         <v>105</v>
@@ -12193,13 +12311,13 @@
       <c r="B18" s="69" t="s">
         <v>414</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="70" t="s">
         <v>323</v>
       </c>
-      <c r="E18" s="77">
+      <c r="E18" s="76">
         <v>46007</v>
       </c>
       <c r="F18" s="70" t="s">
@@ -12215,26 +12333,26 @@
         <v>95</v>
       </c>
       <c r="J18" s="71"/>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="27" t="s">
         <v>590</v>
       </c>
       <c r="L18" s="1"/>
-      <c r="N18" s="29" t="s">
+      <c r="N18" s="78" t="s">
         <v>415</v>
       </c>
-      <c r="O18" s="3" t="s">
+      <c r="O18" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="P18" s="3" t="s">
+      <c r="P18" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="Q18" s="3" t="s">
+      <c r="Q18" s="7" t="s">
         <v>470</v>
       </c>
       <c r="T18" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="V18" s="6" t="s">
+      <c r="V18" s="27" t="s">
         <v>208</v>
       </c>
       <c r="W18" s="70">
@@ -12246,7 +12364,7 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B19" s="69" t="s">
         <v>628</v>
@@ -12265,7 +12383,7 @@
         <v>201</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="I19" s="71" t="s">
         <v>698</v>
@@ -12284,7 +12402,7 @@
       <c r="O19" s="48" t="s">
         <v>170</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="P19" s="27" t="s">
         <v>730</v>
       </c>
       <c r="T19" s="1" t="s">
@@ -12301,29 +12419,26 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="B20" s="69" t="s">
         <v>342</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="70" t="s">
         <v>324</v>
       </c>
-      <c r="E20" s="77">
+      <c r="E20" s="76">
         <v>46006</v>
       </c>
       <c r="F20" s="70" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G20" s="70" t="s">
         <v>201</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="I20" s="71">
         <v>80</v>
@@ -12359,12 +12474,12 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="27" t="s">
         <v>353</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -12387,88 +12502,33 @@
         <v>29</v>
       </c>
       <c r="L21" s="1"/>
-      <c r="N21" s="17" t="s">
+      <c r="N21" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="O21" s="17" t="s">
+      <c r="O21" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="P21" s="7" t="s">
         <v>190</v>
       </c>
       <c r="T21" s="34" t="s">
-        <v>760</v>
-      </c>
-      <c r="V21" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="V21" s="27" t="s">
         <v>208</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>357</v>
       </c>
       <c r="X21" s="34" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I22" s="11"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I23" s="11"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B24" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="70" t="s">
-        <v>327</v>
-      </c>
-      <c r="E24" s="25">
-        <v>45992</v>
-      </c>
-      <c r="F24" s="70"/>
-      <c r="G24" s="70" t="s">
-        <v>201</v>
-      </c>
-      <c r="H24" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="I24" s="71">
-        <v>125</v>
-      </c>
-      <c r="J24" s="70" t="s">
-        <v>205</v>
-      </c>
-      <c r="K24" s="44" t="s">
-        <v>220</v>
-      </c>
-      <c r="L24" s="44"/>
-      <c r="M24" s="7" t="s">
-        <v>640</v>
-      </c>
-      <c r="N24" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="O24" s="68" t="s">
-        <v>510</v>
-      </c>
-      <c r="V24" s="70" t="s">
-        <v>206</v>
-      </c>
-      <c r="W24" s="70">
-        <v>4704</v>
-      </c>
-      <c r="X24" s="70" t="s">
-        <v>597</v>
-      </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B25" s="69" t="s">
@@ -12583,7 +12643,7 @@
         <v>201</v>
       </c>
       <c r="H27" s="66" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I27" s="71">
         <v>80</v>
@@ -12631,11 +12691,11 @@
         <v>46006</v>
       </c>
       <c r="F28" s="70"/>
-      <c r="G28" s="78" t="s">
+      <c r="G28" s="77" t="s">
         <v>621</v>
       </c>
       <c r="H28" s="70" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I28" s="71">
         <v>85</v>
@@ -12676,58 +12736,150 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I29" s="11"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
+      <c r="B29" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>317</v>
+      </c>
+      <c r="E29" s="63">
+        <v>45993</v>
+      </c>
+      <c r="F29" s="70" t="s">
+        <v>269</v>
+      </c>
+      <c r="G29" s="70" t="s">
+        <v>201</v>
+      </c>
+      <c r="H29" s="70" t="s">
+        <v>732</v>
+      </c>
+      <c r="I29" s="71">
+        <v>125</v>
+      </c>
+      <c r="J29" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="K29" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="L29" s="44" t="s">
+        <v>508</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="N29" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="O29" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="P29" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q29" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="R29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="V29" s="70" t="s">
+        <v>206</v>
+      </c>
+      <c r="W29" s="70">
+        <v>4704</v>
+      </c>
+      <c r="X29" s="70" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I30" s="11"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B30" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>327</v>
+      </c>
+      <c r="E30" s="63">
+        <v>45992</v>
+      </c>
+      <c r="F30" s="70" t="s">
+        <v>269</v>
+      </c>
+      <c r="G30" s="70" t="s">
+        <v>201</v>
+      </c>
+      <c r="H30" s="70" t="s">
+        <v>203</v>
+      </c>
+      <c r="I30" s="71">
+        <v>125</v>
+      </c>
+      <c r="J30" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="K30" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="L30" s="44"/>
+      <c r="M30" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="N30" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="O30" s="68" t="s">
+        <v>510</v>
+      </c>
+      <c r="V30" s="70" t="s">
+        <v>206</v>
+      </c>
+      <c r="W30" s="70">
+        <v>4704</v>
+      </c>
+      <c r="X30" s="70" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="H31" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="I31" s="11"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
+        <v>742</v>
+      </c>
       <c r="L31" s="1"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="I32" s="11"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="9:18" x14ac:dyDescent="0.2">
-      <c r="I33" s="11"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
+    <row r="33" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="9:18" x14ac:dyDescent="0.2">
-      <c r="I34" s="11"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
+    <row r="34" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="9:18" x14ac:dyDescent="0.2">
-      <c r="I35" s="11"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+    <row r="35" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L35" s="1"/>
     </row>
-    <row r="40" spans="9:18" x14ac:dyDescent="0.2">
-      <c r="R40" s="6"/>
+    <row r="40" spans="12:18" x14ac:dyDescent="0.2">
+      <c r="R40" s="27"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C24" r:id="rId1" xr:uid="{51B5B240-F127-424D-934E-35581681C3C1}"/>
-    <hyperlink ref="K24" r:id="rId2" display="?" xr:uid="{B55DD6F4-6DFA-F748-B417-2D6FE5C2C5B6}"/>
-    <hyperlink ref="N24" r:id="rId3" xr:uid="{6ACA983C-1371-ED47-902A-15D9AD890924}"/>
+    <hyperlink ref="C30" r:id="rId1" xr:uid="{51B5B240-F127-424D-934E-35581681C3C1}"/>
+    <hyperlink ref="K30" r:id="rId2" display="?" xr:uid="{B55DD6F4-6DFA-F748-B417-2D6FE5C2C5B6}"/>
+    <hyperlink ref="N30" r:id="rId3" xr:uid="{6ACA983C-1371-ED47-902A-15D9AD890924}"/>
     <hyperlink ref="C3" r:id="rId4" xr:uid="{909FEFB2-4956-204A-843C-00B985B282CB}"/>
     <hyperlink ref="K3" r:id="rId5" display="https://www.universityofcalifornia.edu/about-us/information-center/doctoral-program" xr:uid="{2D6345EB-9B56-6047-8029-A392A00D013F}"/>
     <hyperlink ref="H3" r:id="rId6" display="Personal History Statement (~1,2p)" xr:uid="{3553C041-D267-DC43-BD94-E0A93A537FD3}"/>
@@ -12788,7 +12940,7 @@
     <hyperlink ref="M13" r:id="rId61" display="GRASP" xr:uid="{DE823A40-C140-DE43-950E-CCA09F47F0EB}"/>
     <hyperlink ref="S4" r:id="rId62" xr:uid="{3107D36A-7816-0540-96C4-74EF2B6CB421}"/>
     <hyperlink ref="Q4" r:id="rId63" xr:uid="{188C7A52-FE43-754F-8376-B52B3291F058}"/>
-    <hyperlink ref="O24" r:id="rId64" xr:uid="{8303D648-D25D-C24E-BEE7-80701D18D5AB}"/>
+    <hyperlink ref="O30" r:id="rId64" xr:uid="{8303D648-D25D-C24E-BEE7-80701D18D5AB}"/>
     <hyperlink ref="R11" r:id="rId65" xr:uid="{C466F216-F9DD-E043-B5E3-FA91388CB9DA}"/>
     <hyperlink ref="O11" r:id="rId66" xr:uid="{9A9F50B7-7E5C-A242-9AA0-8F4A93473724}"/>
     <hyperlink ref="N19" r:id="rId67" xr:uid="{CBE57E7C-0C01-E044-86D1-E1B8FB8205DF}"/>
@@ -12826,7 +12978,7 @@
     <hyperlink ref="P12" r:id="rId99" xr:uid="{9949A074-DDD8-0748-A3D5-D296EE2CB2E6}"/>
     <hyperlink ref="N12" r:id="rId100" xr:uid="{9CA5BC65-45BA-CA4B-BB50-70554955B512}"/>
     <hyperlink ref="H10" r:id="rId101" xr:uid="{68701F73-D566-3C4A-BAB4-5FF42E7B15B1}"/>
-    <hyperlink ref="M24" r:id="rId102" xr:uid="{81606837-51A2-4C4D-8F7C-74672D0A0AE7}"/>
+    <hyperlink ref="M30" r:id="rId102" xr:uid="{81606837-51A2-4C4D-8F7C-74672D0A0AE7}"/>
     <hyperlink ref="M3" r:id="rId103" xr:uid="{4A7FD456-BBDB-5C41-8E50-1899168920A1}"/>
     <hyperlink ref="M4" r:id="rId104" display="IRIM" xr:uid="{07717B9D-4A30-2D46-A24F-29C2EC8A2F57}"/>
     <hyperlink ref="M5" r:id="rId105" xr:uid="{C25FBFE7-937C-674B-8FB8-4203D37F3AFC}"/>
@@ -12859,14 +13011,14 @@
     <hyperlink ref="H9" r:id="rId132" display="Personal Statement (Unlimited)" xr:uid="{71E9B93E-CA71-924E-ABF3-1BF301BAF16A}"/>
     <hyperlink ref="E18" r:id="rId133" display="https://cs.unc.edu/graduate/graduate-admissions/admissions-deadline/" xr:uid="{A8DA038C-62AF-7049-923E-C802B5D0F120}"/>
     <hyperlink ref="C18" r:id="rId134" xr:uid="{1F11307D-180C-7F4E-8F58-3C796024EADC}"/>
-    <hyperlink ref="C2" r:id="rId135" xr:uid="{9BBA89A6-0F3B-DC48-9929-53F346B0AEC8}"/>
-    <hyperlink ref="K2" r:id="rId136" display="?" xr:uid="{44F0BD16-9489-304C-AA7B-73439E846FB2}"/>
-    <hyperlink ref="N2" r:id="rId137" location="people" xr:uid="{8000CF1A-E833-7046-85A6-F8FD94F89DD6}"/>
-    <hyperlink ref="P2" r:id="rId138" xr:uid="{1020D82E-17AD-0843-92AB-4DEFC033D629}"/>
-    <hyperlink ref="O2" r:id="rId139" xr:uid="{47F0EA44-5277-5445-BB7A-BDDCF1050356}"/>
-    <hyperlink ref="Q2" r:id="rId140" xr:uid="{44235266-313A-EB4D-822B-20B3417A492B}"/>
-    <hyperlink ref="R2" r:id="rId141" xr:uid="{0DA4B984-247B-014C-AF10-7B70DD5E6E5B}"/>
-    <hyperlink ref="M2" r:id="rId142" xr:uid="{CF22B631-12A1-DF4D-B5B5-DC93A74172A4}"/>
+    <hyperlink ref="C29" r:id="rId135" xr:uid="{9BBA89A6-0F3B-DC48-9929-53F346B0AEC8}"/>
+    <hyperlink ref="K29" r:id="rId136" display="?" xr:uid="{44F0BD16-9489-304C-AA7B-73439E846FB2}"/>
+    <hyperlink ref="N29" r:id="rId137" location="people" xr:uid="{8000CF1A-E833-7046-85A6-F8FD94F89DD6}"/>
+    <hyperlink ref="P29" r:id="rId138" xr:uid="{1020D82E-17AD-0843-92AB-4DEFC033D629}"/>
+    <hyperlink ref="O29" r:id="rId139" xr:uid="{47F0EA44-5277-5445-BB7A-BDDCF1050356}"/>
+    <hyperlink ref="Q29" r:id="rId140" xr:uid="{44235266-313A-EB4D-822B-20B3417A492B}"/>
+    <hyperlink ref="R29" r:id="rId141" xr:uid="{0DA4B984-247B-014C-AF10-7B70DD5E6E5B}"/>
+    <hyperlink ref="M29" r:id="rId142" xr:uid="{CF22B631-12A1-DF4D-B5B5-DC93A74172A4}"/>
     <hyperlink ref="N5" r:id="rId143" xr:uid="{76506796-C1E0-6349-ABE0-0536ABD45091}"/>
     <hyperlink ref="K8" r:id="rId144" display="12%(36/313)" xr:uid="{B150AADE-A14F-C24C-B2FF-F7650A150E11}"/>
     <hyperlink ref="C8" r:id="rId145" xr:uid="{BEB53160-CC16-4B4F-8683-4043A3679F0E}"/>
@@ -12901,6 +13053,8 @@
     <hyperlink ref="O15" r:id="rId174" xr:uid="{1C8BE2D9-25D8-7040-AFBB-870B90C39D41}"/>
     <hyperlink ref="P11" r:id="rId175" xr:uid="{5A0E2DC6-7112-CB42-8B13-0D714E7EE698}"/>
     <hyperlink ref="Q11" r:id="rId176" xr:uid="{BC88C10D-785F-534A-B349-B2DA4E7086B9}"/>
+    <hyperlink ref="J5" r:id="rId177" display="Accept LoR after deadline" xr:uid="{240597F5-DBD6-B24D-A770-7F680D569E5B}"/>
+    <hyperlink ref="C2" r:id="rId178" xr:uid="{89DD44D2-039D-2D4B-BF53-164442E02001}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
